--- a/doc/테스트/E2E_시나리오_CASE1-6.xlsx
+++ b/doc/테스트/E2E_시나리오_CASE1-6.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -610,16 +610,16 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:27</t>
+          <t>2026-09-28 23:34</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>0145ba81dd</t>
+          <t>09cbe67b2a</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>24/0/0</t>
+          <t>26/0/0</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="J5" s="10" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0</v>
@@ -665,50 +665,50 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:25</t>
+          <t>2026-09-28 23:33</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>0145ba81dd</t>
+          <t>09cbe67b2a</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>24/0/0</t>
+          <t>26/0/0</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" s="10" t="n">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:14</t>
+          <t>2026-09-28 23:27</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>6c4132ffc2</t>
+          <t>0145ba81dd</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>22/0/0</t>
+          <t>24/0/0</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="J7" s="10" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0</v>
@@ -775,50 +775,50 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:13</t>
+          <t>2026-09-28 23:25</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>6d745d5356</t>
+          <t>0145ba81dd</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>22/0/0</t>
+          <t>24/0/0</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0</v>
@@ -830,109 +830,105 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:11</t>
+          <t>2026-09-28 11:14</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>b65bfe6fe8</t>
+          <t>6c4132ffc2</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>20/2/0</t>
+          <t>22/0/0</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>20</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>93</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>C2-19, C2-20</t>
-        </is>
-      </c>
+      <c r="M9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:24</t>
+          <t>2026-09-28 11:13</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>0ae6ece6c2</t>
+          <t>6d745d5356</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>18/0/0</t>
+          <t>22/0/0</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="10" t="n">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
@@ -944,76 +940,80 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:22</t>
+          <t>2026-09-28 11:11</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>f40fc41604</t>
+          <t>b65bfe6fe8</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>18/0/0</t>
+          <t>20/2/0</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>89</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>20</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="6" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>C2-19, C2-20</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:21</t>
+          <t>2026-09-28 09:24</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>f40fc41604</t>
+          <t>0ae6ece6c2</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1023,26 +1023,26 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:16</t>
+          <t>2026-09-28 09:22</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>51a52339ab</t>
+          <t>f40fc41604</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>16/0/0</t>
+          <t>18/0/0</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="J13" s="10" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
@@ -1109,50 +1109,50 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:07</t>
+          <t>2026-09-28 09:21</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>07a26890b5</t>
+          <t>f40fc41604</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>16/0/0</t>
+          <t>18/0/0</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
@@ -1164,21 +1164,21 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:06</t>
+          <t>2026-09-28 09:16</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>07a26890b5</t>
+          <t>51a52339ab</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>16/1/0</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1206,28 +1206,24 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J15" s="11" t="n">
-        <v>86</v>
+      <c r="J15" s="10" t="n">
+        <v>87</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>C1-13</t>
-        </is>
-      </c>
+      <c r="M15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:06</t>
+          <t>2026-09-28 09:07</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1237,7 +1233,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1247,26 +1243,26 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J16" s="10" t="n">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
@@ -1278,38 +1274,38 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:46</t>
+          <t>2026-09-28 09:06</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>b588bab9b3</t>
+          <t>07a26890b5</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>16/1/0</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
+          <t>16/0/0</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>15/0/0</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
           <t>14/0/0</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>15/0/0</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>14/0/0</t>
-        </is>
-      </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
           <t>12/0/0</t>
@@ -1320,63 +1316,67 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J17" s="10" t="n">
-        <v>85</v>
+      <c r="J17" s="11" t="n">
+        <v>86</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>C1-13</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:40</t>
+          <t>2026-09-28 09:06</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>d5213f9578</t>
+          <t>07a26890b5</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>16/0/0</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="10" t="n">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
@@ -1384,98 +1384,90 @@
       <c r="L18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>사업계획서 체크포인트(C2-14) 추가 후 전체 통과</t>
-        </is>
-      </c>
+      <c r="M18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:39</t>
+          <t>2026-09-28 08:46</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>d5213f9578</t>
+          <t>b588bab9b3</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>13/1/0</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>13</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>C2-14</t>
-        </is>
-      </c>
+      <c r="M19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:26</t>
+          <t>2026-09-28 08:40</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>9b24f45ce5</t>
+          <t>d5213f9578</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -1485,16 +1477,16 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J20" s="10" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0</v>
@@ -1502,90 +1494,98 @@
       <c r="L20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>사업계획서 체크포인트(C2-14) 추가 후 전체 통과</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:25</t>
+          <t>2026-09-28 08:39</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>9b24f45ce5</t>
+          <t>d5213f9578</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>13/1/0</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>84</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>13</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>C2-14</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:24</t>
+          <t>2026-09-28 08:26</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>22774ad88d</t>
+          <t>9b24f45ce5</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>16/1/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -1595,41 +1595,37 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>83</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>14</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>C1-02</t>
-        </is>
-      </c>
+      <c r="M22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:01</t>
+          <t>2026-09-28 08:25</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>a6368b6542</t>
+          <t>9b24f45ce5</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -1675,21 +1671,21 @@
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:00</t>
+          <t>2026-09-28 08:24</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>a6368b6542</t>
+          <t>22774ad88d</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>16/1/0</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1717,33 +1713,33 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J24" s="10" t="n">
-        <v>84</v>
+      <c r="J24" s="11" t="n">
+        <v>83</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>보드 수정 반영(기동 코드 주석 위치) — 해시 변경</t>
+          <t>C1-02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:58</t>
+          <t>2026-09-28 08:01</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>a59d40dd6c</t>
+          <t>a6368b6542</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -1789,16 +1785,16 @@
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:56</t>
+          <t>2026-09-28 08:00</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>a59d40dd6c</t>
+          <t>a6368b6542</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
@@ -1808,7 +1804,7 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>11/2/0</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
@@ -1831,28 +1827,28 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J26" s="11" t="n">
-        <v>82</v>
+      <c r="J26" s="10" t="n">
+        <v>84</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>C2-09, C2-10 — 하네스 선택자 결함(보드 무관), 3회차에서 수정 확인</t>
+          <t>보드 수정 반영(기동 코드 주석 위치) — 해시 변경</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:56</t>
+          <t>2026-09-28 07:58</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -1867,31 +1863,31 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J27" s="10" t="n">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
@@ -1899,7 +1895,121 @@
       <c r="L27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>a59d40dd6c</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>17/0/0</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>11/2/0</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>15/0/0</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>14/0/0</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>12/0/0</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>C2-09, C2-10 — 하네스 선택자 결함(보드 무관), 3회차에서 수정 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>a59d40dd6c</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>17/0/0</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>CASE1만 실행(하네스 점검)</t>
         </is>
@@ -1996,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AP21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2149,8 @@
     <col width="40" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="40" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="40" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2055,6 +2167,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2273,6 +2386,17 @@
           <t>23회차 메모</t>
         </is>
       </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 결과
+2026-09-28 23:34</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2403,6 +2527,12 @@
         </is>
       </c>
       <c r="AN5" s="6" t="inlineStr"/>
+      <c r="AO5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2537,6 +2667,12 @@
         </is>
       </c>
       <c r="AN6" s="6" t="inlineStr"/>
+      <c r="AO6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2671,6 +2807,12 @@
         </is>
       </c>
       <c r="AN7" s="6" t="inlineStr"/>
+      <c r="AO7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2801,6 +2943,12 @@
         </is>
       </c>
       <c r="AN8" s="6" t="inlineStr"/>
+      <c r="AO8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2931,6 +3079,12 @@
         </is>
       </c>
       <c r="AN9" s="6" t="inlineStr"/>
+      <c r="AO9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -3065,6 +3219,12 @@
         </is>
       </c>
       <c r="AN10" s="6" t="inlineStr"/>
+      <c r="AO10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -3195,6 +3355,12 @@
         </is>
       </c>
       <c r="AN11" s="6" t="inlineStr"/>
+      <c r="AO11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -3329,6 +3495,12 @@
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr"/>
+      <c r="AO12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -3459,6 +3631,12 @@
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr"/>
+      <c r="AO13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -3589,6 +3767,12 @@
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr"/>
+      <c r="AO14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -3719,6 +3903,12 @@
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr"/>
+      <c r="AO15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -3849,6 +4039,12 @@
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr"/>
+      <c r="AO16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -3987,6 +4183,12 @@
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr"/>
+      <c r="AO17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -4117,6 +4319,12 @@
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr"/>
+      <c r="AO18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -4247,6 +4455,12 @@
         </is>
       </c>
       <c r="AN19" s="6" t="inlineStr"/>
+      <c r="AO19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -4377,6 +4591,12 @@
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr"/>
+      <c r="AO20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -4507,6 +4727,12 @@
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr"/>
+      <c r="AO21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP21" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4519,7 +4745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV28"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4570,6 +4796,10 @@
     <col width="40" customWidth="1" min="46" max="46"/>
     <col width="12" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="40" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="40" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4586,6 +4816,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4848,6 +5079,28 @@
           <t>23회차 메모</t>
         </is>
       </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>24회차 결과
+2026-09-28 23:33</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>24회차 메모</t>
+        </is>
+      </c>
+      <c r="AY4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 결과
+2026-09-28 23:34</t>
+        </is>
+      </c>
+      <c r="AZ4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -5006,6 +5259,18 @@
         </is>
       </c>
       <c r="AV5" s="6" t="inlineStr"/>
+      <c r="AW5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX5" s="6" t="inlineStr"/>
+      <c r="AY5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -5160,6 +5425,18 @@
         </is>
       </c>
       <c r="AV6" s="6" t="inlineStr"/>
+      <c r="AW6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX6" s="6" t="inlineStr"/>
+      <c r="AY6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -5314,6 +5591,18 @@
         </is>
       </c>
       <c r="AV7" s="6" t="inlineStr"/>
+      <c r="AW7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX7" s="6" t="inlineStr"/>
+      <c r="AY7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -5472,6 +5761,18 @@
         </is>
       </c>
       <c r="AV8" s="6" t="inlineStr"/>
+      <c r="AW8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX8" s="6" t="inlineStr"/>
+      <c r="AY8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -5626,6 +5927,18 @@
         </is>
       </c>
       <c r="AV9" s="6" t="inlineStr"/>
+      <c r="AW9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX9" s="6" t="inlineStr"/>
+      <c r="AY9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -5780,6 +6093,18 @@
         </is>
       </c>
       <c r="AV10" s="6" t="inlineStr"/>
+      <c r="AW10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX10" s="6" t="inlineStr"/>
+      <c r="AY10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -5934,6 +6259,18 @@
         </is>
       </c>
       <c r="AV11" s="6" t="inlineStr"/>
+      <c r="AW11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX11" s="6" t="inlineStr"/>
+      <c r="AY11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -6088,6 +6425,18 @@
         </is>
       </c>
       <c r="AV12" s="6" t="inlineStr"/>
+      <c r="AW12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr"/>
+      <c r="AY12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -6246,6 +6595,18 @@
         </is>
       </c>
       <c r="AV13" s="6" t="inlineStr"/>
+      <c r="AW13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX13" s="6" t="inlineStr"/>
+      <c r="AY13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -6408,6 +6769,18 @@
         </is>
       </c>
       <c r="AV14" s="6" t="inlineStr"/>
+      <c r="AW14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr"/>
+      <c r="AY14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -6562,6 +6935,18 @@
         </is>
       </c>
       <c r="AV15" s="6" t="inlineStr"/>
+      <c r="AW15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr"/>
+      <c r="AY15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -6716,6 +7101,18 @@
         </is>
       </c>
       <c r="AV16" s="6" t="inlineStr"/>
+      <c r="AW16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr"/>
+      <c r="AY16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -6870,6 +7267,18 @@
         </is>
       </c>
       <c r="AV17" s="6" t="inlineStr"/>
+      <c r="AW17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr"/>
+      <c r="AY17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -6996,6 +7405,18 @@
         </is>
       </c>
       <c r="AV18" s="6" t="inlineStr"/>
+      <c r="AW18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX18" s="6" t="inlineStr"/>
+      <c r="AY18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -7100,6 +7521,18 @@
         </is>
       </c>
       <c r="AV19" s="6" t="inlineStr"/>
+      <c r="AW19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr"/>
+      <c r="AY19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -7204,6 +7637,18 @@
         </is>
       </c>
       <c r="AV20" s="6" t="inlineStr"/>
+      <c r="AW20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX20" s="6" t="inlineStr"/>
+      <c r="AY20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -7284,6 +7729,18 @@
         </is>
       </c>
       <c r="AV21" s="6" t="inlineStr"/>
+      <c r="AW21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX21" s="6" t="inlineStr"/>
+      <c r="AY21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -7364,6 +7821,18 @@
         </is>
       </c>
       <c r="AV22" s="6" t="inlineStr"/>
+      <c r="AW22" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr"/>
+      <c r="AY22" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -7430,6 +7899,18 @@
         </is>
       </c>
       <c r="AV23" s="6" t="inlineStr"/>
+      <c r="AW23" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX23" s="6" t="inlineStr"/>
+      <c r="AY23" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -7496,6 +7977,18 @@
         </is>
       </c>
       <c r="AV24" s="6" t="inlineStr"/>
+      <c r="AW24" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX24" s="6" t="inlineStr"/>
+      <c r="AY24" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -7558,6 +8051,18 @@
         </is>
       </c>
       <c r="AV25" s="6" t="inlineStr"/>
+      <c r="AW25" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX25" s="6" t="inlineStr"/>
+      <c r="AY25" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -7620,6 +8125,18 @@
         </is>
       </c>
       <c r="AV26" s="6" t="inlineStr"/>
+      <c r="AW26" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX26" s="6" t="inlineStr"/>
+      <c r="AY26" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -7659,6 +8176,18 @@
         </is>
       </c>
       <c r="AV27" s="6" t="inlineStr"/>
+      <c r="AW27" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX27" s="6" t="inlineStr"/>
+      <c r="AY27" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -7703,6 +8232,106 @@
         </is>
       </c>
       <c r="AV28" s="6" t="inlineStr"/>
+      <c r="AW28" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX28" s="6" t="inlineStr"/>
+      <c r="AY28" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>C2-25</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>명함으로 등록(텍스트)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>기관 탭 «명함으로 등록» → 텍스트 → 명함 읽기 → 등록 창 열기 → 기관 저장 → 담당자 저장</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>유형 추정값·새 기관 기본, 기관 창(유형·이름·전화·주소·상세·메모) 채움, 담당자 창(이름·직함 분리·휴대폰·이메일) 채움, 저장 후 연결</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>명함에 있는 값만</t>
+        </is>
+      </c>
+      <c r="AW29" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX29" s="6" t="inlineStr"/>
+      <c r="AY29" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>C2-26</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>명함으로 등록(사진·기존 기관)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>담당자 탭 «명함으로 등록» → PNG 명함 → 읽기 → 등록 창 열기 → 취소 → 정리</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>이미지 1장 전달, 기존 기관 기본 선택·유형 숨김, 중복 담당자 경고, 담당자 창 기관 = 기존</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>사진 저장 안 함</t>
+        </is>
+      </c>
+      <c r="AW30" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AX30" s="6" t="inlineStr"/>
+      <c r="AY30" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AZ30" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7715,2159 +8344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="40" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="40" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="40" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="40" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="40" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
-    <col width="40" customWidth="1" min="38" max="38"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>CASE3 — 골프 양말 · 봉조 자동화 편직기 (원공고)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 4쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>조작</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>기대 결과</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>자동화 방식</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>근거</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2회차 결과
-2026-09-28 07:56</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2회차 메모</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>3회차 결과
-2026-09-28 07:58</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>3회차 메모</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>4회차 결과
-2026-09-28 08:00</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>4회차 메모</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>5회차 결과
-2026-09-28 08:01</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>5회차 메모</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>6회차 결과
-2026-09-28 08:24</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>6회차 메모</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>7회차 결과
-2026-09-28 08:25</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>7회차 메모</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>10회차 결과
-2026-09-28 08:40</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>10회차 메모</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>11회차 결과
-2026-09-28 08:46</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>11회차 메모</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>13회차 결과
-2026-09-28 09:06</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>13회차 메모</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>14회차 결과
-2026-09-28 09:07</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>14회차 메모</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>15회차 결과
-2026-09-28 09:16</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>15회차 메모</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>17회차 결과
-2026-09-28 09:22</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>17회차 메모</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>18회차 결과
-2026-09-28 09:24</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>18회차 메모</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>21회차 결과
-2026-09-28 11:14</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>21회차 메모</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>22회차 결과
-2026-09-28 23:25</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>22회차 메모</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>23회차 결과
-2026-09-28 23:27</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>23회차 메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>C3-01</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>이사를 소공인 담당자로</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>기관 1곳에 대표·이사 등록, 과제 소공인 = 이사</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>상세 소공인 «[테스트] C3담당 이사»</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>실경영은 담당 이사</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr"/>
-      <c r="U5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V5" s="6" t="inlineStr"/>
-      <c r="W5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X5" s="6" t="inlineStr"/>
-      <c r="Y5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z5" s="6" t="inlineStr"/>
-      <c r="AA5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB5" s="6" t="inlineStr"/>
-      <c r="AC5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD5" s="6" t="inlineStr"/>
-      <c r="AE5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF5" s="6" t="inlineStr"/>
-      <c r="AG5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH5" s="6" t="inlineStr"/>
-      <c r="AI5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ5" s="6" t="inlineStr"/>
-      <c r="AK5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>C3-02</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>존칭</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>1단계 보내기 → 소공인 · 일정 조율</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>«[테스트] C3담당 이사님 안녕하세요.»(«이사 대표님» 아님)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr"/>
-      <c r="O6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T6" s="6" t="inlineStr"/>
-      <c r="U6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V6" s="6" t="inlineStr"/>
-      <c r="W6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X6" s="6" t="inlineStr"/>
-      <c r="Y6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z6" s="6" t="inlineStr"/>
-      <c r="AA6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB6" s="6" t="inlineStr"/>
-      <c r="AC6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD6" s="6" t="inlineStr"/>
-      <c r="AE6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF6" s="6" t="inlineStr"/>
-      <c r="AG6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH6" s="6" t="inlineStr"/>
-      <c r="AI6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ6" s="6" t="inlineStr"/>
-      <c r="AK6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>C3-03</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>마스터 반영</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>이사 전화 010-0000-3334로 수정</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>과제 스냅샷 전화 자동 반영</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr"/>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr"/>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr"/>
-      <c r="U7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V7" s="6" t="inlineStr"/>
-      <c r="W7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X7" s="6" t="inlineStr"/>
-      <c r="Y7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z7" s="6" t="inlineStr"/>
-      <c r="AA7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB7" s="6" t="inlineStr"/>
-      <c r="AC7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD7" s="6" t="inlineStr"/>
-      <c r="AE7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF7" s="6" t="inlineStr"/>
-      <c r="AG7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH7" s="6" t="inlineStr"/>
-      <c r="AI7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ7" s="6" t="inlineStr"/>
-      <c r="AK7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>C3-04</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>전화 검색</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>검색 «01000003334»</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>결과에 과제·담당자</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr"/>
-      <c r="O8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr"/>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T8" s="6" t="inlineStr"/>
-      <c r="U8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V8" s="6" t="inlineStr"/>
-      <c r="W8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X8" s="6" t="inlineStr"/>
-      <c r="Y8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z8" s="6" t="inlineStr"/>
-      <c r="AA8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB8" s="6" t="inlineStr"/>
-      <c r="AC8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD8" s="6" t="inlineStr"/>
-      <c r="AE8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF8" s="6" t="inlineStr"/>
-      <c r="AG8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH8" s="6" t="inlineStr"/>
-      <c r="AI8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ8" s="6" t="inlineStr"/>
-      <c r="AK8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>C3-05</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>검색 변형</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>«3334», «0000-3334», «0000 3334»</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>같은 결과</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr"/>
-      <c r="O9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr"/>
-      <c r="U9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V9" s="6" t="inlineStr"/>
-      <c r="W9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X9" s="6" t="inlineStr"/>
-      <c r="Y9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z9" s="6" t="inlineStr"/>
-      <c r="AA9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB9" s="6" t="inlineStr"/>
-      <c r="AC9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD9" s="6" t="inlineStr"/>
-      <c r="AE9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF9" s="6" t="inlineStr"/>
-      <c r="AG9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH9" s="6" t="inlineStr"/>
-      <c r="AI9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ9" s="6" t="inlineStr"/>
-      <c r="AK9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>C3-06</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>견적 오기</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>S/W 단가 «6,600,00» 입력 → 거부 확인 후 «6,000,000»으로 등록</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>«쉼표 자리가 맞지 않습니다» 오류로 저장 안 됨 → 6,000,000 저장</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>원문 합계 «6,600,00원»</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr"/>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr"/>
-      <c r="O10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T10" s="6" t="inlineStr"/>
-      <c r="U10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V10" s="6" t="inlineStr"/>
-      <c r="W10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X10" s="6" t="inlineStr"/>
-      <c r="Y10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z10" s="6" t="inlineStr"/>
-      <c r="AA10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB10" s="6" t="inlineStr"/>
-      <c r="AC10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD10" s="6" t="inlineStr"/>
-      <c r="AE10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF10" s="6" t="inlineStr"/>
-      <c r="AG10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH10" s="6" t="inlineStr"/>
-      <c r="AI10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ10" s="6" t="inlineStr"/>
-      <c r="AK10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>C3-07</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>편직기 2, S/W 1</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>«검토 중 · 2대»</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr"/>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T11" s="6" t="inlineStr"/>
-      <c r="U11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V11" s="6" t="inlineStr"/>
-      <c r="W11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X11" s="6" t="inlineStr"/>
-      <c r="Y11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z11" s="6" t="inlineStr"/>
-      <c r="AA11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB11" s="6" t="inlineStr"/>
-      <c r="AC11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD11" s="6" t="inlineStr"/>
-      <c r="AE11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF11" s="6" t="inlineStr"/>
-      <c r="AG11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH11" s="6" t="inlineStr"/>
-      <c r="AI11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>C3-08</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>납기 예정</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>6단계 예정일 T+30(입금 후 30일)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>카드 «다음 … 장비 공급 D-30»</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>납기 입금 후 30일 이내</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr"/>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr"/>
-      <c r="O12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr"/>
-      <c r="Q12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr"/>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T12" s="6" t="inlineStr"/>
-      <c r="U12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr"/>
-      <c r="W12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X12" s="6" t="inlineStr"/>
-      <c r="Y12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z12" s="6" t="inlineStr"/>
-      <c r="AA12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB12" s="6" t="inlineStr"/>
-      <c r="AC12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD12" s="6" t="inlineStr"/>
-      <c r="AE12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF12" s="6" t="inlineStr"/>
-      <c r="AG12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH12" s="6" t="inlineStr"/>
-      <c r="AI12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>C3-09</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>캘린더 등록</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>«일정» 탭 6단계 «등록»</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 1건, «등록됨», 활동 «캘린더 · 자동»</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr"/>
-      <c r="O13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr"/>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr"/>
-      <c r="U13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr"/>
-      <c r="W13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X13" s="6" t="inlineStr"/>
-      <c r="Y13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z13" s="6" t="inlineStr"/>
-      <c r="AA13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB13" s="6" t="inlineStr"/>
-      <c r="AC13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD13" s="6" t="inlineStr"/>
-      <c r="AE13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF13" s="6" t="inlineStr"/>
-      <c r="AG13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH13" s="6" t="inlineStr"/>
-      <c r="AI13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>C3-10</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 내용</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>목 이벤트 확인</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>제목 «[스마트제조] … · 6. 장비 공급», 종일, 시작 T+30·끝 T+31, Asia/Seoul</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>캘린더 앱 확인 대체</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr"/>
-      <c r="O14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr"/>
-      <c r="Q14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr"/>
-      <c r="U14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr"/>
-      <c r="W14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X14" s="6" t="inlineStr"/>
-      <c r="Y14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z14" s="6" t="inlineStr"/>
-      <c r="AA14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB14" s="6" t="inlineStr"/>
-      <c r="AC14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD14" s="6" t="inlineStr"/>
-      <c r="AE14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF14" s="6" t="inlineStr"/>
-      <c r="AG14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH14" s="6" t="inlineStr"/>
-      <c r="AI14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>C3-11</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>날짜 변경 감지</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>예정일 T+35 → «오늘» 캘린더 미등록</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>«날짜 변경 (캘린더 T+30)»</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr"/>
-      <c r="O15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr"/>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr"/>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr"/>
-      <c r="U15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr"/>
-      <c r="W15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X15" s="6" t="inlineStr"/>
-      <c r="Y15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z15" s="6" t="inlineStr"/>
-      <c r="AA15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB15" s="6" t="inlineStr"/>
-      <c r="AC15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD15" s="6" t="inlineStr"/>
-      <c r="AE15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF15" s="6" t="inlineStr"/>
-      <c r="AG15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH15" s="6" t="inlineStr"/>
-      <c r="AI15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>C3-12</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>날짜 수정</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>«일정» 탭 «날짜 수정»</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 T+35, 활동 제목 «날짜 변경 T+30 → T+35», 미등록 목록에서 사라짐</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr"/>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr"/>
-      <c r="O16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr"/>
-      <c r="U16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr"/>
-      <c r="W16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X16" s="6" t="inlineStr"/>
-      <c r="Y16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z16" s="6" t="inlineStr"/>
-      <c r="AA16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB16" s="6" t="inlineStr"/>
-      <c r="AC16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD16" s="6" t="inlineStr"/>
-      <c r="AE16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF16" s="6" t="inlineStr"/>
-      <c r="AG16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH16" s="6" t="inlineStr"/>
-      <c r="AI16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>C3-13</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>메모 → 초안</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>2단계 메모 후 수행일지 2차 초안</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>활동요약에 «· (MM-DD) 원문»</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr"/>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr"/>
-      <c r="O17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr"/>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T17" s="6" t="inlineStr"/>
-      <c r="U17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr"/>
-      <c r="W17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X17" s="6" t="inlineStr"/>
-      <c r="Y17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z17" s="6" t="inlineStr"/>
-      <c r="AA17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB17" s="6" t="inlineStr"/>
-      <c r="AC17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD17" s="6" t="inlineStr"/>
-      <c r="AE17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF17" s="6" t="inlineStr"/>
-      <c r="AG17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH17" s="6" t="inlineStr"/>
-      <c r="AI17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>C3-14</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>서명란</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>2차 초안 서명란 확인</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>«신청인(대표) : [테스트] C3담당» — 이사 이름(질문 3)</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr"/>
-      <c r="O18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr"/>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T18" s="6" t="inlineStr"/>
-      <c r="U18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr"/>
-      <c r="W18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X18" s="6" t="inlineStr"/>
-      <c r="Y18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z18" s="6" t="inlineStr"/>
-      <c r="AA18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB18" s="6" t="inlineStr"/>
-      <c r="AC18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD18" s="6" t="inlineStr"/>
-      <c r="AE18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF18" s="6" t="inlineStr"/>
-      <c r="AG18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH18" s="6" t="inlineStr"/>
-      <c r="AI18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>C3-15</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>정리</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>과제 삭제</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>«구글 캘린더에 등록된 일정 1건은 지워지지 않았습니다» 안내, 이후 장비·담당자·기관 삭제</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr"/>
-      <c r="O19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr"/>
-      <c r="Q19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr"/>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T19" s="6" t="inlineStr"/>
-      <c r="U19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr"/>
-      <c r="W19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X19" s="6" t="inlineStr"/>
-      <c r="Y19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z19" s="6" t="inlineStr"/>
-      <c r="AA19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB19" s="6" t="inlineStr"/>
-      <c r="AC19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD19" s="6" t="inlineStr"/>
-      <c r="AE19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF19" s="6" t="inlineStr"/>
-      <c r="AG19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH19" s="6" t="inlineStr"/>
-      <c r="AI19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL19" s="6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN18"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9915,17 +8392,18 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE4 — 지르코니아 치과 보철 · CNC 밀링 (추가공고)</t>
+          <t>CASE3 — 골프 양말 · 봉조 자동화 편직기 (원공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 5쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
-        </is>
-      </c>
-    </row>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 4쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10025,145 +8503,145 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>8회차 결과
-2026-09-28 08:26</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>8회차 메모</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
           <t>10회차 결과
 2026-09-28 08:40</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>10회차 메모</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>11회차 결과
 2026-09-28 08:46</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>11회차 메모</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>13회차 결과
 2026-09-28 09:06</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>13회차 메모</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>14회차 결과
 2026-09-28 09:07</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>14회차 메모</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>15회차 결과
 2026-09-28 09:16</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>15회차 메모</t>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>17회차 결과
 2026-09-28 09:22</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>17회차 메모</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>18회차 결과
 2026-09-28 09:24</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>18회차 메모</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>21회차 결과
 2026-09-28 11:14</t>
         </is>
       </c>
-      <c r="AJ4" s="3" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>21회차 메모</t>
         </is>
       </c>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>22회차 결과
 2026-09-28 23:25</t>
         </is>
       </c>
-      <c r="AL4" s="3" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr">
         <is>
           <t>22회차 메모</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <t>23회차 결과
 2026-09-28 23:27</t>
         </is>
       </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>23회차 메모</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 결과
+2026-09-28 23:34</t>
+        </is>
+      </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>23회차 메모</t>
+          <t>25회차 메모</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C4-01</t>
+          <t>C3-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>공고 미지정</t>
+          <t>이사를 소공인 담당자로</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>공고 구분 비우고 과제 생성</t>
+          <t>기관 1곳에 대표·이사 등록, 과제 소공인 = 이사</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>카드 «공고 미확인», 상세 경고 문구</t>
+          <t>상세 소공인 «[테스트] C3담당 이사»</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -10171,7 +8649,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>실경영은 담당 이사</t>
+        </is>
+      </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -10278,22 +8760,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C4-02</t>
+          <t>C3-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>미확인 필터</t>
+          <t>존칭</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>공고 필터 = 공고 미확인</t>
+          <t>1단계 보내기 → 소공인 · 일정 조율</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>이 과제 보임</t>
+          <t>«[테스트] C3담당 이사님 안녕하세요.»(«이사 대표님» 아님)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -10408,22 +8890,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C4-03</t>
+          <t>C3-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>추가공고 지정</t>
+          <t>마스터 반영</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>상세 공고 구분 = 추가공고</t>
+          <t>이사 전화 010-0000-3334로 수정</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>배지 «추가공고», 원공고 필터에서 숨김, CSV 공고 열 «추가공고»</t>
+          <t>과제 스냅샷 전화 자동 반영</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -10431,11 +8913,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>연매출 2억원 미만</t>
-        </is>
-      </c>
+      <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -10542,34 +9020,30 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C4-04</t>
+          <t>C3-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 화면</t>
+          <t>전화 검색</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>390×844 에뮬레이션</t>
+          <t>검색 «01000003334»</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>하단 탭바(더보기 보임, 기관 탭 숨김), 가로 넘침 없음, 범례 숨김</t>
+          <t>결과에 과제·담당자</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>실기기 대체</t>
-        </is>
-      </c>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -10676,27 +9150,27 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C4-05</t>
+          <t>C3-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 진단 입력</t>
+          <t>검색 변형</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>1차 진단 5칸 입력, 칸 이동은 탭 한 번</t>
+          <t>«3334», «0000-3334», «0000 3334»</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>입력칸 16px, 다음 칸으로 포커스 이동, 값 저장</t>
+          <t>같은 결과</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -10806,32 +9280,32 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C4-06</t>
+          <t>C3-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>입력 중 재그리기</t>
+          <t>견적 오기</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>입력 중 스냅샷 강제 발행</t>
+          <t>S/W 단가 «6,600,00» 입력 → 거부 확인 후 «6,000,000»으로 등록</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>입력 중인 글자 유지</t>
+          <t>«쉼표 자리가 맞지 않습니다» 오류로 저장 안 됨 → 6,000,000 저장</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>다른 기기 수정 대체</t>
+          <t>원문 합계 «6,600,00원»</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -10940,22 +9414,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C4-07</t>
+          <t>C3-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2차 진단 입력</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>②·③·기록 수준 입력</t>
+          <t>편직기 2, S/W 1</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>«검토 중 · 2대»</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -11070,22 +9544,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C4-08</t>
+          <t>C3-08</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1차 초안 반영</t>
+          <t>납기 예정</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>1단계 초안</t>
+          <t>6단계 예정일 T+30(입금 후 30일)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>입력 5칸 원문, ⑤⑥⑦ «미확인 — …»</t>
+          <t>카드 «다음 … 장비 공급 D-30»</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -11093,7 +9567,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>납기 입금 후 30일 이내</t>
+        </is>
+      </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -11200,27 +9678,27 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C4-09</t>
+          <t>C3-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2·3차 초안</t>
+          <t>캘린더 등록</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>2·7단계 초안</t>
+          <t>«일정» 탭 6단계 «등록»</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>2차 ③ 원문, 3차 향후 사후관리 «미확인 — …»</t>
+          <t>이벤트 1건, «등록됨», 활동 «캘린더 · 자동»</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
@@ -11330,32 +9808,32 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C4-10</t>
+          <t>C3-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>수치 비생성</t>
+          <t>이벤트 내용</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>초안 숫자 대조</t>
+          <t>목 이벤트 확인</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>6개·10개 외 수치(%, 증가율) 없음</t>
+          <t>제목 «[스마트제조] … · 6. 장비 공급», 종일, 시작 T+30·끝 T+31, Asia/Seoul</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>하루 6개 → 10개</t>
+          <t>캘린더 앱 확인 대체</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -11464,22 +9942,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C4-11</t>
+          <t>C3-11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>결과보고서 초안</t>
+          <t>날짜 변경 감지</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>8단계 초안</t>
+          <t>예정일 T+35 → «오늘» 캘린더 미등록</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>3. KPI에 1차 ②·④·2차 ② 진단 줄, 5.에 기록 방식 줄, 초안 표시</t>
+          <t>«날짜 변경 (캘린더 T+30)»</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -11594,27 +10072,27 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C4-12</t>
+          <t>C3-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>장비·자산 → 초안</t>
+          <t>날짜 수정</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>덴탈 CNC밀링기·Dentalsoft 등록, 자산 각 1 → 3차·결과보고서 초안</t>
+          <t>«일정» 탭 «날짜 수정»</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>3차 «④ 도입 장비»·결과보고서 4에 «[H/W] 덴탈 CNC밀링기 마닉스 5SA × 1대 (검토 중)»·«[S/W] Dentalsoft × 1식 (검토 중)», 금액 없음</t>
+          <t>이벤트 T+35, 활동 제목 «날짜 변경 T+30 → T+35», 미등록 목록에서 사라짐</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
@@ -11724,27 +10202,27 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>C4-13</t>
+          <t>C3-13</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 더보기</t>
+          <t>메모 → 초안</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>더보기 → 자산</t>
+          <t>2단계 메모 후 수행일지 2차 초안</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>메뉴 열림, 버튼 라벨 «자산 ▴», 자산 목록</t>
+          <t>활동요약에 «· (MM-DD) 원문»</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
@@ -11854,22 +10332,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>C4-14</t>
+          <t>C3-14</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>정리</t>
+          <t>서명란</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>과제·장비·담당자·기관 삭제</t>
+          <t>2차 초안 서명란 확인</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>삭제 완료</t>
+          <t>«신청인(대표) : [테스트] C3담당» — 이사 이름(질문 3)</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -11980,19 +10458,149 @@
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>C3-15</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>정리</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>«구글 캘린더에 등록된 일정 1건은 지워지지 않았습니다» 안내, 이후 장비·담당자·기관 삭제</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr"/>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr"/>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr"/>
+      <c r="U19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr"/>
+      <c r="W19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X19" s="6" t="inlineStr"/>
+      <c r="Y19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z19" s="6" t="inlineStr"/>
+      <c r="AA19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB19" s="6" t="inlineStr"/>
+      <c r="AC19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD19" s="6" t="inlineStr"/>
+      <c r="AE19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF19" s="6" t="inlineStr"/>
+      <c r="AG19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr"/>
+      <c r="AI19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ19" s="6" t="inlineStr"/>
+      <c r="AK19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL19" s="6" t="inlineStr"/>
+      <c r="AM19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN19" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL16"/>
+  <dimension ref="A1:AP18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12033,22 +10641,27 @@
     <col width="40" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="40" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="40" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="40" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE5 — 친환경 벽지 · 라텍스 프린터 + 자동견적 (추가공고)</t>
+          <t>CASE4 — 지르코니아 치과 보철 · CNC 밀링 (추가공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 6쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
-        </is>
-      </c>
-    </row>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 5쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -12148,134 +10761,156 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
+          <t>8회차 결과
+2026-09-28 08:26</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>8회차 메모</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
           <t>10회차 결과
 2026-09-28 08:40</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>10회차 메모</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>11회차 결과
 2026-09-28 08:46</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>11회차 메모</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>13회차 결과
 2026-09-28 09:06</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>13회차 메모</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>14회차 결과
 2026-09-28 09:07</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>14회차 메모</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>15회차 결과
 2026-09-28 09:16</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>15회차 메모</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>17회차 결과
 2026-09-28 09:22</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>17회차 메모</t>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>18회차 결과
 2026-09-28 09:24</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>18회차 메모</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>21회차 결과
 2026-09-28 11:14</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr">
         <is>
           <t>21회차 메모</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <t>22회차 결과
 2026-09-28 23:25</t>
         </is>
       </c>
-      <c r="AJ4" s="3" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>22회차 메모</t>
         </is>
       </c>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>23회차 결과
 2026-09-28 23:27</t>
         </is>
       </c>
-      <c r="AL4" s="3" t="inlineStr">
+      <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>23회차 메모</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 결과
+2026-09-28 23:34</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 메모</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C5-01</t>
+          <t>C4-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>지연·다음 예정</t>
+          <t>공고 미지정</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>추가공고 과제, 1단계 T-3, 2단계 T+4</t>
+          <t>공고 구분 비우고 과제 생성</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>카드 «다음 … 1차 방문 D+3», «지연 1»</t>
+          <t>카드 «공고 미확인», 상세 경고 문구</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -12380,26 +11015,38 @@
         </is>
       </c>
       <c r="AL5" s="6" t="inlineStr"/>
+      <c r="AM5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN5" s="6" t="inlineStr"/>
+      <c r="AO5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C5-02</t>
+          <t>C4-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>오늘 탭</t>
+          <t>미확인 필터</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>«오늘» 탭</t>
+          <t>공고 필터 = 공고 미확인</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>기한 경과에 1단계, 7일 안의 방문에 2단계</t>
+          <t>이 과제 보임</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -12504,26 +11151,38 @@
         </is>
       </c>
       <c r="AL6" s="6" t="inlineStr"/>
+      <c r="AM6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN6" s="6" t="inlineStr"/>
+      <c r="AO6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C5-03</t>
+          <t>C4-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>완료 누락 알림</t>
+          <t>추가공고 지정</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>1단계 산출물 미체크로 완료</t>
+          <t>상세 공고 구분 = 추가공고</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>알림에 «현장진단표, 1차 방문 확인 서명», 상태 «완료» 유지</t>
+          <t>배지 «추가공고», 원공고 필터에서 숨김, CSV 공고 열 «추가공고»</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -12531,7 +11190,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>연매출 2억원 미만</t>
+        </is>
+      </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -12628,34 +11291,50 @@
         </is>
       </c>
       <c r="AL7" s="6" t="inlineStr"/>
+      <c r="AM7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN7" s="6" t="inlineStr"/>
+      <c r="AO7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C5-04</t>
+          <t>C4-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>알림 줄어듦</t>
+          <t>휴대폰 화면</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>현장진단표 체크 → 나머지 체크</t>
+          <t>390×844 에뮬레이션</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>알림 1개로 줄고, 다 체크하면 사라짐</t>
+          <t>하단 탭바(더보기 보임, 기관 탭 숨김), 가로 넘침 없음, 범례 숨김</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>실기기 대체</t>
+        </is>
+      </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -12752,31 +11431,43 @@
         </is>
       </c>
       <c r="AL8" s="6" t="inlineStr"/>
+      <c r="AM8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN8" s="6" t="inlineStr"/>
+      <c r="AO8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C5-05</t>
+          <t>C4-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>서류 미수집</t>
+          <t>휴대폰 진단 입력</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>체크 1개 해제 → «오늘»</t>
+          <t>1차 진단 5칸 입력, 칸 이동은 탭 한 번</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>서명·서류 미수집에 1단계</t>
+          <t>입력칸 16px, 다음 칸으로 포커스 이동, 값 저장</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -12876,34 +11567,50 @@
         </is>
       </c>
       <c r="AL9" s="6" t="inlineStr"/>
+      <c r="AM9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN9" s="6" t="inlineStr"/>
+      <c r="AO9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C5-06</t>
+          <t>C4-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>카톡 수동 기록</t>
+          <t>입력 중 재그리기</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>수행일지 송부 → 카톡 보냄 기록</t>
+          <t>입력 중 스냅샷 강제 발행</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>«카톡으로 보냄을 … 기록했습니다(수동 기록)», 버튼 «기록됨» 비활성</t>
+          <t>입력 중인 글자 유지</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr"/>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>다른 기기 수정 대체</t>
+        </is>
+      </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -13000,26 +11707,38 @@
         </is>
       </c>
       <c r="AL10" s="6" t="inlineStr"/>
+      <c r="AM10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN10" s="6" t="inlineStr"/>
+      <c r="AO10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C5-07</t>
+          <t>C4-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>기록자</t>
+          <t>2차 진단 입력</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>«활동» 탭</t>
+          <t>②·③·기록 수준 입력</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>«카톡 · 수동», 기록자 «시험자»</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -13124,26 +11843,38 @@
         </is>
       </c>
       <c r="AL11" s="6" t="inlineStr"/>
+      <c r="AM11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN11" s="6" t="inlineStr"/>
+      <c r="AO11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C5-08</t>
+          <t>C4-08</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>메모 작성자</t>
+          <t>1차 초안 반영</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>1단계 메모</t>
+          <t>1단계 초안</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>머리 «… · 시험자», 한국 시간</t>
+          <t>입력 5칸 원문, ⑤⑥⑦ «미확인 — …»</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -13151,11 +11882,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>KPI 설정 필요</t>
-        </is>
-      </c>
+      <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -13252,26 +11979,38 @@
         </is>
       </c>
       <c r="AL12" s="6" t="inlineStr"/>
+      <c r="AM12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN12" s="6" t="inlineStr"/>
+      <c r="AO12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C5-09</t>
+          <t>C4-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>포함 품목</t>
+          <t>2·3차 초안</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>LATEX 730 / CNYX RIP(단가 비움) / QT-AI LITE 5,286,000</t>
+          <t>2·7단계 초안</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>RIP 단가 «—»</t>
+          <t>2차 ③ 원문, 3차 향후 사후관리 «미확인 — …»</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -13279,11 +12018,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>RIP «포함», S/W 할인 −714,000</t>
-        </is>
-      </c>
+      <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -13380,26 +12115,38 @@
         </is>
       </c>
       <c r="AL13" s="6" t="inlineStr"/>
+      <c r="AM13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN13" s="6" t="inlineStr"/>
+      <c r="AO13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C5-10</t>
+          <t>C4-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>자산</t>
+          <t>수치 비생성</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>3건 등록 → 과제 상세 견적 합계</t>
+          <t>초안 숫자 대조</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>H/W 37,000,000원, «단가 없는 장비 1건 제외(CNYX RIP)», 경고 «1,174,889원 초과»</t>
+          <t>6개·10개 외 수치(%, 증가율) 없음</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -13407,7 +12154,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>하루 6개 → 10개</t>
+        </is>
+      </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -13504,26 +12255,38 @@
         </is>
       </c>
       <c r="AL14" s="6" t="inlineStr"/>
+      <c r="AM14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN14" s="6" t="inlineStr"/>
+      <c r="AO14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C5-11</t>
+          <t>C4-11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>전체 백업</t>
+          <t>결과보고서 초안</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>«전체 백업 (JSON)»</t>
+          <t>8단계 초안</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>파일명·counts·notice «extra»·by id 포함, 이름 «시험자» 미포함</t>
+          <t>3. KPI에 1차 ②·④·2차 ② 진단 줄, 5.에 기록 방식 줄, 초안 표시</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -13628,26 +12391,38 @@
         </is>
       </c>
       <c r="AL15" s="6" t="inlineStr"/>
+      <c r="AM15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN15" s="6" t="inlineStr"/>
+      <c r="AO15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C5-12</t>
+          <t>C4-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>정리</t>
+          <t>장비·자산 → 초안</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>과제·CASE5 장비 삭제(QT-AI 공급사 유지)</t>
+          <t>덴탈 CNC밀링기·Dentalsoft 등록, 자산 각 1 → 3차·결과보고서 초안</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>삭제 완료</t>
+          <t>3차 «④ 도입 장비»·결과보고서 4에 «[H/W] 덴탈 CNC밀링기 마닉스 5SA × 1대 (검토 중)»·«[S/W] Dentalsoft × 1식 (검토 중)», 금액 없음</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -13752,19 +12527,303 @@
         </is>
       </c>
       <c r="AL16" s="6" t="inlineStr"/>
+      <c r="AM16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN16" s="6" t="inlineStr"/>
+      <c r="AO16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>C4-13</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>휴대폰 더보기</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>더보기 → 자산</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>메뉴 열림, 버튼 라벨 «자산 ▴», 자산 목록</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr"/>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr"/>
+      <c r="U17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr"/>
+      <c r="W17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X17" s="6" t="inlineStr"/>
+      <c r="Y17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z17" s="6" t="inlineStr"/>
+      <c r="AA17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB17" s="6" t="inlineStr"/>
+      <c r="AC17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD17" s="6" t="inlineStr"/>
+      <c r="AE17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF17" s="6" t="inlineStr"/>
+      <c r="AG17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr"/>
+      <c r="AI17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ17" s="6" t="inlineStr"/>
+      <c r="AK17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL17" s="6" t="inlineStr"/>
+      <c r="AM17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN17" s="6" t="inlineStr"/>
+      <c r="AO17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>C4-14</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>정리</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>과제·장비·담당자·기관 삭제</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>삭제 완료</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr"/>
+      <c r="U18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr"/>
+      <c r="W18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X18" s="6" t="inlineStr"/>
+      <c r="Y18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z18" s="6" t="inlineStr"/>
+      <c r="AA18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB18" s="6" t="inlineStr"/>
+      <c r="AC18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD18" s="6" t="inlineStr"/>
+      <c r="AE18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF18" s="6" t="inlineStr"/>
+      <c r="AG18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH18" s="6" t="inlineStr"/>
+      <c r="AI18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ18" s="6" t="inlineStr"/>
+      <c r="AK18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL18" s="6" t="inlineStr"/>
+      <c r="AM18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN18" s="6" t="inlineStr"/>
+      <c r="AO18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP18" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL17"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13805,22 +12864,25 @@
     <col width="40" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="40" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="40" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE6 — 디자인·출력 · 솔벤 플로터·재단기 (원공고)</t>
+          <t>CASE5 — 친환경 벽지 · 라텍스 프린터 + 자동견적 (추가공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 7쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
-        </is>
-      </c>
-    </row>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 6쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -14028,26 +13090,37 @@
           <t>23회차 메모</t>
         </is>
       </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 결과
+2026-09-28 23:34</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C6-01</t>
+          <t>C5-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>과제 생성</t>
+          <t>지연·다음 예정</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>과제(원공고), H/W 공급사 기관</t>
+          <t>추가공고 과제, 1단계 T-3, 2단계 T+4</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>카드 «다음 … 1차 방문 D+3», «지연 1»</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -14055,11 +13128,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>연매출 2억원 이상</t>
-        </is>
-      </c>
+      <c r="F5" s="6" t="inlineStr"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -14156,26 +13225,32 @@
         </is>
       </c>
       <c r="AL5" s="6" t="inlineStr"/>
+      <c r="AM5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C6-02</t>
+          <t>C5-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>오늘 탭</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>VG3-640 / RET-2002 / QT-AI BASIC(QT-AI 공급사, LITE 표기 메모)</t>
+          <t>«오늘» 탭</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>기한 경과에 1단계, 7일 안의 방문에 2단계</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -14183,11 +13258,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>품명 BASIC·사양 LITE형 불일치</t>
-        </is>
-      </c>
+      <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -14284,26 +13355,32 @@
         </is>
       </c>
       <c r="AL6" s="6" t="inlineStr"/>
+      <c r="AM6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C6-03</t>
+          <t>C5-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>공급사 장비</t>
+          <t>완료 누락 알림</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>QT-AI 공급사 기관 상세</t>
+          <t>1단계 산출물 미체크로 완료</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>«공급 장비»에 QT-AI 자동견적(BASIC)</t>
+          <t>알림에 «현장진단표, 1차 방문 확인 서명», 상태 «완료» 유지</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -14408,26 +13485,32 @@
         </is>
       </c>
       <c r="AL7" s="6" t="inlineStr"/>
+      <c r="AM7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C6-04</t>
+          <t>C5-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>자산</t>
+          <t>알림 줄어듦</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>3건</t>
+          <t>현장진단표 체크 → 나머지 체크</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>알림 1개로 줄고, 다 체크하면 사라짐</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -14532,26 +13615,32 @@
         </is>
       </c>
       <c r="AL8" s="6" t="inlineStr"/>
+      <c r="AM8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C6-05</t>
+          <t>C5-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>장비 필터</t>
+          <t>서류 미수집</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>장비 탭 S/W 칩 + 검색 «QT-AI»</t>
+          <t>체크 1개 해제 → «오늘»</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>QT-AI BASIC만</t>
+          <t>서명·서류 미수집에 1단계</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -14656,26 +13745,32 @@
         </is>
       </c>
       <c r="AL9" s="6" t="inlineStr"/>
+      <c r="AM9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C6-06</t>
+          <t>C5-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>통합 검색</t>
+          <t>카톡 수동 기록</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>상단 검색 «VG3» → 결과 클릭</t>
+          <t>수행일지 송부 → 카톡 보냄 기록</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>장비 상세, 도입된 자산에 과제</t>
+          <t>«카톡으로 보냄을 … 기록했습니다(수동 기록)», 버튼 «기록됨» 비활성</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -14780,26 +13875,32 @@
         </is>
       </c>
       <c r="AL10" s="6" t="inlineStr"/>
+      <c r="AM10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C6-07</t>
+          <t>C5-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>S/W 한도</t>
+          <t>기록자</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>42,383,000÷9=4,709,222 &lt; 6,000,000 → 과제 상세 확인 + 메모</t>
+          <t>«활동» 탭</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>H/W 42,383,000원, 경고 «1,290,778원 초과»</t>
+          <t>«카톡 · 수동», 기록자 «시험자»</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -14904,10 +14005,1882 @@
         </is>
       </c>
       <c r="AL11" s="6" t="inlineStr"/>
+      <c r="AM11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>C5-08</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>메모 작성자</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>1단계 메모</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>머리 «… · 시험자», 한국 시간</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>KPI 설정 필요</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr"/>
+      <c r="O12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr"/>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr"/>
+      <c r="U12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V12" s="6" t="inlineStr"/>
+      <c r="W12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X12" s="6" t="inlineStr"/>
+      <c r="Y12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z12" s="6" t="inlineStr"/>
+      <c r="AA12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB12" s="6" t="inlineStr"/>
+      <c r="AC12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD12" s="6" t="inlineStr"/>
+      <c r="AE12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF12" s="6" t="inlineStr"/>
+      <c r="AG12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr"/>
+      <c r="AI12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ12" s="6" t="inlineStr"/>
+      <c r="AK12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL12" s="6" t="inlineStr"/>
+      <c r="AM12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>C5-09</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>포함 품목</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>LATEX 730 / CNYX RIP(단가 비움) / QT-AI LITE 5,286,000</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>RIP 단가 «—»</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>RIP «포함», S/W 할인 −714,000</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr"/>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr"/>
+      <c r="U13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr"/>
+      <c r="W13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr"/>
+      <c r="Y13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z13" s="6" t="inlineStr"/>
+      <c r="AA13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB13" s="6" t="inlineStr"/>
+      <c r="AC13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD13" s="6" t="inlineStr"/>
+      <c r="AE13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF13" s="6" t="inlineStr"/>
+      <c r="AG13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr"/>
+      <c r="AI13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ13" s="6" t="inlineStr"/>
+      <c r="AK13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL13" s="6" t="inlineStr"/>
+      <c r="AM13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>C5-10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>3건 등록 → 과제 상세 견적 합계</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>H/W 37,000,000원, «단가 없는 장비 1건 제외(CNYX RIP)», 경고 «1,174,889원 초과»</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr"/>
+      <c r="U14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr"/>
+      <c r="W14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X14" s="6" t="inlineStr"/>
+      <c r="Y14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z14" s="6" t="inlineStr"/>
+      <c r="AA14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB14" s="6" t="inlineStr"/>
+      <c r="AC14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD14" s="6" t="inlineStr"/>
+      <c r="AE14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF14" s="6" t="inlineStr"/>
+      <c r="AG14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr"/>
+      <c r="AI14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ14" s="6" t="inlineStr"/>
+      <c r="AK14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL14" s="6" t="inlineStr"/>
+      <c r="AM14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>C5-11</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>전체 백업</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>«전체 백업 (JSON)»</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>파일명·counts·notice «extra»·by id 포함, 이름 «시험자» 미포함</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr"/>
+      <c r="U15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr"/>
+      <c r="W15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr"/>
+      <c r="Y15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z15" s="6" t="inlineStr"/>
+      <c r="AA15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB15" s="6" t="inlineStr"/>
+      <c r="AC15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD15" s="6" t="inlineStr"/>
+      <c r="AE15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF15" s="6" t="inlineStr"/>
+      <c r="AG15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr"/>
+      <c r="AI15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ15" s="6" t="inlineStr"/>
+      <c r="AK15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL15" s="6" t="inlineStr"/>
+      <c r="AM15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>C5-12</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>정리</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>과제·CASE5 장비 삭제(QT-AI 공급사 유지)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>삭제 완료</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr"/>
+      <c r="U16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr"/>
+      <c r="W16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr"/>
+      <c r="Y16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z16" s="6" t="inlineStr"/>
+      <c r="AA16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB16" s="6" t="inlineStr"/>
+      <c r="AC16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD16" s="6" t="inlineStr"/>
+      <c r="AE16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF16" s="6" t="inlineStr"/>
+      <c r="AG16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH16" s="6" t="inlineStr"/>
+      <c r="AI16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ16" s="6" t="inlineStr"/>
+      <c r="AK16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL16" s="6" t="inlineStr"/>
+      <c r="AM16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN16" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="40" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="40" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="40" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="40" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="40" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="40" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="40" customWidth="1" min="40" max="40"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>CASE6 — 디자인·출력 · 솔벤 플로터·재단기 (원공고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 7쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>조작</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>기대 결과</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>자동화 방식</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2회차 결과
+2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2회차 메모</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>3회차 결과
+2026-09-28 07:58</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>3회차 메모</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>4회차 결과
+2026-09-28 08:00</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>4회차 메모</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>5회차 결과
+2026-09-28 08:01</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>5회차 메모</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>6회차 결과
+2026-09-28 08:24</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>6회차 메모</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>7회차 결과
+2026-09-28 08:25</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>7회차 메모</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>10회차 결과
+2026-09-28 08:40</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>10회차 메모</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>11회차 결과
+2026-09-28 08:46</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>11회차 메모</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>13회차 결과
+2026-09-28 09:06</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>13회차 메모</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>14회차 결과
+2026-09-28 09:07</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>14회차 메모</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>15회차 결과
+2026-09-28 09:16</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>15회차 메모</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>17회차 결과
+2026-09-28 09:22</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>17회차 메모</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>18회차 결과
+2026-09-28 09:24</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>18회차 메모</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>21회차 결과
+2026-09-28 11:14</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>21회차 메모</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>22회차 결과
+2026-09-28 23:25</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>22회차 메모</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>23회차 결과
+2026-09-28 23:27</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>23회차 메모</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 결과
+2026-09-28 23:34</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>C6-01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>과제 생성</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>과제(원공고), H/W 공급사 기관</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>연매출 2억원 이상</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr"/>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr"/>
+      <c r="U5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr"/>
+      <c r="W5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="inlineStr"/>
+      <c r="Y5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z5" s="6" t="inlineStr"/>
+      <c r="AA5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB5" s="6" t="inlineStr"/>
+      <c r="AC5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD5" s="6" t="inlineStr"/>
+      <c r="AE5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF5" s="6" t="inlineStr"/>
+      <c r="AG5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH5" s="6" t="inlineStr"/>
+      <c r="AI5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ5" s="6" t="inlineStr"/>
+      <c r="AK5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL5" s="6" t="inlineStr"/>
+      <c r="AM5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>C6-02</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>VG3-640 / RET-2002 / QT-AI BASIC(QT-AI 공급사, LITE 표기 메모)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>품명 BASIC·사양 LITE형 불일치</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr"/>
+      <c r="U6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr"/>
+      <c r="W6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X6" s="6" t="inlineStr"/>
+      <c r="Y6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="inlineStr"/>
+      <c r="AA6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB6" s="6" t="inlineStr"/>
+      <c r="AC6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD6" s="6" t="inlineStr"/>
+      <c r="AE6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF6" s="6" t="inlineStr"/>
+      <c r="AG6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH6" s="6" t="inlineStr"/>
+      <c r="AI6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ6" s="6" t="inlineStr"/>
+      <c r="AK6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL6" s="6" t="inlineStr"/>
+      <c r="AM6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>C6-03</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>공급사 장비</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>QT-AI 공급사 기관 상세</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>«공급 장비»에 QT-AI 자동견적(BASIC)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr"/>
+      <c r="U7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr"/>
+      <c r="Y7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="inlineStr"/>
+      <c r="AA7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB7" s="6" t="inlineStr"/>
+      <c r="AC7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD7" s="6" t="inlineStr"/>
+      <c r="AE7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF7" s="6" t="inlineStr"/>
+      <c r="AG7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH7" s="6" t="inlineStr"/>
+      <c r="AI7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ7" s="6" t="inlineStr"/>
+      <c r="AK7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL7" s="6" t="inlineStr"/>
+      <c r="AM7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>C6-04</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>3건</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X8" s="6" t="inlineStr"/>
+      <c r="Y8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z8" s="6" t="inlineStr"/>
+      <c r="AA8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB8" s="6" t="inlineStr"/>
+      <c r="AC8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD8" s="6" t="inlineStr"/>
+      <c r="AE8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF8" s="6" t="inlineStr"/>
+      <c r="AG8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH8" s="6" t="inlineStr"/>
+      <c r="AI8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ8" s="6" t="inlineStr"/>
+      <c r="AK8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL8" s="6" t="inlineStr"/>
+      <c r="AM8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>C6-05</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>장비 필터</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>장비 탭 S/W 칩 + 검색 «QT-AI»</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>QT-AI BASIC만</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X9" s="6" t="inlineStr"/>
+      <c r="Y9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z9" s="6" t="inlineStr"/>
+      <c r="AA9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB9" s="6" t="inlineStr"/>
+      <c r="AC9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD9" s="6" t="inlineStr"/>
+      <c r="AE9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF9" s="6" t="inlineStr"/>
+      <c r="AG9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH9" s="6" t="inlineStr"/>
+      <c r="AI9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ9" s="6" t="inlineStr"/>
+      <c r="AK9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL9" s="6" t="inlineStr"/>
+      <c r="AM9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>C6-06</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>통합 검색</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>상단 검색 «VG3» → 결과 클릭</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>장비 상세, 도입된 자산에 과제</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr"/>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr"/>
+      <c r="U10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X10" s="6" t="inlineStr"/>
+      <c r="Y10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z10" s="6" t="inlineStr"/>
+      <c r="AA10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB10" s="6" t="inlineStr"/>
+      <c r="AC10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD10" s="6" t="inlineStr"/>
+      <c r="AE10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF10" s="6" t="inlineStr"/>
+      <c r="AG10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH10" s="6" t="inlineStr"/>
+      <c r="AI10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ10" s="6" t="inlineStr"/>
+      <c r="AK10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL10" s="6" t="inlineStr"/>
+      <c r="AM10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>C6-07</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>S/W 한도</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>42,383,000÷9=4,709,222 &lt; 6,000,000 → 과제 상세 확인 + 메모</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>H/W 42,383,000원, 경고 «1,290,778원 초과»</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr"/>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr"/>
+      <c r="U11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X11" s="6" t="inlineStr"/>
+      <c r="Y11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z11" s="6" t="inlineStr"/>
+      <c r="AA11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB11" s="6" t="inlineStr"/>
+      <c r="AC11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD11" s="6" t="inlineStr"/>
+      <c r="AE11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF11" s="6" t="inlineStr"/>
+      <c r="AG11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr"/>
+      <c r="AI11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ11" s="6" t="inlineStr"/>
+      <c r="AK11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL11" s="6" t="inlineStr"/>
+      <c r="AM11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>C6-08</t>
         </is>
       </c>
@@ -15028,6 +16001,12 @@
         </is>
       </c>
       <c r="AL12" s="6" t="inlineStr"/>
+      <c r="AM12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -15152,6 +16131,12 @@
         </is>
       </c>
       <c r="AL13" s="6" t="inlineStr"/>
+      <c r="AM13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -15276,6 +16261,12 @@
         </is>
       </c>
       <c r="AL14" s="6" t="inlineStr"/>
+      <c r="AM14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -15400,6 +16391,12 @@
         </is>
       </c>
       <c r="AL15" s="6" t="inlineStr"/>
+      <c r="AM15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -15524,6 +16521,12 @@
         </is>
       </c>
       <c r="AL16" s="6" t="inlineStr"/>
+      <c r="AM16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -15648,6 +16651,12 @@
         </is>
       </c>
       <c r="AL17" s="6" t="inlineStr"/>
+      <c r="AM17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN17" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/doc/테스트/E2E_시나리오_CASE1-6.xlsx
+++ b/doc/테스트/E2E_시나리오_CASE1-6.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -610,16 +610,16 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:34</t>
+          <t>2026-09-28 23:48</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>09cbe67b2a</t>
+          <t>084be90acd</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>26/0/0</t>
+          <t>27/0/0</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="J5" s="10" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0</v>
@@ -665,16 +665,16 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:33</t>
+          <t>2026-09-28 23:47</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>09cbe67b2a</t>
+          <t>084be90acd</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>26/0/0</t>
+          <t>27/0/0</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="J6" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0</v>
@@ -720,16 +720,16 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:27</t>
+          <t>2026-09-28 23:34</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>0145ba81dd</t>
+          <t>09cbe67b2a</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>24/0/0</t>
+          <t>26/0/0</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="J7" s="10" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0</v>
@@ -775,50 +775,50 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:25</t>
+          <t>2026-09-28 23:33</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>0145ba81dd</t>
+          <t>09cbe67b2a</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>24/0/0</t>
+          <t>26/0/0</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0</v>
@@ -830,16 +830,16 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:14</t>
+          <t>2026-09-28 23:27</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>6c4132ffc2</t>
+          <t>0145ba81dd</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>22/0/0</t>
+          <t>24/0/0</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="J9" s="10" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
@@ -885,50 +885,50 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:13</t>
+          <t>2026-09-28 23:25</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>6d745d5356</t>
+          <t>0145ba81dd</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>22/0/0</t>
+          <t>24/0/0</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J10" s="10" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
@@ -940,109 +940,105 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:11</t>
+          <t>2026-09-28 11:14</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>b65bfe6fe8</t>
+          <t>6c4132ffc2</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>20/2/0</t>
+          <t>22/0/0</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>20</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>93</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>C2-19, C2-20</t>
-        </is>
-      </c>
+      <c r="M11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:24</t>
+          <t>2026-09-28 11:13</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>0ae6ece6c2</t>
+          <t>6d745d5356</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>18/0/0</t>
+          <t>22/0/0</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
@@ -1054,76 +1050,80 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:22</t>
+          <t>2026-09-28 11:11</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>f40fc41604</t>
+          <t>b65bfe6fe8</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>18/0/0</t>
+          <t>20/2/0</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>89</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>20</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="6" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>C2-19, C2-20</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:21</t>
+          <t>2026-09-28 09:24</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>f40fc41604</t>
+          <t>0ae6ece6c2</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1133,26 +1133,26 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
@@ -1164,16 +1164,16 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:16</t>
+          <t>2026-09-28 09:22</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>51a52339ab</t>
+          <t>f40fc41604</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>16/0/0</t>
+          <t>18/0/0</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="J15" s="10" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
@@ -1219,50 +1219,50 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:07</t>
+          <t>2026-09-28 09:21</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>07a26890b5</t>
+          <t>f40fc41604</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>16/0/0</t>
+          <t>18/0/0</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="10" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
@@ -1274,21 +1274,21 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:06</t>
+          <t>2026-09-28 09:16</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>07a26890b5</t>
+          <t>51a52339ab</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>16/1/0</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1316,28 +1316,24 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J17" s="11" t="n">
-        <v>86</v>
+      <c r="J17" s="10" t="n">
+        <v>87</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>C1-13</t>
-        </is>
-      </c>
+      <c r="M17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:06</t>
+          <t>2026-09-28 09:07</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1347,7 +1343,7 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1357,26 +1353,26 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J18" s="10" t="n">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
@@ -1388,38 +1384,38 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:46</t>
+          <t>2026-09-28 09:06</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>b588bab9b3</t>
+          <t>07a26890b5</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>16/1/0</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
+          <t>16/0/0</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>15/0/0</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
           <t>14/0/0</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>15/0/0</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>14/0/0</t>
-        </is>
-      </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
           <t>12/0/0</t>
@@ -1430,63 +1426,67 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J19" s="10" t="n">
-        <v>85</v>
+      <c r="J19" s="11" t="n">
+        <v>86</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="6" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>C1-13</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:40</t>
+          <t>2026-09-28 09:06</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>d5213f9578</t>
+          <t>07a26890b5</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>16/0/0</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="10" t="n">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0</v>
@@ -1494,98 +1494,90 @@
       <c r="L20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>사업계획서 체크포인트(C2-14) 추가 후 전체 통과</t>
-        </is>
-      </c>
+      <c r="M20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:39</t>
+          <t>2026-09-28 08:46</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>d5213f9578</t>
+          <t>b588bab9b3</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>13/1/0</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>13</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>C2-14</t>
-        </is>
-      </c>
+      <c r="M21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:26</t>
+          <t>2026-09-28 08:40</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>9b24f45ce5</t>
+          <t>d5213f9578</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -1595,16 +1587,16 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J22" s="10" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
@@ -1612,90 +1604,98 @@
       <c r="L22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>사업계획서 체크포인트(C2-14) 추가 후 전체 통과</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:25</t>
+          <t>2026-09-28 08:39</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>9b24f45ce5</t>
+          <t>d5213f9578</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>13/1/0</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>84</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>13</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>C2-14</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:24</t>
+          <t>2026-09-28 08:26</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>22774ad88d</t>
+          <t>9b24f45ce5</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>16/1/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -1705,41 +1705,37 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>83</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>14</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="6" t="inlineStr">
-        <is>
-          <t>C1-02</t>
-        </is>
-      </c>
+      <c r="M24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:01</t>
+          <t>2026-09-28 08:25</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>a6368b6542</t>
+          <t>9b24f45ce5</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -1785,21 +1781,21 @@
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:00</t>
+          <t>2026-09-28 08:24</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>a6368b6542</t>
+          <t>22774ad88d</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>16/1/0</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1827,33 +1823,33 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J26" s="10" t="n">
-        <v>84</v>
+      <c r="J26" s="11" t="n">
+        <v>83</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>보드 수정 반영(기동 코드 주석 위치) — 해시 변경</t>
+          <t>C1-02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:58</t>
+          <t>2026-09-28 08:01</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>a59d40dd6c</t>
+          <t>a6368b6542</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -1899,16 +1895,16 @@
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:56</t>
+          <t>2026-09-28 08:00</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>a59d40dd6c</t>
+          <t>a6368b6542</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -1918,7 +1914,7 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>11/2/0</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
@@ -1941,28 +1937,28 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J28" s="11" t="n">
-        <v>82</v>
+      <c r="J28" s="10" t="n">
+        <v>84</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>C2-09, C2-10 — 하네스 선택자 결함(보드 무관), 3회차에서 수정 확인</t>
+          <t>보드 수정 반영(기동 코드 주석 위치) — 해시 변경</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:56</t>
+          <t>2026-09-28 07:58</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -1977,31 +1973,31 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J29" s="10" t="n">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
@@ -2009,7 +2005,121 @@
       <c r="L29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="6" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>a59d40dd6c</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>17/0/0</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>11/2/0</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>15/0/0</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>14/0/0</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>12/0/0</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>C2-09, C2-10 — 하네스 선택자 결함(보드 무관), 3회차에서 수정 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>a59d40dd6c</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>17/0/0</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
         <is>
           <t>CASE1만 실행(하네스 점검)</t>
         </is>
@@ -2106,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP21"/>
+  <dimension ref="A1:AR21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2151,6 +2261,8 @@
     <col width="40" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="40" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2397,6 +2509,17 @@
           <t>25회차 메모</t>
         </is>
       </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 결과
+2026-09-28 23:48</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2533,6 +2656,12 @@
         </is>
       </c>
       <c r="AP5" s="6" t="inlineStr"/>
+      <c r="AQ5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2673,6 +2802,12 @@
         </is>
       </c>
       <c r="AP6" s="6" t="inlineStr"/>
+      <c r="AQ6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2813,6 +2948,12 @@
         </is>
       </c>
       <c r="AP7" s="6" t="inlineStr"/>
+      <c r="AQ7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2949,6 +3090,12 @@
         </is>
       </c>
       <c r="AP8" s="6" t="inlineStr"/>
+      <c r="AQ8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -3085,6 +3232,12 @@
         </is>
       </c>
       <c r="AP9" s="6" t="inlineStr"/>
+      <c r="AQ9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -3225,6 +3378,12 @@
         </is>
       </c>
       <c r="AP10" s="6" t="inlineStr"/>
+      <c r="AQ10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -3361,6 +3520,12 @@
         </is>
       </c>
       <c r="AP11" s="6" t="inlineStr"/>
+      <c r="AQ11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -3501,6 +3666,12 @@
         </is>
       </c>
       <c r="AP12" s="6" t="inlineStr"/>
+      <c r="AQ12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -3637,6 +3808,12 @@
         </is>
       </c>
       <c r="AP13" s="6" t="inlineStr"/>
+      <c r="AQ13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -3773,6 +3950,12 @@
         </is>
       </c>
       <c r="AP14" s="6" t="inlineStr"/>
+      <c r="AQ14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -3909,6 +4092,12 @@
         </is>
       </c>
       <c r="AP15" s="6" t="inlineStr"/>
+      <c r="AQ15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -4045,6 +4234,12 @@
         </is>
       </c>
       <c r="AP16" s="6" t="inlineStr"/>
+      <c r="AQ16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -4189,6 +4384,12 @@
         </is>
       </c>
       <c r="AP17" s="6" t="inlineStr"/>
+      <c r="AQ17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -4325,6 +4526,12 @@
         </is>
       </c>
       <c r="AP18" s="6" t="inlineStr"/>
+      <c r="AQ18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -4461,6 +4668,12 @@
         </is>
       </c>
       <c r="AP19" s="6" t="inlineStr"/>
+      <c r="AQ19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -4597,6 +4810,12 @@
         </is>
       </c>
       <c r="AP20" s="6" t="inlineStr"/>
+      <c r="AQ20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -4733,6 +4952,12 @@
         </is>
       </c>
       <c r="AP21" s="6" t="inlineStr"/>
+      <c r="AQ21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR21" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4745,7 +4970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:BD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4800,6 +5025,10 @@
     <col width="40" customWidth="1" min="50" max="50"/>
     <col width="12" customWidth="1" min="51" max="51"/>
     <col width="40" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="40" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="40" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5101,6 +5330,28 @@
           <t>25회차 메모</t>
         </is>
       </c>
+      <c r="BA4" s="3" t="inlineStr">
+        <is>
+          <t>26회차 결과
+2026-09-28 23:47</t>
+        </is>
+      </c>
+      <c r="BB4" s="3" t="inlineStr">
+        <is>
+          <t>26회차 메모</t>
+        </is>
+      </c>
+      <c r="BC4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 결과
+2026-09-28 23:48</t>
+        </is>
+      </c>
+      <c r="BD4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -5271,6 +5522,18 @@
         </is>
       </c>
       <c r="AZ5" s="6" t="inlineStr"/>
+      <c r="BA5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB5" s="6" t="inlineStr"/>
+      <c r="BC5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -5437,6 +5700,18 @@
         </is>
       </c>
       <c r="AZ6" s="6" t="inlineStr"/>
+      <c r="BA6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB6" s="6" t="inlineStr"/>
+      <c r="BC6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -5603,6 +5878,18 @@
         </is>
       </c>
       <c r="AZ7" s="6" t="inlineStr"/>
+      <c r="BA7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB7" s="6" t="inlineStr"/>
+      <c r="BC7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -5773,6 +6060,18 @@
         </is>
       </c>
       <c r="AZ8" s="6" t="inlineStr"/>
+      <c r="BA8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB8" s="6" t="inlineStr"/>
+      <c r="BC8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -5939,6 +6238,18 @@
         </is>
       </c>
       <c r="AZ9" s="6" t="inlineStr"/>
+      <c r="BA9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB9" s="6" t="inlineStr"/>
+      <c r="BC9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -6105,6 +6416,18 @@
         </is>
       </c>
       <c r="AZ10" s="6" t="inlineStr"/>
+      <c r="BA10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB10" s="6" t="inlineStr"/>
+      <c r="BC10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -6271,6 +6594,18 @@
         </is>
       </c>
       <c r="AZ11" s="6" t="inlineStr"/>
+      <c r="BA11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB11" s="6" t="inlineStr"/>
+      <c r="BC11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -6437,6 +6772,18 @@
         </is>
       </c>
       <c r="AZ12" s="6" t="inlineStr"/>
+      <c r="BA12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB12" s="6" t="inlineStr"/>
+      <c r="BC12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -6607,6 +6954,18 @@
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr"/>
+      <c r="BA13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB13" s="6" t="inlineStr"/>
+      <c r="BC13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -6781,6 +7140,18 @@
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr"/>
+      <c r="BA14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB14" s="6" t="inlineStr"/>
+      <c r="BC14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -6947,6 +7318,18 @@
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr"/>
+      <c r="BA15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB15" s="6" t="inlineStr"/>
+      <c r="BC15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -7113,6 +7496,18 @@
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr"/>
+      <c r="BA16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB16" s="6" t="inlineStr"/>
+      <c r="BC16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -7279,6 +7674,18 @@
         </is>
       </c>
       <c r="AZ17" s="6" t="inlineStr"/>
+      <c r="BA17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB17" s="6" t="inlineStr"/>
+      <c r="BC17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -7417,6 +7824,18 @@
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr"/>
+      <c r="BA18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB18" s="6" t="inlineStr"/>
+      <c r="BC18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -7533,6 +7952,18 @@
         </is>
       </c>
       <c r="AZ19" s="6" t="inlineStr"/>
+      <c r="BA19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB19" s="6" t="inlineStr"/>
+      <c r="BC19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -7649,6 +8080,18 @@
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr"/>
+      <c r="BA20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB20" s="6" t="inlineStr"/>
+      <c r="BC20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -7741,6 +8184,18 @@
         </is>
       </c>
       <c r="AZ21" s="6" t="inlineStr"/>
+      <c r="BA21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB21" s="6" t="inlineStr"/>
+      <c r="BC21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -7833,6 +8288,18 @@
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr"/>
+      <c r="BA22" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB22" s="6" t="inlineStr"/>
+      <c r="BC22" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -7911,6 +8378,18 @@
         </is>
       </c>
       <c r="AZ23" s="6" t="inlineStr"/>
+      <c r="BA23" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB23" s="6" t="inlineStr"/>
+      <c r="BC23" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -7989,6 +8468,18 @@
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr"/>
+      <c r="BA24" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB24" s="6" t="inlineStr"/>
+      <c r="BC24" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -8063,6 +8554,18 @@
         </is>
       </c>
       <c r="AZ25" s="6" t="inlineStr"/>
+      <c r="BA25" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB25" s="6" t="inlineStr"/>
+      <c r="BC25" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -8137,6 +8640,18 @@
         </is>
       </c>
       <c r="AZ26" s="6" t="inlineStr"/>
+      <c r="BA26" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB26" s="6" t="inlineStr"/>
+      <c r="BC26" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -8188,6 +8703,18 @@
         </is>
       </c>
       <c r="AZ27" s="6" t="inlineStr"/>
+      <c r="BA27" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB27" s="6" t="inlineStr"/>
+      <c r="BC27" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -8244,6 +8771,18 @@
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr"/>
+      <c r="BA28" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB28" s="6" t="inlineStr"/>
+      <c r="BC28" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -8288,6 +8827,18 @@
         </is>
       </c>
       <c r="AZ29" s="6" t="inlineStr"/>
+      <c r="BA29" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB29" s="6" t="inlineStr"/>
+      <c r="BC29" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -8332,6 +8883,62 @@
         </is>
       </c>
       <c r="AZ30" s="6" t="inlineStr"/>
+      <c r="BA30" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB30" s="6" t="inlineStr"/>
+      <c r="BC30" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>C2-27</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>보드 도우미(대화창)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>«💬 도우미» → 명함 PNG 붙여 넣기(Ctrl+V) → «이 명함 읽어 줘» → «유형은 공급기업이야» → «등록해 줘» → 기관·담당자 저장 → «과제 …?» → 닫기 → 정리</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>이미지 1장·기존 기관 목록 전달, 대화에 명함 카드, 대화로 유형 정정, «등록해 줘»로 미리 채운 기관 창(공급기업) → 담당자 창, 저장·연결, 명함 외 요청은 못 한다고 답함</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>저장은 사람이</t>
+        </is>
+      </c>
+      <c r="BA31" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BB31" s="6" t="inlineStr"/>
+      <c r="BC31" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BD31" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8344,2263 +8951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="40" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="40" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="40" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="40" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="40" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
-    <col width="40" customWidth="1" min="38" max="38"/>
-    <col width="12" customWidth="1" min="39" max="39"/>
-    <col width="40" customWidth="1" min="40" max="40"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>CASE3 — 골프 양말 · 봉조 자동화 편직기 (원공고)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 4쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>조작</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>기대 결과</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>자동화 방식</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>근거</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2회차 결과
-2026-09-28 07:56</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2회차 메모</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>3회차 결과
-2026-09-28 07:58</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>3회차 메모</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>4회차 결과
-2026-09-28 08:00</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>4회차 메모</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>5회차 결과
-2026-09-28 08:01</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>5회차 메모</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>6회차 결과
-2026-09-28 08:24</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>6회차 메모</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>7회차 결과
-2026-09-28 08:25</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>7회차 메모</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>10회차 결과
-2026-09-28 08:40</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>10회차 메모</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>11회차 결과
-2026-09-28 08:46</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>11회차 메모</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>13회차 결과
-2026-09-28 09:06</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>13회차 메모</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>14회차 결과
-2026-09-28 09:07</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>14회차 메모</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>15회차 결과
-2026-09-28 09:16</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>15회차 메모</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>17회차 결과
-2026-09-28 09:22</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>17회차 메모</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>18회차 결과
-2026-09-28 09:24</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>18회차 메모</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>21회차 결과
-2026-09-28 11:14</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>21회차 메모</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>22회차 결과
-2026-09-28 23:25</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>22회차 메모</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>23회차 결과
-2026-09-28 23:27</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>23회차 메모</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>25회차 결과
-2026-09-28 23:34</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>25회차 메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>C3-01</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>이사를 소공인 담당자로</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>기관 1곳에 대표·이사 등록, 과제 소공인 = 이사</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>상세 소공인 «[테스트] C3담당 이사»</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>실경영은 담당 이사</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr"/>
-      <c r="U5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V5" s="6" t="inlineStr"/>
-      <c r="W5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X5" s="6" t="inlineStr"/>
-      <c r="Y5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z5" s="6" t="inlineStr"/>
-      <c r="AA5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB5" s="6" t="inlineStr"/>
-      <c r="AC5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD5" s="6" t="inlineStr"/>
-      <c r="AE5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF5" s="6" t="inlineStr"/>
-      <c r="AG5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH5" s="6" t="inlineStr"/>
-      <c r="AI5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ5" s="6" t="inlineStr"/>
-      <c r="AK5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL5" s="6" t="inlineStr"/>
-      <c r="AM5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>C3-02</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>존칭</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>1단계 보내기 → 소공인 · 일정 조율</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>«[테스트] C3담당 이사님 안녕하세요.»(«이사 대표님» 아님)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr"/>
-      <c r="O6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T6" s="6" t="inlineStr"/>
-      <c r="U6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V6" s="6" t="inlineStr"/>
-      <c r="W6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X6" s="6" t="inlineStr"/>
-      <c r="Y6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z6" s="6" t="inlineStr"/>
-      <c r="AA6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB6" s="6" t="inlineStr"/>
-      <c r="AC6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD6" s="6" t="inlineStr"/>
-      <c r="AE6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF6" s="6" t="inlineStr"/>
-      <c r="AG6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH6" s="6" t="inlineStr"/>
-      <c r="AI6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ6" s="6" t="inlineStr"/>
-      <c r="AK6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL6" s="6" t="inlineStr"/>
-      <c r="AM6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>C3-03</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>마스터 반영</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>이사 전화 010-0000-3334로 수정</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>과제 스냅샷 전화 자동 반영</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr"/>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr"/>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr"/>
-      <c r="U7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V7" s="6" t="inlineStr"/>
-      <c r="W7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X7" s="6" t="inlineStr"/>
-      <c r="Y7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z7" s="6" t="inlineStr"/>
-      <c r="AA7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB7" s="6" t="inlineStr"/>
-      <c r="AC7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD7" s="6" t="inlineStr"/>
-      <c r="AE7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF7" s="6" t="inlineStr"/>
-      <c r="AG7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH7" s="6" t="inlineStr"/>
-      <c r="AI7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ7" s="6" t="inlineStr"/>
-      <c r="AK7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL7" s="6" t="inlineStr"/>
-      <c r="AM7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>C3-04</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>전화 검색</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>검색 «01000003334»</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>결과에 과제·담당자</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr"/>
-      <c r="O8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr"/>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T8" s="6" t="inlineStr"/>
-      <c r="U8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V8" s="6" t="inlineStr"/>
-      <c r="W8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X8" s="6" t="inlineStr"/>
-      <c r="Y8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z8" s="6" t="inlineStr"/>
-      <c r="AA8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB8" s="6" t="inlineStr"/>
-      <c r="AC8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD8" s="6" t="inlineStr"/>
-      <c r="AE8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF8" s="6" t="inlineStr"/>
-      <c r="AG8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH8" s="6" t="inlineStr"/>
-      <c r="AI8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ8" s="6" t="inlineStr"/>
-      <c r="AK8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL8" s="6" t="inlineStr"/>
-      <c r="AM8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>C3-05</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>검색 변형</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>«3334», «0000-3334», «0000 3334»</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>같은 결과</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr"/>
-      <c r="O9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr"/>
-      <c r="U9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V9" s="6" t="inlineStr"/>
-      <c r="W9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X9" s="6" t="inlineStr"/>
-      <c r="Y9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z9" s="6" t="inlineStr"/>
-      <c r="AA9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB9" s="6" t="inlineStr"/>
-      <c r="AC9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD9" s="6" t="inlineStr"/>
-      <c r="AE9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF9" s="6" t="inlineStr"/>
-      <c r="AG9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH9" s="6" t="inlineStr"/>
-      <c r="AI9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ9" s="6" t="inlineStr"/>
-      <c r="AK9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL9" s="6" t="inlineStr"/>
-      <c r="AM9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>C3-06</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>견적 오기</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>S/W 단가 «6,600,00» 입력 → 거부 확인 후 «6,000,000»으로 등록</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>«쉼표 자리가 맞지 않습니다» 오류로 저장 안 됨 → 6,000,000 저장</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>원문 합계 «6,600,00원»</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr"/>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr"/>
-      <c r="O10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T10" s="6" t="inlineStr"/>
-      <c r="U10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V10" s="6" t="inlineStr"/>
-      <c r="W10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X10" s="6" t="inlineStr"/>
-      <c r="Y10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z10" s="6" t="inlineStr"/>
-      <c r="AA10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB10" s="6" t="inlineStr"/>
-      <c r="AC10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD10" s="6" t="inlineStr"/>
-      <c r="AE10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF10" s="6" t="inlineStr"/>
-      <c r="AG10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH10" s="6" t="inlineStr"/>
-      <c r="AI10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ10" s="6" t="inlineStr"/>
-      <c r="AK10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL10" s="6" t="inlineStr"/>
-      <c r="AM10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>C3-07</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>편직기 2, S/W 1</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>«검토 중 · 2대»</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr"/>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T11" s="6" t="inlineStr"/>
-      <c r="U11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V11" s="6" t="inlineStr"/>
-      <c r="W11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X11" s="6" t="inlineStr"/>
-      <c r="Y11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z11" s="6" t="inlineStr"/>
-      <c r="AA11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB11" s="6" t="inlineStr"/>
-      <c r="AC11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD11" s="6" t="inlineStr"/>
-      <c r="AE11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF11" s="6" t="inlineStr"/>
-      <c r="AG11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH11" s="6" t="inlineStr"/>
-      <c r="AI11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL11" s="6" t="inlineStr"/>
-      <c r="AM11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>C3-08</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>납기 예정</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>6단계 예정일 T+30(입금 후 30일)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>카드 «다음 … 장비 공급 D-30»</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>납기 입금 후 30일 이내</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr"/>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr"/>
-      <c r="O12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr"/>
-      <c r="Q12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr"/>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T12" s="6" t="inlineStr"/>
-      <c r="U12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr"/>
-      <c r="W12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X12" s="6" t="inlineStr"/>
-      <c r="Y12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z12" s="6" t="inlineStr"/>
-      <c r="AA12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB12" s="6" t="inlineStr"/>
-      <c r="AC12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD12" s="6" t="inlineStr"/>
-      <c r="AE12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF12" s="6" t="inlineStr"/>
-      <c r="AG12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH12" s="6" t="inlineStr"/>
-      <c r="AI12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL12" s="6" t="inlineStr"/>
-      <c r="AM12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>C3-09</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>캘린더 등록</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>«일정» 탭 6단계 «등록»</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 1건, «등록됨», 활동 «캘린더 · 자동»</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr"/>
-      <c r="O13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr"/>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr"/>
-      <c r="U13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr"/>
-      <c r="W13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X13" s="6" t="inlineStr"/>
-      <c r="Y13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z13" s="6" t="inlineStr"/>
-      <c r="AA13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB13" s="6" t="inlineStr"/>
-      <c r="AC13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD13" s="6" t="inlineStr"/>
-      <c r="AE13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF13" s="6" t="inlineStr"/>
-      <c r="AG13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH13" s="6" t="inlineStr"/>
-      <c r="AI13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL13" s="6" t="inlineStr"/>
-      <c r="AM13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>C3-10</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 내용</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>목 이벤트 확인</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>제목 «[스마트제조] … · 6. 장비 공급», 종일, 시작 T+30·끝 T+31, Asia/Seoul</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>캘린더 앱 확인 대체</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr"/>
-      <c r="O14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr"/>
-      <c r="Q14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr"/>
-      <c r="U14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr"/>
-      <c r="W14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X14" s="6" t="inlineStr"/>
-      <c r="Y14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z14" s="6" t="inlineStr"/>
-      <c r="AA14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB14" s="6" t="inlineStr"/>
-      <c r="AC14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD14" s="6" t="inlineStr"/>
-      <c r="AE14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF14" s="6" t="inlineStr"/>
-      <c r="AG14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH14" s="6" t="inlineStr"/>
-      <c r="AI14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL14" s="6" t="inlineStr"/>
-      <c r="AM14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>C3-11</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>날짜 변경 감지</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>예정일 T+35 → «오늘» 캘린더 미등록</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>«날짜 변경 (캘린더 T+30)»</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr"/>
-      <c r="O15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr"/>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr"/>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr"/>
-      <c r="U15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr"/>
-      <c r="W15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X15" s="6" t="inlineStr"/>
-      <c r="Y15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z15" s="6" t="inlineStr"/>
-      <c r="AA15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB15" s="6" t="inlineStr"/>
-      <c r="AC15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD15" s="6" t="inlineStr"/>
-      <c r="AE15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF15" s="6" t="inlineStr"/>
-      <c r="AG15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH15" s="6" t="inlineStr"/>
-      <c r="AI15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL15" s="6" t="inlineStr"/>
-      <c r="AM15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>C3-12</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>날짜 수정</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>«일정» 탭 «날짜 수정»</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 T+35, 활동 제목 «날짜 변경 T+30 → T+35», 미등록 목록에서 사라짐</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr"/>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr"/>
-      <c r="O16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr"/>
-      <c r="U16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr"/>
-      <c r="W16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X16" s="6" t="inlineStr"/>
-      <c r="Y16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z16" s="6" t="inlineStr"/>
-      <c r="AA16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB16" s="6" t="inlineStr"/>
-      <c r="AC16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD16" s="6" t="inlineStr"/>
-      <c r="AE16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF16" s="6" t="inlineStr"/>
-      <c r="AG16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH16" s="6" t="inlineStr"/>
-      <c r="AI16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL16" s="6" t="inlineStr"/>
-      <c r="AM16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>C3-13</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>메모 → 초안</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>2단계 메모 후 수행일지 2차 초안</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>활동요약에 «· (MM-DD) 원문»</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr"/>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr"/>
-      <c r="O17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr"/>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T17" s="6" t="inlineStr"/>
-      <c r="U17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr"/>
-      <c r="W17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X17" s="6" t="inlineStr"/>
-      <c r="Y17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z17" s="6" t="inlineStr"/>
-      <c r="AA17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB17" s="6" t="inlineStr"/>
-      <c r="AC17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD17" s="6" t="inlineStr"/>
-      <c r="AE17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF17" s="6" t="inlineStr"/>
-      <c r="AG17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH17" s="6" t="inlineStr"/>
-      <c r="AI17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL17" s="6" t="inlineStr"/>
-      <c r="AM17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>C3-14</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>서명란</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>2차 초안 서명란 확인</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>«신청인(대표) : [테스트] C3담당» — 이사 이름(질문 3)</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr"/>
-      <c r="O18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr"/>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T18" s="6" t="inlineStr"/>
-      <c r="U18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr"/>
-      <c r="W18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X18" s="6" t="inlineStr"/>
-      <c r="Y18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z18" s="6" t="inlineStr"/>
-      <c r="AA18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB18" s="6" t="inlineStr"/>
-      <c r="AC18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD18" s="6" t="inlineStr"/>
-      <c r="AE18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF18" s="6" t="inlineStr"/>
-      <c r="AG18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH18" s="6" t="inlineStr"/>
-      <c r="AI18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL18" s="6" t="inlineStr"/>
-      <c r="AM18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>C3-15</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>정리</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>과제 삭제</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>«구글 캘린더에 등록된 일정 1건은 지워지지 않았습니다» 안내, 이후 장비·담당자·기관 삭제</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr"/>
-      <c r="O19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr"/>
-      <c r="Q19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr"/>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T19" s="6" t="inlineStr"/>
-      <c r="U19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr"/>
-      <c r="W19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X19" s="6" t="inlineStr"/>
-      <c r="Y19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z19" s="6" t="inlineStr"/>
-      <c r="AA19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB19" s="6" t="inlineStr"/>
-      <c r="AC19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD19" s="6" t="inlineStr"/>
-      <c r="AE19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF19" s="6" t="inlineStr"/>
-      <c r="AG19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH19" s="6" t="inlineStr"/>
-      <c r="AI19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL19" s="6" t="inlineStr"/>
-      <c r="AM19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN19" s="6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AP18"/>
+  <dimension ref="A1:AP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10650,14 +9001,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE4 — 지르코니아 치과 보철 · CNC 밀링 (추가공고)</t>
+          <t>CASE3 — 골프 양말 · 봉조 자동화 편직기 (원공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 5쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 4쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
         </is>
       </c>
     </row>
@@ -10761,156 +9112,156 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>8회차 결과
-2026-09-28 08:26</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>8회차 메모</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
           <t>10회차 결과
 2026-09-28 08:40</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>10회차 메모</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>11회차 결과
 2026-09-28 08:46</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>11회차 메모</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>13회차 결과
 2026-09-28 09:06</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>13회차 메모</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>14회차 결과
 2026-09-28 09:07</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>14회차 메모</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>15회차 결과
 2026-09-28 09:16</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>15회차 메모</t>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>17회차 결과
 2026-09-28 09:22</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>17회차 메모</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>18회차 결과
 2026-09-28 09:24</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>18회차 메모</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>21회차 결과
 2026-09-28 11:14</t>
         </is>
       </c>
-      <c r="AJ4" s="3" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>21회차 메모</t>
         </is>
       </c>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>22회차 결과
 2026-09-28 23:25</t>
         </is>
       </c>
-      <c r="AL4" s="3" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr">
         <is>
           <t>22회차 메모</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <t>23회차 결과
 2026-09-28 23:27</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>23회차 메모</t>
         </is>
       </c>
-      <c r="AO4" s="3" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>25회차 결과
 2026-09-28 23:34</t>
         </is>
       </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 메모</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 결과
+2026-09-28 23:48</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>25회차 메모</t>
+          <t>27회차 메모</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C4-01</t>
+          <t>C3-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>공고 미지정</t>
+          <t>이사를 소공인 담당자로</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>공고 구분 비우고 과제 생성</t>
+          <t>기관 1곳에 대표·이사 등록, 과제 소공인 = 이사</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>카드 «공고 미확인», 상세 경고 문구</t>
+          <t>상세 소공인 «[테스트] C3담당 이사»</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -10918,7 +9269,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>실경영은 담당 이사</t>
+        </is>
+      </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -11031,22 +9386,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C4-02</t>
+          <t>C3-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>미확인 필터</t>
+          <t>존칭</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>공고 필터 = 공고 미확인</t>
+          <t>1단계 보내기 → 소공인 · 일정 조율</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>이 과제 보임</t>
+          <t>«[테스트] C3담당 이사님 안녕하세요.»(«이사 대표님» 아님)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -11167,22 +9522,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C4-03</t>
+          <t>C3-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>추가공고 지정</t>
+          <t>마스터 반영</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>상세 공고 구분 = 추가공고</t>
+          <t>이사 전화 010-0000-3334로 수정</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>배지 «추가공고», 원공고 필터에서 숨김, CSV 공고 열 «추가공고»</t>
+          <t>과제 스냅샷 전화 자동 반영</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -11190,11 +9545,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>연매출 2억원 미만</t>
-        </is>
-      </c>
+      <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -11307,34 +9658,30 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C4-04</t>
+          <t>C3-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 화면</t>
+          <t>전화 검색</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>390×844 에뮬레이션</t>
+          <t>검색 «01000003334»</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>하단 탭바(더보기 보임, 기관 탭 숨김), 가로 넘침 없음, 범례 숨김</t>
+          <t>결과에 과제·담당자</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>실기기 대체</t>
-        </is>
-      </c>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -11447,27 +9794,27 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C4-05</t>
+          <t>C3-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 진단 입력</t>
+          <t>검색 변형</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>1차 진단 5칸 입력, 칸 이동은 탭 한 번</t>
+          <t>«3334», «0000-3334», «0000 3334»</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>입력칸 16px, 다음 칸으로 포커스 이동, 값 저장</t>
+          <t>같은 결과</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -11583,32 +9930,32 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C4-06</t>
+          <t>C3-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>입력 중 재그리기</t>
+          <t>견적 오기</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>입력 중 스냅샷 강제 발행</t>
+          <t>S/W 단가 «6,600,00» 입력 → 거부 확인 후 «6,000,000»으로 등록</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>입력 중인 글자 유지</t>
+          <t>«쉼표 자리가 맞지 않습니다» 오류로 저장 안 됨 → 6,000,000 저장</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>다른 기기 수정 대체</t>
+          <t>원문 합계 «6,600,00원»</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -11723,22 +10070,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C4-07</t>
+          <t>C3-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2차 진단 입력</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>②·③·기록 수준 입력</t>
+          <t>편직기 2, S/W 1</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>«검토 중 · 2대»</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -11859,22 +10206,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C4-08</t>
+          <t>C3-08</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1차 초안 반영</t>
+          <t>납기 예정</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>1단계 초안</t>
+          <t>6단계 예정일 T+30(입금 후 30일)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>입력 5칸 원문, ⑤⑥⑦ «미확인 — …»</t>
+          <t>카드 «다음 … 장비 공급 D-30»</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -11882,7 +10229,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>납기 입금 후 30일 이내</t>
+        </is>
+      </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -11995,27 +10346,27 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C4-09</t>
+          <t>C3-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2·3차 초안</t>
+          <t>캘린더 등록</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>2·7단계 초안</t>
+          <t>«일정» 탭 6단계 «등록»</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>2차 ③ 원문, 3차 향후 사후관리 «미확인 — …»</t>
+          <t>이벤트 1건, «등록됨», 활동 «캘린더 · 자동»</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
@@ -12131,32 +10482,32 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C4-10</t>
+          <t>C3-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>수치 비생성</t>
+          <t>이벤트 내용</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>초안 숫자 대조</t>
+          <t>목 이벤트 확인</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>6개·10개 외 수치(%, 증가율) 없음</t>
+          <t>제목 «[스마트제조] … · 6. 장비 공급», 종일, 시작 T+30·끝 T+31, Asia/Seoul</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>하루 6개 → 10개</t>
+          <t>캘린더 앱 확인 대체</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -12271,22 +10622,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C4-11</t>
+          <t>C3-11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>결과보고서 초안</t>
+          <t>날짜 변경 감지</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>8단계 초안</t>
+          <t>예정일 T+35 → «오늘» 캘린더 미등록</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>3. KPI에 1차 ②·④·2차 ② 진단 줄, 5.에 기록 방식 줄, 초안 표시</t>
+          <t>«날짜 변경 (캘린더 T+30)»</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -12407,27 +10758,27 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C4-12</t>
+          <t>C3-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>장비·자산 → 초안</t>
+          <t>날짜 수정</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>덴탈 CNC밀링기·Dentalsoft 등록, 자산 각 1 → 3차·결과보고서 초안</t>
+          <t>«일정» 탭 «날짜 수정»</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>3차 «④ 도입 장비»·결과보고서 4에 «[H/W] 덴탈 CNC밀링기 마닉스 5SA × 1대 (검토 중)»·«[S/W] Dentalsoft × 1식 (검토 중)», 금액 없음</t>
+          <t>이벤트 T+35, 활동 제목 «날짜 변경 T+30 → T+35», 미등록 목록에서 사라짐</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
@@ -12543,27 +10894,27 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>C4-13</t>
+          <t>C3-13</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 더보기</t>
+          <t>메모 → 초안</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>더보기 → 자산</t>
+          <t>2단계 메모 후 수행일지 2차 초안</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>메뉴 열림, 버튼 라벨 «자산 ▴», 자산 목록</t>
+          <t>활동요약에 «· (MM-DD) 원문»</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
@@ -12679,22 +11030,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>C4-14</t>
+          <t>C3-14</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>정리</t>
+          <t>서명란</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>과제·장비·담당자·기관 삭제</t>
+          <t>2차 초안 서명란 확인</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>삭제 완료</t>
+          <t>«신청인(대표) : [테스트] C3담당» — 이사 이름(질문 3)</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -12811,19 +11162,155 @@
         </is>
       </c>
       <c r="AP18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>C3-15</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>정리</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>«구글 캘린더에 등록된 일정 1건은 지워지지 않았습니다» 안내, 이후 장비·담당자·기관 삭제</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr"/>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr"/>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr"/>
+      <c r="U19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr"/>
+      <c r="W19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X19" s="6" t="inlineStr"/>
+      <c r="Y19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z19" s="6" t="inlineStr"/>
+      <c r="AA19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB19" s="6" t="inlineStr"/>
+      <c r="AC19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD19" s="6" t="inlineStr"/>
+      <c r="AE19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF19" s="6" t="inlineStr"/>
+      <c r="AG19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr"/>
+      <c r="AI19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ19" s="6" t="inlineStr"/>
+      <c r="AK19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL19" s="6" t="inlineStr"/>
+      <c r="AM19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN19" s="6" t="inlineStr"/>
+      <c r="AO19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP19" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AR18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12866,19 +11353,23 @@
     <col width="40" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="40" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="40" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE5 — 친환경 벽지 · 라텍스 프린터 + 자동견적 (추가공고)</t>
+          <t>CASE4 — 지르코니아 치과 보철 · CNC 밀링 (추가공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 6쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 5쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
         </is>
       </c>
     </row>
@@ -12982,145 +11473,167 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
+          <t>8회차 결과
+2026-09-28 08:26</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>8회차 메모</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
           <t>10회차 결과
 2026-09-28 08:40</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>10회차 메모</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>11회차 결과
 2026-09-28 08:46</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>11회차 메모</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>13회차 결과
 2026-09-28 09:06</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>13회차 메모</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>14회차 결과
 2026-09-28 09:07</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>14회차 메모</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>15회차 결과
 2026-09-28 09:16</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>15회차 메모</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>17회차 결과
 2026-09-28 09:22</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>17회차 메모</t>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>18회차 결과
 2026-09-28 09:24</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>18회차 메모</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>21회차 결과
 2026-09-28 11:14</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr">
         <is>
           <t>21회차 메모</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <t>22회차 결과
 2026-09-28 23:25</t>
         </is>
       </c>
-      <c r="AJ4" s="3" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>22회차 메모</t>
         </is>
       </c>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>23회차 결과
 2026-09-28 23:27</t>
         </is>
       </c>
-      <c r="AL4" s="3" t="inlineStr">
+      <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>23회차 메모</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>25회차 결과
 2026-09-28 23:34</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr">
         <is>
           <t>25회차 메모</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 결과
+2026-09-28 23:48</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 메모</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C5-01</t>
+          <t>C4-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>지연·다음 예정</t>
+          <t>공고 미지정</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>추가공고 과제, 1단계 T-3, 2단계 T+4</t>
+          <t>공고 구분 비우고 과제 생성</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>카드 «다음 … 1차 방문 D+3», «지연 1»</t>
+          <t>카드 «공고 미확인», 상세 경고 문구</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -13231,26 +11744,38 @@
         </is>
       </c>
       <c r="AN5" s="6" t="inlineStr"/>
+      <c r="AO5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP5" s="6" t="inlineStr"/>
+      <c r="AQ5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C5-02</t>
+          <t>C4-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>오늘 탭</t>
+          <t>미확인 필터</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>«오늘» 탭</t>
+          <t>공고 필터 = 공고 미확인</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>기한 경과에 1단계, 7일 안의 방문에 2단계</t>
+          <t>이 과제 보임</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -13361,26 +11886,38 @@
         </is>
       </c>
       <c r="AN6" s="6" t="inlineStr"/>
+      <c r="AO6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP6" s="6" t="inlineStr"/>
+      <c r="AQ6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C5-03</t>
+          <t>C4-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>완료 누락 알림</t>
+          <t>추가공고 지정</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>1단계 산출물 미체크로 완료</t>
+          <t>상세 공고 구분 = 추가공고</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>알림에 «현장진단표, 1차 방문 확인 서명», 상태 «완료» 유지</t>
+          <t>배지 «추가공고», 원공고 필터에서 숨김, CSV 공고 열 «추가공고»</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -13388,7 +11925,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>연매출 2억원 미만</t>
+        </is>
+      </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -13491,34 +12032,50 @@
         </is>
       </c>
       <c r="AN7" s="6" t="inlineStr"/>
+      <c r="AO7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP7" s="6" t="inlineStr"/>
+      <c r="AQ7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C5-04</t>
+          <t>C4-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>알림 줄어듦</t>
+          <t>휴대폰 화면</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>현장진단표 체크 → 나머지 체크</t>
+          <t>390×844 에뮬레이션</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>알림 1개로 줄고, 다 체크하면 사라짐</t>
+          <t>하단 탭바(더보기 보임, 기관 탭 숨김), 가로 넘침 없음, 범례 숨김</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>실기기 대체</t>
+        </is>
+      </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -13621,31 +12178,43 @@
         </is>
       </c>
       <c r="AN8" s="6" t="inlineStr"/>
+      <c r="AO8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP8" s="6" t="inlineStr"/>
+      <c r="AQ8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C5-05</t>
+          <t>C4-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>서류 미수집</t>
+          <t>휴대폰 진단 입력</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>체크 1개 해제 → «오늘»</t>
+          <t>1차 진단 5칸 입력, 칸 이동은 탭 한 번</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>서명·서류 미수집에 1단계</t>
+          <t>입력칸 16px, 다음 칸으로 포커스 이동, 값 저장</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -13751,34 +12320,50 @@
         </is>
       </c>
       <c r="AN9" s="6" t="inlineStr"/>
+      <c r="AO9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP9" s="6" t="inlineStr"/>
+      <c r="AQ9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C5-06</t>
+          <t>C4-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>카톡 수동 기록</t>
+          <t>입력 중 재그리기</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>수행일지 송부 → 카톡 보냄 기록</t>
+          <t>입력 중 스냅샷 강제 발행</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>«카톡으로 보냄을 … 기록했습니다(수동 기록)», 버튼 «기록됨» 비활성</t>
+          <t>입력 중인 글자 유지</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr"/>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>다른 기기 수정 대체</t>
+        </is>
+      </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -13881,26 +12466,38 @@
         </is>
       </c>
       <c r="AN10" s="6" t="inlineStr"/>
+      <c r="AO10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP10" s="6" t="inlineStr"/>
+      <c r="AQ10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C5-07</t>
+          <t>C4-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>기록자</t>
+          <t>2차 진단 입력</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>«활동» 탭</t>
+          <t>②·③·기록 수준 입력</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>«카톡 · 수동», 기록자 «시험자»</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -14011,26 +12608,38 @@
         </is>
       </c>
       <c r="AN11" s="6" t="inlineStr"/>
+      <c r="AO11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP11" s="6" t="inlineStr"/>
+      <c r="AQ11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C5-08</t>
+          <t>C4-08</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>메모 작성자</t>
+          <t>1차 초안 반영</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>1단계 메모</t>
+          <t>1단계 초안</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>머리 «… · 시험자», 한국 시간</t>
+          <t>입력 5칸 원문, ⑤⑥⑦ «미확인 — …»</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -14038,11 +12647,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>KPI 설정 필요</t>
-        </is>
-      </c>
+      <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -14145,26 +12750,38 @@
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr"/>
+      <c r="AO12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP12" s="6" t="inlineStr"/>
+      <c r="AQ12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C5-09</t>
+          <t>C4-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>포함 품목</t>
+          <t>2·3차 초안</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>LATEX 730 / CNYX RIP(단가 비움) / QT-AI LITE 5,286,000</t>
+          <t>2·7단계 초안</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>RIP 단가 «—»</t>
+          <t>2차 ③ 원문, 3차 향후 사후관리 «미확인 — …»</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -14172,11 +12789,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>RIP «포함», S/W 할인 −714,000</t>
-        </is>
-      </c>
+      <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -14279,26 +12892,38 @@
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr"/>
+      <c r="AO13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP13" s="6" t="inlineStr"/>
+      <c r="AQ13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C5-10</t>
+          <t>C4-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>자산</t>
+          <t>수치 비생성</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>3건 등록 → 과제 상세 견적 합계</t>
+          <t>초안 숫자 대조</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>H/W 37,000,000원, «단가 없는 장비 1건 제외(CNYX RIP)», 경고 «1,174,889원 초과»</t>
+          <t>6개·10개 외 수치(%, 증가율) 없음</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -14306,7 +12931,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>하루 6개 → 10개</t>
+        </is>
+      </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -14409,26 +13038,38 @@
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr"/>
+      <c r="AO14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP14" s="6" t="inlineStr"/>
+      <c r="AQ14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C5-11</t>
+          <t>C4-11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>전체 백업</t>
+          <t>결과보고서 초안</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>«전체 백업 (JSON)»</t>
+          <t>8단계 초안</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>파일명·counts·notice «extra»·by id 포함, 이름 «시험자» 미포함</t>
+          <t>3. KPI에 1차 ②·④·2차 ② 진단 줄, 5.에 기록 방식 줄, 초안 표시</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -14539,26 +13180,38 @@
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr"/>
+      <c r="AO15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP15" s="6" t="inlineStr"/>
+      <c r="AQ15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C5-12</t>
+          <t>C4-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>정리</t>
+          <t>장비·자산 → 초안</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>과제·CASE5 장비 삭제(QT-AI 공급사 유지)</t>
+          <t>덴탈 CNC밀링기·Dentalsoft 등록, 자산 각 1 → 3차·결과보고서 초안</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>삭제 완료</t>
+          <t>3차 «④ 도입 장비»·결과보고서 4에 «[H/W] 덴탈 CNC밀링기 마닉스 5SA × 1대 (검토 중)»·«[S/W] Dentalsoft × 1식 (검토 중)», 금액 없음</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -14669,19 +13322,315 @@
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr"/>
+      <c r="AO16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP16" s="6" t="inlineStr"/>
+      <c r="AQ16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>C4-13</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>휴대폰 더보기</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>더보기 → 자산</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>메뉴 열림, 버튼 라벨 «자산 ▴», 자산 목록</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr"/>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr"/>
+      <c r="U17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr"/>
+      <c r="W17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X17" s="6" t="inlineStr"/>
+      <c r="Y17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z17" s="6" t="inlineStr"/>
+      <c r="AA17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB17" s="6" t="inlineStr"/>
+      <c r="AC17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD17" s="6" t="inlineStr"/>
+      <c r="AE17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF17" s="6" t="inlineStr"/>
+      <c r="AG17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr"/>
+      <c r="AI17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ17" s="6" t="inlineStr"/>
+      <c r="AK17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL17" s="6" t="inlineStr"/>
+      <c r="AM17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN17" s="6" t="inlineStr"/>
+      <c r="AO17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP17" s="6" t="inlineStr"/>
+      <c r="AQ17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>C4-14</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>정리</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>과제·장비·담당자·기관 삭제</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>삭제 완료</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr"/>
+      <c r="U18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr"/>
+      <c r="W18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X18" s="6" t="inlineStr"/>
+      <c r="Y18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z18" s="6" t="inlineStr"/>
+      <c r="AA18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB18" s="6" t="inlineStr"/>
+      <c r="AC18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD18" s="6" t="inlineStr"/>
+      <c r="AE18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF18" s="6" t="inlineStr"/>
+      <c r="AG18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH18" s="6" t="inlineStr"/>
+      <c r="AI18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ18" s="6" t="inlineStr"/>
+      <c r="AK18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL18" s="6" t="inlineStr"/>
+      <c r="AM18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN18" s="6" t="inlineStr"/>
+      <c r="AO18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP18" s="6" t="inlineStr"/>
+      <c r="AQ18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR18" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN17"/>
+  <dimension ref="A1:AP16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14724,19 +13673,21 @@
     <col width="40" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="40" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="40" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE6 — 디자인·출력 · 솔벤 플로터·재단기 (원공고)</t>
+          <t>CASE5 — 친환경 벽지 · 라텍스 프린터 + 자동견적 (추가공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 7쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 6쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
         </is>
       </c>
     </row>
@@ -14959,26 +13910,37 @@
           <t>25회차 메모</t>
         </is>
       </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 결과
+2026-09-28 23:48</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C6-01</t>
+          <t>C5-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>과제 생성</t>
+          <t>지연·다음 예정</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>과제(원공고), H/W 공급사 기관</t>
+          <t>추가공고 과제, 1단계 T-3, 2단계 T+4</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>카드 «다음 … 1차 방문 D+3», «지연 1»</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -14986,11 +13948,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>연매출 2억원 이상</t>
-        </is>
-      </c>
+      <c r="F5" s="6" t="inlineStr"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -15093,26 +14051,32 @@
         </is>
       </c>
       <c r="AN5" s="6" t="inlineStr"/>
+      <c r="AO5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C6-02</t>
+          <t>C5-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>오늘 탭</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>VG3-640 / RET-2002 / QT-AI BASIC(QT-AI 공급사, LITE 표기 메모)</t>
+          <t>«오늘» 탭</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>기한 경과에 1단계, 7일 안의 방문에 2단계</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -15120,11 +14084,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>품명 BASIC·사양 LITE형 불일치</t>
-        </is>
-      </c>
+      <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -15227,26 +14187,32 @@
         </is>
       </c>
       <c r="AN6" s="6" t="inlineStr"/>
+      <c r="AO6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C6-03</t>
+          <t>C5-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>공급사 장비</t>
+          <t>완료 누락 알림</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>QT-AI 공급사 기관 상세</t>
+          <t>1단계 산출물 미체크로 완료</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>«공급 장비»에 QT-AI 자동견적(BASIC)</t>
+          <t>알림에 «현장진단표, 1차 방문 확인 서명», 상태 «완료» 유지</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -15357,26 +14323,32 @@
         </is>
       </c>
       <c r="AN7" s="6" t="inlineStr"/>
+      <c r="AO7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C6-04</t>
+          <t>C5-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>자산</t>
+          <t>알림 줄어듦</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>3건</t>
+          <t>현장진단표 체크 → 나머지 체크</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>알림 1개로 줄고, 다 체크하면 사라짐</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -15487,26 +14459,32 @@
         </is>
       </c>
       <c r="AN8" s="6" t="inlineStr"/>
+      <c r="AO8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C6-05</t>
+          <t>C5-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>장비 필터</t>
+          <t>서류 미수집</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>장비 탭 S/W 칩 + 검색 «QT-AI»</t>
+          <t>체크 1개 해제 → «오늘»</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>QT-AI BASIC만</t>
+          <t>서명·서류 미수집에 1단계</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -15617,26 +14595,32 @@
         </is>
       </c>
       <c r="AN9" s="6" t="inlineStr"/>
+      <c r="AO9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C6-06</t>
+          <t>C5-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>통합 검색</t>
+          <t>카톡 수동 기록</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>상단 검색 «VG3» → 결과 클릭</t>
+          <t>수행일지 송부 → 카톡 보냄 기록</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>장비 상세, 도입된 자산에 과제</t>
+          <t>«카톡으로 보냄을 … 기록했습니다(수동 기록)», 버튼 «기록됨» 비활성</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -15747,26 +14731,32 @@
         </is>
       </c>
       <c r="AN10" s="6" t="inlineStr"/>
+      <c r="AO10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C6-07</t>
+          <t>C5-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>S/W 한도</t>
+          <t>기록자</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>42,383,000÷9=4,709,222 &lt; 6,000,000 → 과제 상세 확인 + 메모</t>
+          <t>«활동» 탭</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>H/W 42,383,000원, 경고 «1,290,778원 초과»</t>
+          <t>«카톡 · 수동», 기록자 «시험자»</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -15877,26 +14867,32 @@
         </is>
       </c>
       <c r="AN11" s="6" t="inlineStr"/>
+      <c r="AO11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C6-08</t>
+          <t>C5-08</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>장비 삭제 거부</t>
+          <t>메모 작성자</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>VG3-640 삭제</t>
+          <t>1단계 메모</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>«자산 1건에 쓰이고 있어 삭제할 수 없습니다»</t>
+          <t>머리 «… · 시험자», 한국 시간</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -15904,7 +14900,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>KPI 설정 필요</t>
+        </is>
+      </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -16007,26 +15007,32 @@
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr"/>
+      <c r="AO12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C6-09</t>
+          <t>C5-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>과제 삭제 안전장치</t>
+          <t>포함 품목</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>과제 «삭제» 1회 후 4초</t>
+          <t>LATEX 730 / CNYX RIP(단가 비움) / QT-AI LITE 5,286,000</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>«삭제 확인» → «삭제»로 복귀</t>
+          <t>RIP 단가 «—»</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -16034,7 +15040,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>RIP «포함», S/W 할인 −714,000</t>
+        </is>
+      </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -16137,26 +15147,32 @@
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr"/>
+      <c r="AO13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C6-10</t>
+          <t>C5-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>과제 삭제</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>«삭제» 두 번</t>
+          <t>3건 등록 → 과제 상세 견적 합계</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>과제 삭제, 자산 동반 삭제(0건), 장비 3종 남음</t>
+          <t>H/W 37,000,000원, «단가 없는 장비 1건 제외(CNYX RIP)», 경고 «1,174,889원 초과»</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -16267,26 +15283,32 @@
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr"/>
+      <c r="AO14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C6-11</t>
+          <t>C5-11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>장비 삭제</t>
+          <t>전체 백업</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>VG3-640 삭제</t>
+          <t>«전체 백업 (JSON)»</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>삭제됨</t>
+          <t>파일명·counts·notice «extra»·by id 포함, 이름 «시험자» 미포함</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -16397,26 +15419,32 @@
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr"/>
+      <c r="AO15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C6-12</t>
+          <t>C5-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>기관 삭제 거부</t>
+          <t>정리</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>담당자 있는 기관 삭제</t>
+          <t>과제·CASE5 장비 삭제(QT-AI 공급사 유지)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>«소속 담당자 n명이 있어 삭제할 수 없습니다»</t>
+          <t>삭제 완료</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -16527,6 +15555,1955 @@
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr"/>
+      <c r="AO16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP16" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AP17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="40" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="40" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="40" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="40" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="40" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="40" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="40" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="40" customWidth="1" min="42" max="42"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>CASE6 — 디자인·출력 · 솔벤 플로터·재단기 (원공고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 7쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>조작</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>기대 결과</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>자동화 방식</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2회차 결과
+2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2회차 메모</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>3회차 결과
+2026-09-28 07:58</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>3회차 메모</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>4회차 결과
+2026-09-28 08:00</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>4회차 메모</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>5회차 결과
+2026-09-28 08:01</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>5회차 메모</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>6회차 결과
+2026-09-28 08:24</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>6회차 메모</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>7회차 결과
+2026-09-28 08:25</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>7회차 메모</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>10회차 결과
+2026-09-28 08:40</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>10회차 메모</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>11회차 결과
+2026-09-28 08:46</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>11회차 메모</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>13회차 결과
+2026-09-28 09:06</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>13회차 메모</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>14회차 결과
+2026-09-28 09:07</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>14회차 메모</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>15회차 결과
+2026-09-28 09:16</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>15회차 메모</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>17회차 결과
+2026-09-28 09:22</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>17회차 메모</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>18회차 결과
+2026-09-28 09:24</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>18회차 메모</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>21회차 결과
+2026-09-28 11:14</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>21회차 메모</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>22회차 결과
+2026-09-28 23:25</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>22회차 메모</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>23회차 결과
+2026-09-28 23:27</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>23회차 메모</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 결과
+2026-09-28 23:34</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 메모</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 결과
+2026-09-28 23:48</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>C6-01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>과제 생성</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>과제(원공고), H/W 공급사 기관</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>연매출 2억원 이상</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr"/>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr"/>
+      <c r="U5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr"/>
+      <c r="W5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="inlineStr"/>
+      <c r="Y5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z5" s="6" t="inlineStr"/>
+      <c r="AA5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB5" s="6" t="inlineStr"/>
+      <c r="AC5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD5" s="6" t="inlineStr"/>
+      <c r="AE5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF5" s="6" t="inlineStr"/>
+      <c r="AG5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH5" s="6" t="inlineStr"/>
+      <c r="AI5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ5" s="6" t="inlineStr"/>
+      <c r="AK5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL5" s="6" t="inlineStr"/>
+      <c r="AM5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN5" s="6" t="inlineStr"/>
+      <c r="AO5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>C6-02</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>VG3-640 / RET-2002 / QT-AI BASIC(QT-AI 공급사, LITE 표기 메모)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>품명 BASIC·사양 LITE형 불일치</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr"/>
+      <c r="U6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr"/>
+      <c r="W6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X6" s="6" t="inlineStr"/>
+      <c r="Y6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="inlineStr"/>
+      <c r="AA6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB6" s="6" t="inlineStr"/>
+      <c r="AC6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD6" s="6" t="inlineStr"/>
+      <c r="AE6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF6" s="6" t="inlineStr"/>
+      <c r="AG6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH6" s="6" t="inlineStr"/>
+      <c r="AI6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ6" s="6" t="inlineStr"/>
+      <c r="AK6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL6" s="6" t="inlineStr"/>
+      <c r="AM6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN6" s="6" t="inlineStr"/>
+      <c r="AO6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>C6-03</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>공급사 장비</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>QT-AI 공급사 기관 상세</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>«공급 장비»에 QT-AI 자동견적(BASIC)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr"/>
+      <c r="U7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr"/>
+      <c r="Y7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="inlineStr"/>
+      <c r="AA7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB7" s="6" t="inlineStr"/>
+      <c r="AC7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD7" s="6" t="inlineStr"/>
+      <c r="AE7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF7" s="6" t="inlineStr"/>
+      <c r="AG7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH7" s="6" t="inlineStr"/>
+      <c r="AI7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ7" s="6" t="inlineStr"/>
+      <c r="AK7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL7" s="6" t="inlineStr"/>
+      <c r="AM7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN7" s="6" t="inlineStr"/>
+      <c r="AO7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>C6-04</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>3건</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X8" s="6" t="inlineStr"/>
+      <c r="Y8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z8" s="6" t="inlineStr"/>
+      <c r="AA8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB8" s="6" t="inlineStr"/>
+      <c r="AC8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD8" s="6" t="inlineStr"/>
+      <c r="AE8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF8" s="6" t="inlineStr"/>
+      <c r="AG8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH8" s="6" t="inlineStr"/>
+      <c r="AI8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ8" s="6" t="inlineStr"/>
+      <c r="AK8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL8" s="6" t="inlineStr"/>
+      <c r="AM8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN8" s="6" t="inlineStr"/>
+      <c r="AO8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>C6-05</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>장비 필터</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>장비 탭 S/W 칩 + 검색 «QT-AI»</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>QT-AI BASIC만</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X9" s="6" t="inlineStr"/>
+      <c r="Y9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z9" s="6" t="inlineStr"/>
+      <c r="AA9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB9" s="6" t="inlineStr"/>
+      <c r="AC9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD9" s="6" t="inlineStr"/>
+      <c r="AE9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF9" s="6" t="inlineStr"/>
+      <c r="AG9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH9" s="6" t="inlineStr"/>
+      <c r="AI9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ9" s="6" t="inlineStr"/>
+      <c r="AK9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL9" s="6" t="inlineStr"/>
+      <c r="AM9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN9" s="6" t="inlineStr"/>
+      <c r="AO9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>C6-06</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>통합 검색</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>상단 검색 «VG3» → 결과 클릭</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>장비 상세, 도입된 자산에 과제</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr"/>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr"/>
+      <c r="U10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X10" s="6" t="inlineStr"/>
+      <c r="Y10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z10" s="6" t="inlineStr"/>
+      <c r="AA10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB10" s="6" t="inlineStr"/>
+      <c r="AC10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD10" s="6" t="inlineStr"/>
+      <c r="AE10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF10" s="6" t="inlineStr"/>
+      <c r="AG10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH10" s="6" t="inlineStr"/>
+      <c r="AI10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ10" s="6" t="inlineStr"/>
+      <c r="AK10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL10" s="6" t="inlineStr"/>
+      <c r="AM10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN10" s="6" t="inlineStr"/>
+      <c r="AO10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>C6-07</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>S/W 한도</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>42,383,000÷9=4,709,222 &lt; 6,000,000 → 과제 상세 확인 + 메모</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>H/W 42,383,000원, 경고 «1,290,778원 초과»</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr"/>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr"/>
+      <c r="U11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X11" s="6" t="inlineStr"/>
+      <c r="Y11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z11" s="6" t="inlineStr"/>
+      <c r="AA11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB11" s="6" t="inlineStr"/>
+      <c r="AC11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD11" s="6" t="inlineStr"/>
+      <c r="AE11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF11" s="6" t="inlineStr"/>
+      <c r="AG11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr"/>
+      <c r="AI11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ11" s="6" t="inlineStr"/>
+      <c r="AK11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL11" s="6" t="inlineStr"/>
+      <c r="AM11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN11" s="6" t="inlineStr"/>
+      <c r="AO11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>C6-08</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>장비 삭제 거부</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>VG3-640 삭제</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>«자산 1건에 쓰이고 있어 삭제할 수 없습니다»</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr"/>
+      <c r="O12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr"/>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr"/>
+      <c r="U12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V12" s="6" t="inlineStr"/>
+      <c r="W12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X12" s="6" t="inlineStr"/>
+      <c r="Y12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z12" s="6" t="inlineStr"/>
+      <c r="AA12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB12" s="6" t="inlineStr"/>
+      <c r="AC12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD12" s="6" t="inlineStr"/>
+      <c r="AE12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF12" s="6" t="inlineStr"/>
+      <c r="AG12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr"/>
+      <c r="AI12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ12" s="6" t="inlineStr"/>
+      <c r="AK12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL12" s="6" t="inlineStr"/>
+      <c r="AM12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN12" s="6" t="inlineStr"/>
+      <c r="AO12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>C6-09</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제 안전장치</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>과제 «삭제» 1회 후 4초</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>«삭제 확인» → «삭제»로 복귀</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr"/>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr"/>
+      <c r="U13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr"/>
+      <c r="W13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr"/>
+      <c r="Y13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z13" s="6" t="inlineStr"/>
+      <c r="AA13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB13" s="6" t="inlineStr"/>
+      <c r="AC13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD13" s="6" t="inlineStr"/>
+      <c r="AE13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF13" s="6" t="inlineStr"/>
+      <c r="AG13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr"/>
+      <c r="AI13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ13" s="6" t="inlineStr"/>
+      <c r="AK13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL13" s="6" t="inlineStr"/>
+      <c r="AM13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN13" s="6" t="inlineStr"/>
+      <c r="AO13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>C6-10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>«삭제» 두 번</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제, 자산 동반 삭제(0건), 장비 3종 남음</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr"/>
+      <c r="U14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr"/>
+      <c r="W14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X14" s="6" t="inlineStr"/>
+      <c r="Y14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z14" s="6" t="inlineStr"/>
+      <c r="AA14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB14" s="6" t="inlineStr"/>
+      <c r="AC14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD14" s="6" t="inlineStr"/>
+      <c r="AE14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF14" s="6" t="inlineStr"/>
+      <c r="AG14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr"/>
+      <c r="AI14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ14" s="6" t="inlineStr"/>
+      <c r="AK14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL14" s="6" t="inlineStr"/>
+      <c r="AM14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN14" s="6" t="inlineStr"/>
+      <c r="AO14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>C6-11</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>장비 삭제</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>VG3-640 삭제</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>삭제됨</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr"/>
+      <c r="U15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr"/>
+      <c r="W15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr"/>
+      <c r="Y15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z15" s="6" t="inlineStr"/>
+      <c r="AA15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB15" s="6" t="inlineStr"/>
+      <c r="AC15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD15" s="6" t="inlineStr"/>
+      <c r="AE15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF15" s="6" t="inlineStr"/>
+      <c r="AG15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr"/>
+      <c r="AI15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ15" s="6" t="inlineStr"/>
+      <c r="AK15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL15" s="6" t="inlineStr"/>
+      <c r="AM15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN15" s="6" t="inlineStr"/>
+      <c r="AO15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>C6-12</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>기관 삭제 거부</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>담당자 있는 기관 삭제</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>«소속 담당자 n명이 있어 삭제할 수 없습니다»</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr"/>
+      <c r="U16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr"/>
+      <c r="W16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr"/>
+      <c r="Y16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z16" s="6" t="inlineStr"/>
+      <c r="AA16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB16" s="6" t="inlineStr"/>
+      <c r="AC16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD16" s="6" t="inlineStr"/>
+      <c r="AE16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF16" s="6" t="inlineStr"/>
+      <c r="AG16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH16" s="6" t="inlineStr"/>
+      <c r="AI16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ16" s="6" t="inlineStr"/>
+      <c r="AK16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL16" s="6" t="inlineStr"/>
+      <c r="AM16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN16" s="6" t="inlineStr"/>
+      <c r="AO16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -16657,6 +17634,12 @@
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr"/>
+      <c r="AO17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP17" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/doc/테스트/E2E_시나리오_CASE1-6.xlsx
+++ b/doc/테스트/E2E_시나리오_CASE1-6.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -610,16 +610,16 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:48</t>
+          <t>2026-09-28 23:56</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>084be90acd</t>
+          <t>c9a72f41a0</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>27/0/0</t>
+          <t>28/0/0</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="J5" s="10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0</v>
@@ -665,11 +665,11 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:47</t>
+          <t>2026-09-28 23:48</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -689,26 +689,26 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J6" s="10" t="n">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0</v>
@@ -720,50 +720,50 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:34</t>
+          <t>2026-09-28 23:47</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>09cbe67b2a</t>
+          <t>084be90acd</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>26/0/0</t>
+          <t>27/0/0</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J7" s="10" t="n">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0</v>
@@ -775,11 +775,11 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:33</t>
+          <t>2026-09-28 23:34</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -799,26 +799,26 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0</v>
@@ -830,50 +830,50 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:27</t>
+          <t>2026-09-28 23:33</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>0145ba81dd</t>
+          <t>09cbe67b2a</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>24/0/0</t>
+          <t>26/0/0</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="10" t="n">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
@@ -885,11 +885,11 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:25</t>
+          <t>2026-09-28 23:27</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -940,16 +940,16 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:14</t>
+          <t>2026-09-28 23:25</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>6c4132ffc2</t>
+          <t>0145ba81dd</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>22/0/0</t>
+          <t>24/0/0</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="J11" s="10" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
@@ -995,21 +995,21 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:13</t>
+          <t>2026-09-28 11:14</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>6d745d5356</t>
+          <t>6c4132ffc2</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1019,26 +1019,26 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
@@ -1050,16 +1050,16 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:11</t>
+          <t>2026-09-28 11:13</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>b65bfe6fe8</t>
+          <t>6d745d5356</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>20/2/0</t>
+          <t>22/0/0</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -1092,88 +1092,88 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J13" s="11" t="n">
-        <v>20</v>
+      <c r="J13" s="10" t="n">
+        <v>22</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>C2-19, C2-20</t>
-        </is>
-      </c>
+      <c r="M13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:24</t>
+          <t>2026-09-28 11:11</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>0ae6ece6c2</t>
+          <t>b65bfe6fe8</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>18/0/0</t>
+          <t>20/2/0</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>89</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>20</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="6" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>C2-19, C2-20</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:22</t>
+          <t>2026-09-28 09:24</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>f40fc41604</t>
+          <t>0ae6ece6c2</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1219,11 +1219,11 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:21</t>
+          <t>2026-09-28 09:22</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1243,26 +1243,26 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J16" s="10" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
@@ -1274,50 +1274,50 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:16</t>
+          <t>2026-09-28 09:21</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>51a52339ab</t>
+          <t>f40fc41604</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>16/0/0</t>
+          <t>18/0/0</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="10" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
@@ -1329,16 +1329,16 @@
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:07</t>
+          <t>2026-09-28 09:16</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>07a26890b5</t>
+          <t>51a52339ab</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -1384,11 +1384,11 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:06</t>
+          <t>2026-09-28 09:07</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>16/1/0</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1426,24 +1426,20 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J19" s="11" t="n">
-        <v>86</v>
+      <c r="J19" s="10" t="n">
+        <v>87</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>C1-13</t>
-        </is>
-      </c>
+      <c r="M19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -1457,7 +1453,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16/1/0</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1467,81 +1463,85 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>16</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>86</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>C1-13</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:46</t>
+          <t>2026-09-28 09:06</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>b588bab9b3</t>
+          <t>07a26890b5</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>16/0/0</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" s="10" t="n">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
@@ -1553,16 +1553,16 @@
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:40</t>
+          <t>2026-09-28 08:46</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>d5213f9578</t>
+          <t>b588bab9b3</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -1604,19 +1604,15 @@
       <c r="L22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>사업계획서 체크포인트(C2-14) 추가 후 전체 통과</t>
-        </is>
-      </c>
+      <c r="M22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:39</t>
+          <t>2026-09-28 08:40</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1626,61 +1622,61 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>13/1/0</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>13</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>C2-14</t>
+          <t>사업계획서 체크포인트(C2-14) 추가 후 전체 통과</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:26</t>
+          <t>2026-09-28 08:39</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>9b24f45ce5</t>
+          <t>d5213f9578</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -1690,19 +1686,19 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
+          <t>13/1/0</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>14/0/0</t>
-        </is>
-      </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -1713,24 +1709,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J24" s="10" t="n">
-        <v>14</v>
+      <c r="J24" s="11" t="n">
+        <v>13</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>C2-14</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:25</t>
+          <t>2026-09-28 08:26</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -1760,16 +1760,16 @@
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
@@ -1781,21 +1781,21 @@
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:24</t>
+          <t>2026-09-28 08:25</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>22774ad88d</t>
+          <t>9b24f45ce5</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>16/1/0</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1823,38 +1823,34 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J26" s="11" t="n">
-        <v>83</v>
+      <c r="J26" s="10" t="n">
+        <v>84</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>C1-02</t>
-        </is>
-      </c>
+      <c r="M26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:01</t>
+          <t>2026-09-28 08:24</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>a6368b6542</t>
+          <t>22774ad88d</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>16/1/0</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1882,24 +1878,28 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J27" s="10" t="n">
-        <v>84</v>
+      <c r="J27" s="11" t="n">
+        <v>83</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="6" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>C1-02</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:00</t>
+          <t>2026-09-28 08:01</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -1946,24 +1946,20 @@
       <c r="L28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="6" t="inlineStr">
-        <is>
-          <t>보드 수정 반영(기동 코드 주석 위치) — 해시 변경</t>
-        </is>
-      </c>
+      <c r="M28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:58</t>
+          <t>2026-09-28 08:00</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>a59d40dd6c</t>
+          <t>a6368b6542</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -2005,15 +2001,19 @@
       <c r="L29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="6" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>보드 수정 반영(기동 코드 주석 위치) — 해시 변경</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:56</t>
+          <t>2026-09-28 07:58</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>11/2/0</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -2051,24 +2051,20 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J30" s="11" t="n">
-        <v>82</v>
+      <c r="J30" s="10" t="n">
+        <v>84</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="6" t="inlineStr">
-        <is>
-          <t>C2-09, C2-10 — 하네스 선택자 결함(보드 무관), 3회차에서 수정 확인</t>
-        </is>
-      </c>
+      <c r="M30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
@@ -2087,39 +2083,98 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/2/0</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="n">
-        <v>17</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>82</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>C2-09, C2-10 — 하네스 선택자 결함(보드 무관), 3회차에서 수정 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>a59d40dd6c</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>17/0/0</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>CASE1만 실행(하네스 점검)</t>
         </is>
@@ -2216,7 +2271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR21"/>
+  <dimension ref="A1:AT21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2263,6 +2318,8 @@
     <col width="40" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="40" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2520,6 +2577,17 @@
           <t>27회차 메모</t>
         </is>
       </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 결과
+2026-09-28 23:56</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2662,6 +2730,12 @@
         </is>
       </c>
       <c r="AR5" s="6" t="inlineStr"/>
+      <c r="AS5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2808,6 +2882,12 @@
         </is>
       </c>
       <c r="AR6" s="6" t="inlineStr"/>
+      <c r="AS6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2954,6 +3034,12 @@
         </is>
       </c>
       <c r="AR7" s="6" t="inlineStr"/>
+      <c r="AS7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -3096,6 +3182,12 @@
         </is>
       </c>
       <c r="AR8" s="6" t="inlineStr"/>
+      <c r="AS8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -3238,6 +3330,12 @@
         </is>
       </c>
       <c r="AR9" s="6" t="inlineStr"/>
+      <c r="AS9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -3384,6 +3482,12 @@
         </is>
       </c>
       <c r="AR10" s="6" t="inlineStr"/>
+      <c r="AS10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -3526,6 +3630,12 @@
         </is>
       </c>
       <c r="AR11" s="6" t="inlineStr"/>
+      <c r="AS11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -3672,6 +3782,12 @@
         </is>
       </c>
       <c r="AR12" s="6" t="inlineStr"/>
+      <c r="AS12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -3814,6 +3930,12 @@
         </is>
       </c>
       <c r="AR13" s="6" t="inlineStr"/>
+      <c r="AS13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -3956,6 +4078,12 @@
         </is>
       </c>
       <c r="AR14" s="6" t="inlineStr"/>
+      <c r="AS14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -4098,6 +4226,12 @@
         </is>
       </c>
       <c r="AR15" s="6" t="inlineStr"/>
+      <c r="AS15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -4240,6 +4374,12 @@
         </is>
       </c>
       <c r="AR16" s="6" t="inlineStr"/>
+      <c r="AS16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -4390,6 +4530,12 @@
         </is>
       </c>
       <c r="AR17" s="6" t="inlineStr"/>
+      <c r="AS17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -4532,6 +4678,12 @@
         </is>
       </c>
       <c r="AR18" s="6" t="inlineStr"/>
+      <c r="AS18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -4674,6 +4826,12 @@
         </is>
       </c>
       <c r="AR19" s="6" t="inlineStr"/>
+      <c r="AS19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -4816,6 +4974,12 @@
         </is>
       </c>
       <c r="AR20" s="6" t="inlineStr"/>
+      <c r="AS20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -4958,6 +5122,12 @@
         </is>
       </c>
       <c r="AR21" s="6" t="inlineStr"/>
+      <c r="AS21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT21" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4970,7 +5140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD31"/>
+  <dimension ref="A1:BF32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5029,6 +5199,8 @@
     <col width="40" customWidth="1" min="54" max="54"/>
     <col width="12" customWidth="1" min="55" max="55"/>
     <col width="40" customWidth="1" min="56" max="56"/>
+    <col width="12" customWidth="1" min="57" max="57"/>
+    <col width="40" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5352,6 +5524,17 @@
           <t>27회차 메모</t>
         </is>
       </c>
+      <c r="BE4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 결과
+2026-09-28 23:56</t>
+        </is>
+      </c>
+      <c r="BF4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -5534,6 +5717,12 @@
         </is>
       </c>
       <c r="BD5" s="6" t="inlineStr"/>
+      <c r="BE5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -5712,6 +5901,12 @@
         </is>
       </c>
       <c r="BD6" s="6" t="inlineStr"/>
+      <c r="BE6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -5890,6 +6085,12 @@
         </is>
       </c>
       <c r="BD7" s="6" t="inlineStr"/>
+      <c r="BE7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -6072,6 +6273,12 @@
         </is>
       </c>
       <c r="BD8" s="6" t="inlineStr"/>
+      <c r="BE8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -6250,6 +6457,12 @@
         </is>
       </c>
       <c r="BD9" s="6" t="inlineStr"/>
+      <c r="BE9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -6428,6 +6641,12 @@
         </is>
       </c>
       <c r="BD10" s="6" t="inlineStr"/>
+      <c r="BE10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -6606,6 +6825,12 @@
         </is>
       </c>
       <c r="BD11" s="6" t="inlineStr"/>
+      <c r="BE11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -6784,6 +7009,12 @@
         </is>
       </c>
       <c r="BD12" s="6" t="inlineStr"/>
+      <c r="BE12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -6966,6 +7197,12 @@
         </is>
       </c>
       <c r="BD13" s="6" t="inlineStr"/>
+      <c r="BE13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -7152,6 +7389,12 @@
         </is>
       </c>
       <c r="BD14" s="6" t="inlineStr"/>
+      <c r="BE14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -7330,6 +7573,12 @@
         </is>
       </c>
       <c r="BD15" s="6" t="inlineStr"/>
+      <c r="BE15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -7508,6 +7757,12 @@
         </is>
       </c>
       <c r="BD16" s="6" t="inlineStr"/>
+      <c r="BE16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -7686,6 +7941,12 @@
         </is>
       </c>
       <c r="BD17" s="6" t="inlineStr"/>
+      <c r="BE17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -7836,6 +8097,12 @@
         </is>
       </c>
       <c r="BD18" s="6" t="inlineStr"/>
+      <c r="BE18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -7964,6 +8231,12 @@
         </is>
       </c>
       <c r="BD19" s="6" t="inlineStr"/>
+      <c r="BE19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -8092,6 +8365,12 @@
         </is>
       </c>
       <c r="BD20" s="6" t="inlineStr"/>
+      <c r="BE20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -8196,6 +8475,12 @@
         </is>
       </c>
       <c r="BD21" s="6" t="inlineStr"/>
+      <c r="BE21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -8300,6 +8585,12 @@
         </is>
       </c>
       <c r="BD22" s="6" t="inlineStr"/>
+      <c r="BE22" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -8390,6 +8681,12 @@
         </is>
       </c>
       <c r="BD23" s="6" t="inlineStr"/>
+      <c r="BE23" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -8480,6 +8777,12 @@
         </is>
       </c>
       <c r="BD24" s="6" t="inlineStr"/>
+      <c r="BE24" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -8566,6 +8869,12 @@
         </is>
       </c>
       <c r="BD25" s="6" t="inlineStr"/>
+      <c r="BE25" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -8652,6 +8961,12 @@
         </is>
       </c>
       <c r="BD26" s="6" t="inlineStr"/>
+      <c r="BE26" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -8715,6 +9030,12 @@
         </is>
       </c>
       <c r="BD27" s="6" t="inlineStr"/>
+      <c r="BE27" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -8783,6 +9104,12 @@
         </is>
       </c>
       <c r="BD28" s="6" t="inlineStr"/>
+      <c r="BE28" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -8839,6 +9166,12 @@
         </is>
       </c>
       <c r="BD29" s="6" t="inlineStr"/>
+      <c r="BE29" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -8895,6 +9228,12 @@
         </is>
       </c>
       <c r="BD30" s="6" t="inlineStr"/>
+      <c r="BE30" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -8939,6 +9278,46 @@
         </is>
       </c>
       <c r="BD31" s="6" t="inlineStr"/>
+      <c r="BE31" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>C2-28</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>업체명 = 소공인 기관 선택</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>«+ 새 과제» 업체명 목록 → «+ 새 소공인 기관 등록…» → 기관 저장 → 취소 → 정리</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>선택 목록(자유 입력 없음)에 소공인 기관만, 공급기업 없음, 새 기관 창 유형 소공인, 저장하면 그 기관이 선택됨</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="BE32" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BF32" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8951,2366 +9330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="40" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="40" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="40" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="40" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="40" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
-    <col width="40" customWidth="1" min="38" max="38"/>
-    <col width="12" customWidth="1" min="39" max="39"/>
-    <col width="40" customWidth="1" min="40" max="40"/>
-    <col width="12" customWidth="1" min="41" max="41"/>
-    <col width="40" customWidth="1" min="42" max="42"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>CASE3 — 골프 양말 · 봉조 자동화 편직기 (원공고)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 4쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>조작</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>기대 결과</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>자동화 방식</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>근거</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2회차 결과
-2026-09-28 07:56</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2회차 메모</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>3회차 결과
-2026-09-28 07:58</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>3회차 메모</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>4회차 결과
-2026-09-28 08:00</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>4회차 메모</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>5회차 결과
-2026-09-28 08:01</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>5회차 메모</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>6회차 결과
-2026-09-28 08:24</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>6회차 메모</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>7회차 결과
-2026-09-28 08:25</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>7회차 메모</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>10회차 결과
-2026-09-28 08:40</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>10회차 메모</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>11회차 결과
-2026-09-28 08:46</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>11회차 메모</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>13회차 결과
-2026-09-28 09:06</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>13회차 메모</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>14회차 결과
-2026-09-28 09:07</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>14회차 메모</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>15회차 결과
-2026-09-28 09:16</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>15회차 메모</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>17회차 결과
-2026-09-28 09:22</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>17회차 메모</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>18회차 결과
-2026-09-28 09:24</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>18회차 메모</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>21회차 결과
-2026-09-28 11:14</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>21회차 메모</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>22회차 결과
-2026-09-28 23:25</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>22회차 메모</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>23회차 결과
-2026-09-28 23:27</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>23회차 메모</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>25회차 결과
-2026-09-28 23:34</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>25회차 메모</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>27회차 결과
-2026-09-28 23:48</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>27회차 메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>C3-01</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>이사를 소공인 담당자로</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>기관 1곳에 대표·이사 등록, 과제 소공인 = 이사</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>상세 소공인 «[테스트] C3담당 이사»</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>실경영은 담당 이사</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr"/>
-      <c r="U5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V5" s="6" t="inlineStr"/>
-      <c r="W5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X5" s="6" t="inlineStr"/>
-      <c r="Y5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z5" s="6" t="inlineStr"/>
-      <c r="AA5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB5" s="6" t="inlineStr"/>
-      <c r="AC5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD5" s="6" t="inlineStr"/>
-      <c r="AE5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF5" s="6" t="inlineStr"/>
-      <c r="AG5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH5" s="6" t="inlineStr"/>
-      <c r="AI5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ5" s="6" t="inlineStr"/>
-      <c r="AK5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL5" s="6" t="inlineStr"/>
-      <c r="AM5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN5" s="6" t="inlineStr"/>
-      <c r="AO5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>C3-02</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>존칭</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>1단계 보내기 → 소공인 · 일정 조율</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>«[테스트] C3담당 이사님 안녕하세요.»(«이사 대표님» 아님)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr"/>
-      <c r="O6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T6" s="6" t="inlineStr"/>
-      <c r="U6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V6" s="6" t="inlineStr"/>
-      <c r="W6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X6" s="6" t="inlineStr"/>
-      <c r="Y6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z6" s="6" t="inlineStr"/>
-      <c r="AA6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB6" s="6" t="inlineStr"/>
-      <c r="AC6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD6" s="6" t="inlineStr"/>
-      <c r="AE6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF6" s="6" t="inlineStr"/>
-      <c r="AG6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH6" s="6" t="inlineStr"/>
-      <c r="AI6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ6" s="6" t="inlineStr"/>
-      <c r="AK6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL6" s="6" t="inlineStr"/>
-      <c r="AM6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN6" s="6" t="inlineStr"/>
-      <c r="AO6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>C3-03</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>마스터 반영</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>이사 전화 010-0000-3334로 수정</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>과제 스냅샷 전화 자동 반영</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr"/>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr"/>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr"/>
-      <c r="U7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V7" s="6" t="inlineStr"/>
-      <c r="W7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X7" s="6" t="inlineStr"/>
-      <c r="Y7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z7" s="6" t="inlineStr"/>
-      <c r="AA7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB7" s="6" t="inlineStr"/>
-      <c r="AC7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD7" s="6" t="inlineStr"/>
-      <c r="AE7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF7" s="6" t="inlineStr"/>
-      <c r="AG7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH7" s="6" t="inlineStr"/>
-      <c r="AI7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ7" s="6" t="inlineStr"/>
-      <c r="AK7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL7" s="6" t="inlineStr"/>
-      <c r="AM7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN7" s="6" t="inlineStr"/>
-      <c r="AO7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>C3-04</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>전화 검색</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>검색 «01000003334»</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>결과에 과제·담당자</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr"/>
-      <c r="O8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr"/>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T8" s="6" t="inlineStr"/>
-      <c r="U8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V8" s="6" t="inlineStr"/>
-      <c r="W8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X8" s="6" t="inlineStr"/>
-      <c r="Y8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z8" s="6" t="inlineStr"/>
-      <c r="AA8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB8" s="6" t="inlineStr"/>
-      <c r="AC8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD8" s="6" t="inlineStr"/>
-      <c r="AE8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF8" s="6" t="inlineStr"/>
-      <c r="AG8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH8" s="6" t="inlineStr"/>
-      <c r="AI8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ8" s="6" t="inlineStr"/>
-      <c r="AK8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL8" s="6" t="inlineStr"/>
-      <c r="AM8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN8" s="6" t="inlineStr"/>
-      <c r="AO8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>C3-05</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>검색 변형</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>«3334», «0000-3334», «0000 3334»</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>같은 결과</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr"/>
-      <c r="O9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr"/>
-      <c r="U9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V9" s="6" t="inlineStr"/>
-      <c r="W9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X9" s="6" t="inlineStr"/>
-      <c r="Y9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z9" s="6" t="inlineStr"/>
-      <c r="AA9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB9" s="6" t="inlineStr"/>
-      <c r="AC9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD9" s="6" t="inlineStr"/>
-      <c r="AE9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF9" s="6" t="inlineStr"/>
-      <c r="AG9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH9" s="6" t="inlineStr"/>
-      <c r="AI9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ9" s="6" t="inlineStr"/>
-      <c r="AK9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL9" s="6" t="inlineStr"/>
-      <c r="AM9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN9" s="6" t="inlineStr"/>
-      <c r="AO9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>C3-06</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>견적 오기</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>S/W 단가 «6,600,00» 입력 → 거부 확인 후 «6,000,000»으로 등록</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>«쉼표 자리가 맞지 않습니다» 오류로 저장 안 됨 → 6,000,000 저장</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>원문 합계 «6,600,00원»</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr"/>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr"/>
-      <c r="O10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T10" s="6" t="inlineStr"/>
-      <c r="U10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V10" s="6" t="inlineStr"/>
-      <c r="W10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X10" s="6" t="inlineStr"/>
-      <c r="Y10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z10" s="6" t="inlineStr"/>
-      <c r="AA10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB10" s="6" t="inlineStr"/>
-      <c r="AC10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD10" s="6" t="inlineStr"/>
-      <c r="AE10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF10" s="6" t="inlineStr"/>
-      <c r="AG10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH10" s="6" t="inlineStr"/>
-      <c r="AI10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ10" s="6" t="inlineStr"/>
-      <c r="AK10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL10" s="6" t="inlineStr"/>
-      <c r="AM10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN10" s="6" t="inlineStr"/>
-      <c r="AO10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>C3-07</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>편직기 2, S/W 1</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>«검토 중 · 2대»</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr"/>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T11" s="6" t="inlineStr"/>
-      <c r="U11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V11" s="6" t="inlineStr"/>
-      <c r="W11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X11" s="6" t="inlineStr"/>
-      <c r="Y11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z11" s="6" t="inlineStr"/>
-      <c r="AA11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB11" s="6" t="inlineStr"/>
-      <c r="AC11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD11" s="6" t="inlineStr"/>
-      <c r="AE11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF11" s="6" t="inlineStr"/>
-      <c r="AG11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH11" s="6" t="inlineStr"/>
-      <c r="AI11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL11" s="6" t="inlineStr"/>
-      <c r="AM11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN11" s="6" t="inlineStr"/>
-      <c r="AO11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>C3-08</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>납기 예정</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>6단계 예정일 T+30(입금 후 30일)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>카드 «다음 … 장비 공급 D-30»</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>납기 입금 후 30일 이내</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr"/>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr"/>
-      <c r="O12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr"/>
-      <c r="Q12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr"/>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T12" s="6" t="inlineStr"/>
-      <c r="U12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr"/>
-      <c r="W12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X12" s="6" t="inlineStr"/>
-      <c r="Y12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z12" s="6" t="inlineStr"/>
-      <c r="AA12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB12" s="6" t="inlineStr"/>
-      <c r="AC12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD12" s="6" t="inlineStr"/>
-      <c r="AE12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF12" s="6" t="inlineStr"/>
-      <c r="AG12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH12" s="6" t="inlineStr"/>
-      <c r="AI12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL12" s="6" t="inlineStr"/>
-      <c r="AM12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN12" s="6" t="inlineStr"/>
-      <c r="AO12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>C3-09</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>캘린더 등록</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>«일정» 탭 6단계 «등록»</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 1건, «등록됨», 활동 «캘린더 · 자동»</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr"/>
-      <c r="O13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr"/>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr"/>
-      <c r="U13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr"/>
-      <c r="W13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X13" s="6" t="inlineStr"/>
-      <c r="Y13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z13" s="6" t="inlineStr"/>
-      <c r="AA13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB13" s="6" t="inlineStr"/>
-      <c r="AC13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD13" s="6" t="inlineStr"/>
-      <c r="AE13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF13" s="6" t="inlineStr"/>
-      <c r="AG13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH13" s="6" t="inlineStr"/>
-      <c r="AI13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL13" s="6" t="inlineStr"/>
-      <c r="AM13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN13" s="6" t="inlineStr"/>
-      <c r="AO13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>C3-10</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 내용</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>목 이벤트 확인</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>제목 «[스마트제조] … · 6. 장비 공급», 종일, 시작 T+30·끝 T+31, Asia/Seoul</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>캘린더 앱 확인 대체</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr"/>
-      <c r="O14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr"/>
-      <c r="Q14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr"/>
-      <c r="U14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr"/>
-      <c r="W14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X14" s="6" t="inlineStr"/>
-      <c r="Y14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z14" s="6" t="inlineStr"/>
-      <c r="AA14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB14" s="6" t="inlineStr"/>
-      <c r="AC14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD14" s="6" t="inlineStr"/>
-      <c r="AE14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF14" s="6" t="inlineStr"/>
-      <c r="AG14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH14" s="6" t="inlineStr"/>
-      <c r="AI14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL14" s="6" t="inlineStr"/>
-      <c r="AM14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN14" s="6" t="inlineStr"/>
-      <c r="AO14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>C3-11</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>날짜 변경 감지</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>예정일 T+35 → «오늘» 캘린더 미등록</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>«날짜 변경 (캘린더 T+30)»</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr"/>
-      <c r="O15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr"/>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr"/>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr"/>
-      <c r="U15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr"/>
-      <c r="W15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X15" s="6" t="inlineStr"/>
-      <c r="Y15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z15" s="6" t="inlineStr"/>
-      <c r="AA15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB15" s="6" t="inlineStr"/>
-      <c r="AC15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD15" s="6" t="inlineStr"/>
-      <c r="AE15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF15" s="6" t="inlineStr"/>
-      <c r="AG15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH15" s="6" t="inlineStr"/>
-      <c r="AI15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL15" s="6" t="inlineStr"/>
-      <c r="AM15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN15" s="6" t="inlineStr"/>
-      <c r="AO15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>C3-12</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>날짜 수정</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>«일정» 탭 «날짜 수정»</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 T+35, 활동 제목 «날짜 변경 T+30 → T+35», 미등록 목록에서 사라짐</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr"/>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr"/>
-      <c r="O16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr"/>
-      <c r="U16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr"/>
-      <c r="W16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X16" s="6" t="inlineStr"/>
-      <c r="Y16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z16" s="6" t="inlineStr"/>
-      <c r="AA16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB16" s="6" t="inlineStr"/>
-      <c r="AC16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD16" s="6" t="inlineStr"/>
-      <c r="AE16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF16" s="6" t="inlineStr"/>
-      <c r="AG16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH16" s="6" t="inlineStr"/>
-      <c r="AI16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL16" s="6" t="inlineStr"/>
-      <c r="AM16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN16" s="6" t="inlineStr"/>
-      <c r="AO16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>C3-13</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>메모 → 초안</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>2단계 메모 후 수행일지 2차 초안</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>활동요약에 «· (MM-DD) 원문»</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr"/>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr"/>
-      <c r="O17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr"/>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T17" s="6" t="inlineStr"/>
-      <c r="U17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr"/>
-      <c r="W17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X17" s="6" t="inlineStr"/>
-      <c r="Y17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z17" s="6" t="inlineStr"/>
-      <c r="AA17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB17" s="6" t="inlineStr"/>
-      <c r="AC17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD17" s="6" t="inlineStr"/>
-      <c r="AE17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF17" s="6" t="inlineStr"/>
-      <c r="AG17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH17" s="6" t="inlineStr"/>
-      <c r="AI17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL17" s="6" t="inlineStr"/>
-      <c r="AM17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN17" s="6" t="inlineStr"/>
-      <c r="AO17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>C3-14</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>서명란</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>2차 초안 서명란 확인</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>«신청인(대표) : [테스트] C3담당» — 이사 이름(질문 3)</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr"/>
-      <c r="O18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr"/>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T18" s="6" t="inlineStr"/>
-      <c r="U18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr"/>
-      <c r="W18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X18" s="6" t="inlineStr"/>
-      <c r="Y18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z18" s="6" t="inlineStr"/>
-      <c r="AA18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB18" s="6" t="inlineStr"/>
-      <c r="AC18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD18" s="6" t="inlineStr"/>
-      <c r="AE18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF18" s="6" t="inlineStr"/>
-      <c r="AG18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH18" s="6" t="inlineStr"/>
-      <c r="AI18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL18" s="6" t="inlineStr"/>
-      <c r="AM18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN18" s="6" t="inlineStr"/>
-      <c r="AO18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>C3-15</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>정리</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>과제 삭제</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>«구글 캘린더에 등록된 일정 1건은 지워지지 않았습니다» 안내, 이후 장비·담당자·기관 삭제</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr"/>
-      <c r="O19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr"/>
-      <c r="Q19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr"/>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T19" s="6" t="inlineStr"/>
-      <c r="U19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr"/>
-      <c r="W19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X19" s="6" t="inlineStr"/>
-      <c r="Y19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z19" s="6" t="inlineStr"/>
-      <c r="AA19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB19" s="6" t="inlineStr"/>
-      <c r="AC19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD19" s="6" t="inlineStr"/>
-      <c r="AE19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF19" s="6" t="inlineStr"/>
-      <c r="AG19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH19" s="6" t="inlineStr"/>
-      <c r="AI19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL19" s="6" t="inlineStr"/>
-      <c r="AM19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN19" s="6" t="inlineStr"/>
-      <c r="AO19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP19" s="6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AR18"/>
+  <dimension ref="A1:AR19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11362,14 +9382,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE4 — 지르코니아 치과 보철 · CNC 밀링 (추가공고)</t>
+          <t>CASE3 — 골프 양말 · 봉조 자동화 편직기 (원공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 5쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 4쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
         </is>
       </c>
     </row>
@@ -11473,167 +9493,167 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>8회차 결과
-2026-09-28 08:26</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>8회차 메모</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
           <t>10회차 결과
 2026-09-28 08:40</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>10회차 메모</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>11회차 결과
 2026-09-28 08:46</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>11회차 메모</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>13회차 결과
 2026-09-28 09:06</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>13회차 메모</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>14회차 결과
 2026-09-28 09:07</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>14회차 메모</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>15회차 결과
 2026-09-28 09:16</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>15회차 메모</t>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>17회차 결과
 2026-09-28 09:22</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>17회차 메모</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>18회차 결과
 2026-09-28 09:24</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>18회차 메모</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>21회차 결과
 2026-09-28 11:14</t>
         </is>
       </c>
-      <c r="AJ4" s="3" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>21회차 메모</t>
         </is>
       </c>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>22회차 결과
 2026-09-28 23:25</t>
         </is>
       </c>
-      <c r="AL4" s="3" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr">
         <is>
           <t>22회차 메모</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <t>23회차 결과
 2026-09-28 23:27</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>23회차 메모</t>
         </is>
       </c>
-      <c r="AO4" s="3" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>25회차 결과
 2026-09-28 23:34</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
+      <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>25회차 메모</t>
         </is>
       </c>
-      <c r="AQ4" s="3" t="inlineStr">
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>27회차 결과
 2026-09-28 23:48</t>
         </is>
       </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 메모</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 결과
+2026-09-28 23:56</t>
+        </is>
+      </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>27회차 메모</t>
+          <t>28회차 메모</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C4-01</t>
+          <t>C3-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>공고 미지정</t>
+          <t>이사를 소공인 담당자로</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>공고 구분 비우고 과제 생성</t>
+          <t>기관 1곳에 대표·이사 등록, 과제 소공인 = 이사</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>카드 «공고 미확인», 상세 경고 문구</t>
+          <t>상세 소공인 «[테스트] C3담당 이사»</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -11641,7 +9661,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>실경영은 담당 이사</t>
+        </is>
+      </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -11760,22 +9784,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C4-02</t>
+          <t>C3-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>미확인 필터</t>
+          <t>존칭</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>공고 필터 = 공고 미확인</t>
+          <t>1단계 보내기 → 소공인 · 일정 조율</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>이 과제 보임</t>
+          <t>«[테스트] C3담당 이사님 안녕하세요.»(«이사 대표님» 아님)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -11902,22 +9926,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C4-03</t>
+          <t>C3-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>추가공고 지정</t>
+          <t>마스터 반영</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>상세 공고 구분 = 추가공고</t>
+          <t>이사 전화 010-0000-3334로 수정</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>배지 «추가공고», 원공고 필터에서 숨김, CSV 공고 열 «추가공고»</t>
+          <t>과제 스냅샷 전화 자동 반영</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -11925,11 +9949,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>연매출 2억원 미만</t>
-        </is>
-      </c>
+      <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -12048,34 +10068,30 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C4-04</t>
+          <t>C3-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 화면</t>
+          <t>전화 검색</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>390×844 에뮬레이션</t>
+          <t>검색 «01000003334»</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>하단 탭바(더보기 보임, 기관 탭 숨김), 가로 넘침 없음, 범례 숨김</t>
+          <t>결과에 과제·담당자</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>실기기 대체</t>
-        </is>
-      </c>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -12194,27 +10210,27 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C4-05</t>
+          <t>C3-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 진단 입력</t>
+          <t>검색 변형</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>1차 진단 5칸 입력, 칸 이동은 탭 한 번</t>
+          <t>«3334», «0000-3334», «0000 3334»</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>입력칸 16px, 다음 칸으로 포커스 이동, 값 저장</t>
+          <t>같은 결과</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -12336,32 +10352,32 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C4-06</t>
+          <t>C3-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>입력 중 재그리기</t>
+          <t>견적 오기</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>입력 중 스냅샷 강제 발행</t>
+          <t>S/W 단가 «6,600,00» 입력 → 거부 확인 후 «6,000,000»으로 등록</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>입력 중인 글자 유지</t>
+          <t>«쉼표 자리가 맞지 않습니다» 오류로 저장 안 됨 → 6,000,000 저장</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>다른 기기 수정 대체</t>
+          <t>원문 합계 «6,600,00원»</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -12482,22 +10498,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C4-07</t>
+          <t>C3-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2차 진단 입력</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>②·③·기록 수준 입력</t>
+          <t>편직기 2, S/W 1</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>«검토 중 · 2대»</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -12624,22 +10640,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C4-08</t>
+          <t>C3-08</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1차 초안 반영</t>
+          <t>납기 예정</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>1단계 초안</t>
+          <t>6단계 예정일 T+30(입금 후 30일)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>입력 5칸 원문, ⑤⑥⑦ «미확인 — …»</t>
+          <t>카드 «다음 … 장비 공급 D-30»</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -12647,7 +10663,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>납기 입금 후 30일 이내</t>
+        </is>
+      </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -12766,27 +10786,27 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C4-09</t>
+          <t>C3-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2·3차 초안</t>
+          <t>캘린더 등록</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>2·7단계 초안</t>
+          <t>«일정» 탭 6단계 «등록»</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>2차 ③ 원문, 3차 향후 사후관리 «미확인 — …»</t>
+          <t>이벤트 1건, «등록됨», 활동 «캘린더 · 자동»</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
@@ -12908,32 +10928,32 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C4-10</t>
+          <t>C3-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>수치 비생성</t>
+          <t>이벤트 내용</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>초안 숫자 대조</t>
+          <t>목 이벤트 확인</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>6개·10개 외 수치(%, 증가율) 없음</t>
+          <t>제목 «[스마트제조] … · 6. 장비 공급», 종일, 시작 T+30·끝 T+31, Asia/Seoul</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>하루 6개 → 10개</t>
+          <t>캘린더 앱 확인 대체</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -13054,22 +11074,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C4-11</t>
+          <t>C3-11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>결과보고서 초안</t>
+          <t>날짜 변경 감지</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>8단계 초안</t>
+          <t>예정일 T+35 → «오늘» 캘린더 미등록</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>3. KPI에 1차 ②·④·2차 ② 진단 줄, 5.에 기록 방식 줄, 초안 표시</t>
+          <t>«날짜 변경 (캘린더 T+30)»</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -13196,27 +11216,27 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C4-12</t>
+          <t>C3-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>장비·자산 → 초안</t>
+          <t>날짜 수정</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>덴탈 CNC밀링기·Dentalsoft 등록, 자산 각 1 → 3차·결과보고서 초안</t>
+          <t>«일정» 탭 «날짜 수정»</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>3차 «④ 도입 장비»·결과보고서 4에 «[H/W] 덴탈 CNC밀링기 마닉스 5SA × 1대 (검토 중)»·«[S/W] Dentalsoft × 1식 (검토 중)», 금액 없음</t>
+          <t>이벤트 T+35, 활동 제목 «날짜 변경 T+30 → T+35», 미등록 목록에서 사라짐</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
@@ -13338,27 +11358,27 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>C4-13</t>
+          <t>C3-13</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 더보기</t>
+          <t>메모 → 초안</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>더보기 → 자산</t>
+          <t>2단계 메모 후 수행일지 2차 초안</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>메뉴 열림, 버튼 라벨 «자산 ▴», 자산 목록</t>
+          <t>활동요약에 «· (MM-DD) 원문»</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
@@ -13480,22 +11500,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>C4-14</t>
+          <t>C3-14</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>정리</t>
+          <t>서명란</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>과제·장비·담당자·기관 삭제</t>
+          <t>2차 초안 서명란 확인</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>삭제 완료</t>
+          <t>«신청인(대표) : [테스트] C3담당» — 이사 이름(질문 3)</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -13618,19 +11638,161 @@
         </is>
       </c>
       <c r="AR18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>C3-15</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>정리</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>«구글 캘린더에 등록된 일정 1건은 지워지지 않았습니다» 안내, 이후 장비·담당자·기관 삭제</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr"/>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr"/>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr"/>
+      <c r="U19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr"/>
+      <c r="W19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X19" s="6" t="inlineStr"/>
+      <c r="Y19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z19" s="6" t="inlineStr"/>
+      <c r="AA19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB19" s="6" t="inlineStr"/>
+      <c r="AC19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD19" s="6" t="inlineStr"/>
+      <c r="AE19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF19" s="6" t="inlineStr"/>
+      <c r="AG19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr"/>
+      <c r="AI19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ19" s="6" t="inlineStr"/>
+      <c r="AK19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL19" s="6" t="inlineStr"/>
+      <c r="AM19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN19" s="6" t="inlineStr"/>
+      <c r="AO19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP19" s="6" t="inlineStr"/>
+      <c r="AQ19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR19" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP16"/>
+  <dimension ref="A1:AT18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13675,19 +11837,23 @@
     <col width="40" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="40" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="40" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE5 — 친환경 벽지 · 라텍스 프린터 + 자동견적 (추가공고)</t>
+          <t>CASE4 — 지르코니아 치과 보철 · CNC 밀링 (추가공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 6쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 5쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
         </is>
       </c>
     </row>
@@ -13791,156 +11957,178 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
+          <t>8회차 결과
+2026-09-28 08:26</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>8회차 메모</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
           <t>10회차 결과
 2026-09-28 08:40</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>10회차 메모</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>11회차 결과
 2026-09-28 08:46</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>11회차 메모</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>13회차 결과
 2026-09-28 09:06</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>13회차 메모</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>14회차 결과
 2026-09-28 09:07</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>14회차 메모</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>15회차 결과
 2026-09-28 09:16</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>15회차 메모</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>17회차 결과
 2026-09-28 09:22</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>17회차 메모</t>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>18회차 결과
 2026-09-28 09:24</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>18회차 메모</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>21회차 결과
 2026-09-28 11:14</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr">
         <is>
           <t>21회차 메모</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <t>22회차 결과
 2026-09-28 23:25</t>
         </is>
       </c>
-      <c r="AJ4" s="3" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>22회차 메모</t>
         </is>
       </c>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>23회차 결과
 2026-09-28 23:27</t>
         </is>
       </c>
-      <c r="AL4" s="3" t="inlineStr">
+      <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>23회차 메모</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>25회차 결과
 2026-09-28 23:34</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr">
         <is>
           <t>25회차 메모</t>
         </is>
       </c>
-      <c r="AO4" s="3" t="inlineStr">
+      <c r="AQ4" s="3" t="inlineStr">
         <is>
           <t>27회차 결과
 2026-09-28 23:48</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
+      <c r="AR4" s="3" t="inlineStr">
         <is>
           <t>27회차 메모</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 결과
+2026-09-28 23:56</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 메모</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C5-01</t>
+          <t>C4-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>지연·다음 예정</t>
+          <t>공고 미지정</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>추가공고 과제, 1단계 T-3, 2단계 T+4</t>
+          <t>공고 구분 비우고 과제 생성</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>카드 «다음 … 1차 방문 D+3», «지연 1»</t>
+          <t>카드 «공고 미확인», 상세 경고 문구</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -14057,26 +12245,38 @@
         </is>
       </c>
       <c r="AP5" s="6" t="inlineStr"/>
+      <c r="AQ5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR5" s="6" t="inlineStr"/>
+      <c r="AS5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C5-02</t>
+          <t>C4-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>오늘 탭</t>
+          <t>미확인 필터</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>«오늘» 탭</t>
+          <t>공고 필터 = 공고 미확인</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>기한 경과에 1단계, 7일 안의 방문에 2단계</t>
+          <t>이 과제 보임</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -14193,26 +12393,38 @@
         </is>
       </c>
       <c r="AP6" s="6" t="inlineStr"/>
+      <c r="AQ6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR6" s="6" t="inlineStr"/>
+      <c r="AS6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C5-03</t>
+          <t>C4-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>완료 누락 알림</t>
+          <t>추가공고 지정</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>1단계 산출물 미체크로 완료</t>
+          <t>상세 공고 구분 = 추가공고</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>알림에 «현장진단표, 1차 방문 확인 서명», 상태 «완료» 유지</t>
+          <t>배지 «추가공고», 원공고 필터에서 숨김, CSV 공고 열 «추가공고»</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -14220,7 +12432,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>연매출 2억원 미만</t>
+        </is>
+      </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -14329,34 +12545,50 @@
         </is>
       </c>
       <c r="AP7" s="6" t="inlineStr"/>
+      <c r="AQ7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR7" s="6" t="inlineStr"/>
+      <c r="AS7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C5-04</t>
+          <t>C4-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>알림 줄어듦</t>
+          <t>휴대폰 화면</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>현장진단표 체크 → 나머지 체크</t>
+          <t>390×844 에뮬레이션</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>알림 1개로 줄고, 다 체크하면 사라짐</t>
+          <t>하단 탭바(더보기 보임, 기관 탭 숨김), 가로 넘침 없음, 범례 숨김</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>실기기 대체</t>
+        </is>
+      </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -14465,31 +12697,43 @@
         </is>
       </c>
       <c r="AP8" s="6" t="inlineStr"/>
+      <c r="AQ8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR8" s="6" t="inlineStr"/>
+      <c r="AS8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C5-05</t>
+          <t>C4-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>서류 미수집</t>
+          <t>휴대폰 진단 입력</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>체크 1개 해제 → «오늘»</t>
+          <t>1차 진단 5칸 입력, 칸 이동은 탭 한 번</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>서명·서류 미수집에 1단계</t>
+          <t>입력칸 16px, 다음 칸으로 포커스 이동, 값 저장</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -14601,34 +12845,50 @@
         </is>
       </c>
       <c r="AP9" s="6" t="inlineStr"/>
+      <c r="AQ9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR9" s="6" t="inlineStr"/>
+      <c r="AS9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C5-06</t>
+          <t>C4-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>카톡 수동 기록</t>
+          <t>입력 중 재그리기</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>수행일지 송부 → 카톡 보냄 기록</t>
+          <t>입력 중 스냅샷 강제 발행</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>«카톡으로 보냄을 … 기록했습니다(수동 기록)», 버튼 «기록됨» 비활성</t>
+          <t>입력 중인 글자 유지</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr"/>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>다른 기기 수정 대체</t>
+        </is>
+      </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -14737,26 +12997,38 @@
         </is>
       </c>
       <c r="AP10" s="6" t="inlineStr"/>
+      <c r="AQ10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR10" s="6" t="inlineStr"/>
+      <c r="AS10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C5-07</t>
+          <t>C4-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>기록자</t>
+          <t>2차 진단 입력</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>«활동» 탭</t>
+          <t>②·③·기록 수준 입력</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>«카톡 · 수동», 기록자 «시험자»</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -14873,26 +13145,38 @@
         </is>
       </c>
       <c r="AP11" s="6" t="inlineStr"/>
+      <c r="AQ11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR11" s="6" t="inlineStr"/>
+      <c r="AS11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C5-08</t>
+          <t>C4-08</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>메모 작성자</t>
+          <t>1차 초안 반영</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>1단계 메모</t>
+          <t>1단계 초안</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>머리 «… · 시험자», 한국 시간</t>
+          <t>입력 5칸 원문, ⑤⑥⑦ «미확인 — …»</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -14900,11 +13184,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>KPI 설정 필요</t>
-        </is>
-      </c>
+      <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -15013,26 +13293,38 @@
         </is>
       </c>
       <c r="AP12" s="6" t="inlineStr"/>
+      <c r="AQ12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR12" s="6" t="inlineStr"/>
+      <c r="AS12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C5-09</t>
+          <t>C4-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>포함 품목</t>
+          <t>2·3차 초안</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>LATEX 730 / CNYX RIP(단가 비움) / QT-AI LITE 5,286,000</t>
+          <t>2·7단계 초안</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>RIP 단가 «—»</t>
+          <t>2차 ③ 원문, 3차 향후 사후관리 «미확인 — …»</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -15040,11 +13332,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>RIP «포함», S/W 할인 −714,000</t>
-        </is>
-      </c>
+      <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -15153,26 +13441,38 @@
         </is>
       </c>
       <c r="AP13" s="6" t="inlineStr"/>
+      <c r="AQ13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR13" s="6" t="inlineStr"/>
+      <c r="AS13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C5-10</t>
+          <t>C4-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>자산</t>
+          <t>수치 비생성</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>3건 등록 → 과제 상세 견적 합계</t>
+          <t>초안 숫자 대조</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>H/W 37,000,000원, «단가 없는 장비 1건 제외(CNYX RIP)», 경고 «1,174,889원 초과»</t>
+          <t>6개·10개 외 수치(%, 증가율) 없음</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -15180,7 +13480,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>하루 6개 → 10개</t>
+        </is>
+      </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -15289,26 +13593,38 @@
         </is>
       </c>
       <c r="AP14" s="6" t="inlineStr"/>
+      <c r="AQ14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR14" s="6" t="inlineStr"/>
+      <c r="AS14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C5-11</t>
+          <t>C4-11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>전체 백업</t>
+          <t>결과보고서 초안</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>«전체 백업 (JSON)»</t>
+          <t>8단계 초안</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>파일명·counts·notice «extra»·by id 포함, 이름 «시험자» 미포함</t>
+          <t>3. KPI에 1차 ②·④·2차 ② 진단 줄, 5.에 기록 방식 줄, 초안 표시</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -15425,26 +13741,38 @@
         </is>
       </c>
       <c r="AP15" s="6" t="inlineStr"/>
+      <c r="AQ15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR15" s="6" t="inlineStr"/>
+      <c r="AS15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C5-12</t>
+          <t>C4-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>정리</t>
+          <t>장비·자산 → 초안</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>과제·CASE5 장비 삭제(QT-AI 공급사 유지)</t>
+          <t>덴탈 CNC밀링기·Dentalsoft 등록, 자산 각 1 → 3차·결과보고서 초안</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>삭제 완료</t>
+          <t>3차 «④ 도입 장비»·결과보고서 4에 «[H/W] 덴탈 CNC밀링기 마닉스 5SA × 1대 (검토 중)»·«[S/W] Dentalsoft × 1식 (검토 중)», 금액 없음</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -15561,19 +13889,327 @@
         </is>
       </c>
       <c r="AP16" s="6" t="inlineStr"/>
+      <c r="AQ16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR16" s="6" t="inlineStr"/>
+      <c r="AS16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>C4-13</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>휴대폰 더보기</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>더보기 → 자산</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>메뉴 열림, 버튼 라벨 «자산 ▴», 자산 목록</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr"/>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr"/>
+      <c r="U17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr"/>
+      <c r="W17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X17" s="6" t="inlineStr"/>
+      <c r="Y17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z17" s="6" t="inlineStr"/>
+      <c r="AA17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB17" s="6" t="inlineStr"/>
+      <c r="AC17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD17" s="6" t="inlineStr"/>
+      <c r="AE17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF17" s="6" t="inlineStr"/>
+      <c r="AG17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr"/>
+      <c r="AI17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ17" s="6" t="inlineStr"/>
+      <c r="AK17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL17" s="6" t="inlineStr"/>
+      <c r="AM17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN17" s="6" t="inlineStr"/>
+      <c r="AO17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP17" s="6" t="inlineStr"/>
+      <c r="AQ17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR17" s="6" t="inlineStr"/>
+      <c r="AS17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>C4-14</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>정리</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>과제·장비·담당자·기관 삭제</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>삭제 완료</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr"/>
+      <c r="U18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr"/>
+      <c r="W18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X18" s="6" t="inlineStr"/>
+      <c r="Y18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z18" s="6" t="inlineStr"/>
+      <c r="AA18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB18" s="6" t="inlineStr"/>
+      <c r="AC18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD18" s="6" t="inlineStr"/>
+      <c r="AE18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF18" s="6" t="inlineStr"/>
+      <c r="AG18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH18" s="6" t="inlineStr"/>
+      <c r="AI18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ18" s="6" t="inlineStr"/>
+      <c r="AK18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL18" s="6" t="inlineStr"/>
+      <c r="AM18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN18" s="6" t="inlineStr"/>
+      <c r="AO18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP18" s="6" t="inlineStr"/>
+      <c r="AQ18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR18" s="6" t="inlineStr"/>
+      <c r="AS18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT18" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP17"/>
+  <dimension ref="A1:AR16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15618,19 +14254,21 @@
     <col width="40" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="40" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE6 — 디자인·출력 · 솔벤 플로터·재단기 (원공고)</t>
+          <t>CASE5 — 친환경 벽지 · 라텍스 프린터 + 자동견적 (추가공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 7쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 6쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
         </is>
       </c>
     </row>
@@ -15864,26 +14502,37 @@
           <t>27회차 메모</t>
         </is>
       </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 결과
+2026-09-28 23:56</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C6-01</t>
+          <t>C5-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>과제 생성</t>
+          <t>지연·다음 예정</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>과제(원공고), H/W 공급사 기관</t>
+          <t>추가공고 과제, 1단계 T-3, 2단계 T+4</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>카드 «다음 … 1차 방문 D+3», «지연 1»</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -15891,11 +14540,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>연매출 2억원 이상</t>
-        </is>
-      </c>
+      <c r="F5" s="6" t="inlineStr"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -16004,26 +14649,32 @@
         </is>
       </c>
       <c r="AP5" s="6" t="inlineStr"/>
+      <c r="AQ5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C6-02</t>
+          <t>C5-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>오늘 탭</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>VG3-640 / RET-2002 / QT-AI BASIC(QT-AI 공급사, LITE 표기 메모)</t>
+          <t>«오늘» 탭</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>기한 경과에 1단계, 7일 안의 방문에 2단계</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -16031,11 +14682,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>품명 BASIC·사양 LITE형 불일치</t>
-        </is>
-      </c>
+      <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -16144,26 +14791,32 @@
         </is>
       </c>
       <c r="AP6" s="6" t="inlineStr"/>
+      <c r="AQ6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C6-03</t>
+          <t>C5-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>공급사 장비</t>
+          <t>완료 누락 알림</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>QT-AI 공급사 기관 상세</t>
+          <t>1단계 산출물 미체크로 완료</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>«공급 장비»에 QT-AI 자동견적(BASIC)</t>
+          <t>알림에 «현장진단표, 1차 방문 확인 서명», 상태 «완료» 유지</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -16280,26 +14933,32 @@
         </is>
       </c>
       <c r="AP7" s="6" t="inlineStr"/>
+      <c r="AQ7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C6-04</t>
+          <t>C5-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>자산</t>
+          <t>알림 줄어듦</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>3건</t>
+          <t>현장진단표 체크 → 나머지 체크</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>알림 1개로 줄고, 다 체크하면 사라짐</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -16416,26 +15075,32 @@
         </is>
       </c>
       <c r="AP8" s="6" t="inlineStr"/>
+      <c r="AQ8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C6-05</t>
+          <t>C5-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>장비 필터</t>
+          <t>서류 미수집</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>장비 탭 S/W 칩 + 검색 «QT-AI»</t>
+          <t>체크 1개 해제 → «오늘»</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>QT-AI BASIC만</t>
+          <t>서명·서류 미수집에 1단계</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -16552,26 +15217,32 @@
         </is>
       </c>
       <c r="AP9" s="6" t="inlineStr"/>
+      <c r="AQ9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C6-06</t>
+          <t>C5-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>통합 검색</t>
+          <t>카톡 수동 기록</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>상단 검색 «VG3» → 결과 클릭</t>
+          <t>수행일지 송부 → 카톡 보냄 기록</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>장비 상세, 도입된 자산에 과제</t>
+          <t>«카톡으로 보냄을 … 기록했습니다(수동 기록)», 버튼 «기록됨» 비활성</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -16688,26 +15359,32 @@
         </is>
       </c>
       <c r="AP10" s="6" t="inlineStr"/>
+      <c r="AQ10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C6-07</t>
+          <t>C5-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>S/W 한도</t>
+          <t>기록자</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>42,383,000÷9=4,709,222 &lt; 6,000,000 → 과제 상세 확인 + 메모</t>
+          <t>«활동» 탭</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>H/W 42,383,000원, 경고 «1,290,778원 초과»</t>
+          <t>«카톡 · 수동», 기록자 «시험자»</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -16824,26 +15501,32 @@
         </is>
       </c>
       <c r="AP11" s="6" t="inlineStr"/>
+      <c r="AQ11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C6-08</t>
+          <t>C5-08</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>장비 삭제 거부</t>
+          <t>메모 작성자</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>VG3-640 삭제</t>
+          <t>1단계 메모</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>«자산 1건에 쓰이고 있어 삭제할 수 없습니다»</t>
+          <t>머리 «… · 시험자», 한국 시간</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -16851,7 +15534,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>KPI 설정 필요</t>
+        </is>
+      </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -16960,26 +15647,32 @@
         </is>
       </c>
       <c r="AP12" s="6" t="inlineStr"/>
+      <c r="AQ12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C6-09</t>
+          <t>C5-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>과제 삭제 안전장치</t>
+          <t>포함 품목</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>과제 «삭제» 1회 후 4초</t>
+          <t>LATEX 730 / CNYX RIP(단가 비움) / QT-AI LITE 5,286,000</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>«삭제 확인» → «삭제»로 복귀</t>
+          <t>RIP 단가 «—»</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -16987,7 +15680,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>RIP «포함», S/W 할인 −714,000</t>
+        </is>
+      </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -17096,26 +15793,32 @@
         </is>
       </c>
       <c r="AP13" s="6" t="inlineStr"/>
+      <c r="AQ13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C6-10</t>
+          <t>C5-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>과제 삭제</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>«삭제» 두 번</t>
+          <t>3건 등록 → 과제 상세 견적 합계</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>과제 삭제, 자산 동반 삭제(0건), 장비 3종 남음</t>
+          <t>H/W 37,000,000원, «단가 없는 장비 1건 제외(CNYX RIP)», 경고 «1,174,889원 초과»</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -17232,26 +15935,32 @@
         </is>
       </c>
       <c r="AP14" s="6" t="inlineStr"/>
+      <c r="AQ14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C6-11</t>
+          <t>C5-11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>장비 삭제</t>
+          <t>전체 백업</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>VG3-640 삭제</t>
+          <t>«전체 백업 (JSON)»</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>삭제됨</t>
+          <t>파일명·counts·notice «extra»·by id 포함, 이름 «시험자» 미포함</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -17368,26 +16077,32 @@
         </is>
       </c>
       <c r="AP15" s="6" t="inlineStr"/>
+      <c r="AQ15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C6-12</t>
+          <t>C5-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>기관 삭제 거부</t>
+          <t>정리</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>담당자 있는 기관 삭제</t>
+          <t>과제·CASE5 장비 삭제(QT-AI 공급사 유지)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>«소속 담당자 n명이 있어 삭제할 수 없습니다»</t>
+          <t>삭제 완료</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -17504,6 +16219,2040 @@
         </is>
       </c>
       <c r="AP16" s="6" t="inlineStr"/>
+      <c r="AQ16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR16" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AR17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="40" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="40" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="40" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="40" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="40" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="40" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="40" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="40" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>CASE6 — 디자인·출력 · 솔벤 플로터·재단기 (원공고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 7쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>조작</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>기대 결과</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>자동화 방식</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2회차 결과
+2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2회차 메모</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>3회차 결과
+2026-09-28 07:58</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>3회차 메모</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>4회차 결과
+2026-09-28 08:00</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>4회차 메모</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>5회차 결과
+2026-09-28 08:01</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>5회차 메모</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>6회차 결과
+2026-09-28 08:24</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>6회차 메모</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>7회차 결과
+2026-09-28 08:25</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>7회차 메모</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>10회차 결과
+2026-09-28 08:40</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>10회차 메모</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>11회차 결과
+2026-09-28 08:46</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>11회차 메모</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>13회차 결과
+2026-09-28 09:06</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>13회차 메모</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>14회차 결과
+2026-09-28 09:07</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>14회차 메모</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>15회차 결과
+2026-09-28 09:16</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>15회차 메모</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>17회차 결과
+2026-09-28 09:22</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>17회차 메모</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>18회차 결과
+2026-09-28 09:24</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>18회차 메모</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>21회차 결과
+2026-09-28 11:14</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>21회차 메모</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>22회차 결과
+2026-09-28 23:25</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>22회차 메모</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>23회차 결과
+2026-09-28 23:27</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>23회차 메모</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 결과
+2026-09-28 23:34</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 메모</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 결과
+2026-09-28 23:48</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 메모</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 결과
+2026-09-28 23:56</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>C6-01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>과제 생성</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>과제(원공고), H/W 공급사 기관</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>연매출 2억원 이상</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr"/>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr"/>
+      <c r="U5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr"/>
+      <c r="W5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="inlineStr"/>
+      <c r="Y5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z5" s="6" t="inlineStr"/>
+      <c r="AA5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB5" s="6" t="inlineStr"/>
+      <c r="AC5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD5" s="6" t="inlineStr"/>
+      <c r="AE5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF5" s="6" t="inlineStr"/>
+      <c r="AG5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH5" s="6" t="inlineStr"/>
+      <c r="AI5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ5" s="6" t="inlineStr"/>
+      <c r="AK5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL5" s="6" t="inlineStr"/>
+      <c r="AM5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN5" s="6" t="inlineStr"/>
+      <c r="AO5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP5" s="6" t="inlineStr"/>
+      <c r="AQ5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>C6-02</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>VG3-640 / RET-2002 / QT-AI BASIC(QT-AI 공급사, LITE 표기 메모)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>품명 BASIC·사양 LITE형 불일치</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr"/>
+      <c r="U6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr"/>
+      <c r="W6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X6" s="6" t="inlineStr"/>
+      <c r="Y6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="inlineStr"/>
+      <c r="AA6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB6" s="6" t="inlineStr"/>
+      <c r="AC6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD6" s="6" t="inlineStr"/>
+      <c r="AE6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF6" s="6" t="inlineStr"/>
+      <c r="AG6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH6" s="6" t="inlineStr"/>
+      <c r="AI6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ6" s="6" t="inlineStr"/>
+      <c r="AK6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL6" s="6" t="inlineStr"/>
+      <c r="AM6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN6" s="6" t="inlineStr"/>
+      <c r="AO6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP6" s="6" t="inlineStr"/>
+      <c r="AQ6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>C6-03</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>공급사 장비</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>QT-AI 공급사 기관 상세</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>«공급 장비»에 QT-AI 자동견적(BASIC)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr"/>
+      <c r="U7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr"/>
+      <c r="Y7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="inlineStr"/>
+      <c r="AA7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB7" s="6" t="inlineStr"/>
+      <c r="AC7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD7" s="6" t="inlineStr"/>
+      <c r="AE7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF7" s="6" t="inlineStr"/>
+      <c r="AG7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH7" s="6" t="inlineStr"/>
+      <c r="AI7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ7" s="6" t="inlineStr"/>
+      <c r="AK7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL7" s="6" t="inlineStr"/>
+      <c r="AM7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN7" s="6" t="inlineStr"/>
+      <c r="AO7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP7" s="6" t="inlineStr"/>
+      <c r="AQ7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>C6-04</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>3건</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X8" s="6" t="inlineStr"/>
+      <c r="Y8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z8" s="6" t="inlineStr"/>
+      <c r="AA8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB8" s="6" t="inlineStr"/>
+      <c r="AC8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD8" s="6" t="inlineStr"/>
+      <c r="AE8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF8" s="6" t="inlineStr"/>
+      <c r="AG8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH8" s="6" t="inlineStr"/>
+      <c r="AI8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ8" s="6" t="inlineStr"/>
+      <c r="AK8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL8" s="6" t="inlineStr"/>
+      <c r="AM8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN8" s="6" t="inlineStr"/>
+      <c r="AO8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP8" s="6" t="inlineStr"/>
+      <c r="AQ8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>C6-05</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>장비 필터</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>장비 탭 S/W 칩 + 검색 «QT-AI»</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>QT-AI BASIC만</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X9" s="6" t="inlineStr"/>
+      <c r="Y9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z9" s="6" t="inlineStr"/>
+      <c r="AA9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB9" s="6" t="inlineStr"/>
+      <c r="AC9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD9" s="6" t="inlineStr"/>
+      <c r="AE9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF9" s="6" t="inlineStr"/>
+      <c r="AG9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH9" s="6" t="inlineStr"/>
+      <c r="AI9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ9" s="6" t="inlineStr"/>
+      <c r="AK9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL9" s="6" t="inlineStr"/>
+      <c r="AM9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN9" s="6" t="inlineStr"/>
+      <c r="AO9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP9" s="6" t="inlineStr"/>
+      <c r="AQ9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>C6-06</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>통합 검색</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>상단 검색 «VG3» → 결과 클릭</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>장비 상세, 도입된 자산에 과제</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr"/>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr"/>
+      <c r="U10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X10" s="6" t="inlineStr"/>
+      <c r="Y10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z10" s="6" t="inlineStr"/>
+      <c r="AA10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB10" s="6" t="inlineStr"/>
+      <c r="AC10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD10" s="6" t="inlineStr"/>
+      <c r="AE10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF10" s="6" t="inlineStr"/>
+      <c r="AG10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH10" s="6" t="inlineStr"/>
+      <c r="AI10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ10" s="6" t="inlineStr"/>
+      <c r="AK10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL10" s="6" t="inlineStr"/>
+      <c r="AM10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN10" s="6" t="inlineStr"/>
+      <c r="AO10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP10" s="6" t="inlineStr"/>
+      <c r="AQ10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>C6-07</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>S/W 한도</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>42,383,000÷9=4,709,222 &lt; 6,000,000 → 과제 상세 확인 + 메모</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>H/W 42,383,000원, 경고 «1,290,778원 초과»</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr"/>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr"/>
+      <c r="U11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X11" s="6" t="inlineStr"/>
+      <c r="Y11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z11" s="6" t="inlineStr"/>
+      <c r="AA11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB11" s="6" t="inlineStr"/>
+      <c r="AC11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD11" s="6" t="inlineStr"/>
+      <c r="AE11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF11" s="6" t="inlineStr"/>
+      <c r="AG11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr"/>
+      <c r="AI11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ11" s="6" t="inlineStr"/>
+      <c r="AK11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL11" s="6" t="inlineStr"/>
+      <c r="AM11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN11" s="6" t="inlineStr"/>
+      <c r="AO11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP11" s="6" t="inlineStr"/>
+      <c r="AQ11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>C6-08</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>장비 삭제 거부</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>VG3-640 삭제</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>«자산 1건에 쓰이고 있어 삭제할 수 없습니다»</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr"/>
+      <c r="O12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr"/>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr"/>
+      <c r="U12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V12" s="6" t="inlineStr"/>
+      <c r="W12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X12" s="6" t="inlineStr"/>
+      <c r="Y12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z12" s="6" t="inlineStr"/>
+      <c r="AA12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB12" s="6" t="inlineStr"/>
+      <c r="AC12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD12" s="6" t="inlineStr"/>
+      <c r="AE12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF12" s="6" t="inlineStr"/>
+      <c r="AG12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr"/>
+      <c r="AI12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ12" s="6" t="inlineStr"/>
+      <c r="AK12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL12" s="6" t="inlineStr"/>
+      <c r="AM12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN12" s="6" t="inlineStr"/>
+      <c r="AO12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP12" s="6" t="inlineStr"/>
+      <c r="AQ12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>C6-09</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제 안전장치</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>과제 «삭제» 1회 후 4초</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>«삭제 확인» → «삭제»로 복귀</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr"/>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr"/>
+      <c r="U13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr"/>
+      <c r="W13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr"/>
+      <c r="Y13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z13" s="6" t="inlineStr"/>
+      <c r="AA13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB13" s="6" t="inlineStr"/>
+      <c r="AC13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD13" s="6" t="inlineStr"/>
+      <c r="AE13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF13" s="6" t="inlineStr"/>
+      <c r="AG13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr"/>
+      <c r="AI13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ13" s="6" t="inlineStr"/>
+      <c r="AK13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL13" s="6" t="inlineStr"/>
+      <c r="AM13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN13" s="6" t="inlineStr"/>
+      <c r="AO13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP13" s="6" t="inlineStr"/>
+      <c r="AQ13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>C6-10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>«삭제» 두 번</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제, 자산 동반 삭제(0건), 장비 3종 남음</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr"/>
+      <c r="U14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr"/>
+      <c r="W14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X14" s="6" t="inlineStr"/>
+      <c r="Y14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z14" s="6" t="inlineStr"/>
+      <c r="AA14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB14" s="6" t="inlineStr"/>
+      <c r="AC14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD14" s="6" t="inlineStr"/>
+      <c r="AE14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF14" s="6" t="inlineStr"/>
+      <c r="AG14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr"/>
+      <c r="AI14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ14" s="6" t="inlineStr"/>
+      <c r="AK14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL14" s="6" t="inlineStr"/>
+      <c r="AM14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN14" s="6" t="inlineStr"/>
+      <c r="AO14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP14" s="6" t="inlineStr"/>
+      <c r="AQ14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>C6-11</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>장비 삭제</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>VG3-640 삭제</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>삭제됨</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr"/>
+      <c r="U15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr"/>
+      <c r="W15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr"/>
+      <c r="Y15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z15" s="6" t="inlineStr"/>
+      <c r="AA15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB15" s="6" t="inlineStr"/>
+      <c r="AC15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD15" s="6" t="inlineStr"/>
+      <c r="AE15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF15" s="6" t="inlineStr"/>
+      <c r="AG15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr"/>
+      <c r="AI15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ15" s="6" t="inlineStr"/>
+      <c r="AK15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL15" s="6" t="inlineStr"/>
+      <c r="AM15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN15" s="6" t="inlineStr"/>
+      <c r="AO15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP15" s="6" t="inlineStr"/>
+      <c r="AQ15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>C6-12</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>기관 삭제 거부</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>담당자 있는 기관 삭제</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>«소속 담당자 n명이 있어 삭제할 수 없습니다»</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr"/>
+      <c r="U16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr"/>
+      <c r="W16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr"/>
+      <c r="Y16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z16" s="6" t="inlineStr"/>
+      <c r="AA16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB16" s="6" t="inlineStr"/>
+      <c r="AC16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD16" s="6" t="inlineStr"/>
+      <c r="AE16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF16" s="6" t="inlineStr"/>
+      <c r="AG16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH16" s="6" t="inlineStr"/>
+      <c r="AI16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ16" s="6" t="inlineStr"/>
+      <c r="AK16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL16" s="6" t="inlineStr"/>
+      <c r="AM16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN16" s="6" t="inlineStr"/>
+      <c r="AO16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP16" s="6" t="inlineStr"/>
+      <c r="AQ16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -17640,6 +18389,12 @@
         </is>
       </c>
       <c r="AP17" s="6" t="inlineStr"/>
+      <c r="AQ17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR17" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/doc/테스트/E2E_시나리오_CASE1-6.xlsx
+++ b/doc/테스트/E2E_시나리오_CASE1-6.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -610,16 +610,16 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:56</t>
+          <t>2026-09-29 00:03</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>c9a72f41a0</t>
+          <t>470dd8300a</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>28/0/0</t>
+          <t>29/0/0</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="J5" s="10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0</v>
@@ -665,16 +665,16 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:48</t>
+          <t>2026-09-28 23:56</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>084be90acd</t>
+          <t>c9a72f41a0</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>27/0/0</t>
+          <t>28/0/0</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="J6" s="10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0</v>
@@ -720,11 +720,11 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:47</t>
+          <t>2026-09-28 23:48</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -744,26 +744,26 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J7" s="10" t="n">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0</v>
@@ -775,50 +775,50 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:34</t>
+          <t>2026-09-28 23:47</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>09cbe67b2a</t>
+          <t>084be90acd</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>26/0/0</t>
+          <t>27/0/0</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0</v>
@@ -830,11 +830,11 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:33</t>
+          <t>2026-09-28 23:34</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -854,26 +854,26 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J9" s="10" t="n">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
@@ -885,50 +885,50 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:27</t>
+          <t>2026-09-28 23:33</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>0145ba81dd</t>
+          <t>09cbe67b2a</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>24/0/0</t>
+          <t>26/0/0</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="10" t="n">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
@@ -940,11 +940,11 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:25</t>
+          <t>2026-09-28 23:27</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -995,16 +995,16 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:14</t>
+          <t>2026-09-28 23:25</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>6c4132ffc2</t>
+          <t>0145ba81dd</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>22/0/0</t>
+          <t>24/0/0</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
@@ -1050,21 +1050,21 @@
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:13</t>
+          <t>2026-09-28 11:14</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>6d745d5356</t>
+          <t>6c4132ffc2</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1074,26 +1074,26 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J13" s="10" t="n">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
@@ -1105,16 +1105,16 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:11</t>
+          <t>2026-09-28 11:13</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>b65bfe6fe8</t>
+          <t>6d745d5356</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>20/2/0</t>
+          <t>22/0/0</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -1147,88 +1147,88 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J14" s="11" t="n">
-        <v>20</v>
+      <c r="J14" s="10" t="n">
+        <v>22</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>C2-19, C2-20</t>
-        </is>
-      </c>
+      <c r="M14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:24</t>
+          <t>2026-09-28 11:11</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>0ae6ece6c2</t>
+          <t>b65bfe6fe8</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>18/0/0</t>
+          <t>20/2/0</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>89</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>20</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>C2-19, C2-20</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:22</t>
+          <t>2026-09-28 09:24</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>f40fc41604</t>
+          <t>0ae6ece6c2</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -1274,11 +1274,11 @@
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:21</t>
+          <t>2026-09-28 09:22</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1298,26 +1298,26 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J17" s="10" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
@@ -1329,50 +1329,50 @@
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:16</t>
+          <t>2026-09-28 09:21</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>51a52339ab</t>
+          <t>f40fc41604</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>16/0/0</t>
+          <t>18/0/0</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="10" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
@@ -1384,16 +1384,16 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:07</t>
+          <t>2026-09-28 09:16</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>07a26890b5</t>
+          <t>51a52339ab</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -1439,11 +1439,11 @@
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:06</t>
+          <t>2026-09-28 09:07</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>16/1/0</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1481,24 +1481,20 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J20" s="11" t="n">
-        <v>86</v>
+      <c r="J20" s="10" t="n">
+        <v>87</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>C1-13</t>
-        </is>
-      </c>
+      <c r="M20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
@@ -1512,7 +1508,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16/1/0</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1522,81 +1518,85 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>16</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>86</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>C1-13</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:46</t>
+          <t>2026-09-28 09:06</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>b588bab9b3</t>
+          <t>07a26890b5</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>16/0/0</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" s="10" t="n">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
@@ -1608,16 +1608,16 @@
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:40</t>
+          <t>2026-09-28 08:46</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>d5213f9578</t>
+          <t>b588bab9b3</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -1659,19 +1659,15 @@
       <c r="L23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>사업계획서 체크포인트(C2-14) 추가 후 전체 통과</t>
-        </is>
-      </c>
+      <c r="M23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:39</t>
+          <t>2026-09-28 08:40</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -1681,61 +1677,61 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>13/1/0</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>13</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>C2-14</t>
+          <t>사업계획서 체크포인트(C2-14) 추가 후 전체 통과</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:26</t>
+          <t>2026-09-28 08:39</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>9b24f45ce5</t>
+          <t>d5213f9578</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -1745,19 +1741,19 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
+          <t>13/1/0</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>14/0/0</t>
-        </is>
-      </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -1768,24 +1764,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J25" s="10" t="n">
-        <v>14</v>
+      <c r="J25" s="11" t="n">
+        <v>13</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="6" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>C2-14</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:25</t>
+          <t>2026-09-28 08:26</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -1815,16 +1815,16 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="10" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0</v>
@@ -1836,21 +1836,21 @@
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:24</t>
+          <t>2026-09-28 08:25</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>22774ad88d</t>
+          <t>9b24f45ce5</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>16/1/0</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1878,38 +1878,34 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J27" s="11" t="n">
-        <v>83</v>
+      <c r="J27" s="10" t="n">
+        <v>84</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>C1-02</t>
-        </is>
-      </c>
+      <c r="M27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:01</t>
+          <t>2026-09-28 08:24</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>a6368b6542</t>
+          <t>22774ad88d</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>16/1/0</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1937,24 +1933,28 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J28" s="10" t="n">
-        <v>84</v>
+      <c r="J28" s="11" t="n">
+        <v>83</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="6" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>C1-02</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:00</t>
+          <t>2026-09-28 08:01</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -2001,24 +2001,20 @@
       <c r="L29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="6" t="inlineStr">
-        <is>
-          <t>보드 수정 반영(기동 코드 주석 위치) — 해시 변경</t>
-        </is>
-      </c>
+      <c r="M29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:58</t>
+          <t>2026-09-28 08:00</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>a59d40dd6c</t>
+          <t>a6368b6542</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -2060,15 +2056,19 @@
       <c r="L30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="6" t="inlineStr"/>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>보드 수정 반영(기동 코드 주석 위치) — 해시 변경</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:56</t>
+          <t>2026-09-28 07:58</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>11/2/0</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
@@ -2106,24 +2106,20 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J31" s="11" t="n">
-        <v>82</v>
+      <c r="J31" s="10" t="n">
+        <v>84</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="6" t="inlineStr">
-        <is>
-          <t>C2-09, C2-10 — 하네스 선택자 결함(보드 무관), 3회차에서 수정 확인</t>
-        </is>
-      </c>
+      <c r="M31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
@@ -2142,39 +2138,98 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/2/0</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v>17</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>82</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>C2-09, C2-10 — 하네스 선택자 결함(보드 무관), 3회차에서 수정 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>a59d40dd6c</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>17/0/0</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
         <is>
           <t>CASE1만 실행(하네스 점검)</t>
         </is>
@@ -2271,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT21"/>
+  <dimension ref="A1:AV21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2320,6 +2375,8 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="12" customWidth="1" min="45" max="45"/>
     <col width="40" customWidth="1" min="46" max="46"/>
+    <col width="12" customWidth="1" min="47" max="47"/>
+    <col width="40" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2588,6 +2645,17 @@
           <t>28회차 메모</t>
         </is>
       </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>29회차 결과
+2026-09-29 00:03</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>29회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2736,6 +2804,12 @@
         </is>
       </c>
       <c r="AT5" s="6" t="inlineStr"/>
+      <c r="AU5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2888,6 +2962,12 @@
         </is>
       </c>
       <c r="AT6" s="6" t="inlineStr"/>
+      <c r="AU6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -3040,6 +3120,12 @@
         </is>
       </c>
       <c r="AT7" s="6" t="inlineStr"/>
+      <c r="AU7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -3188,6 +3274,12 @@
         </is>
       </c>
       <c r="AT8" s="6" t="inlineStr"/>
+      <c r="AU8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -3336,6 +3428,12 @@
         </is>
       </c>
       <c r="AT9" s="6" t="inlineStr"/>
+      <c r="AU9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -3488,6 +3586,12 @@
         </is>
       </c>
       <c r="AT10" s="6" t="inlineStr"/>
+      <c r="AU10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -3636,6 +3740,12 @@
         </is>
       </c>
       <c r="AT11" s="6" t="inlineStr"/>
+      <c r="AU11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -3788,6 +3898,12 @@
         </is>
       </c>
       <c r="AT12" s="6" t="inlineStr"/>
+      <c r="AU12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -3936,6 +4052,12 @@
         </is>
       </c>
       <c r="AT13" s="6" t="inlineStr"/>
+      <c r="AU13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -4084,6 +4206,12 @@
         </is>
       </c>
       <c r="AT14" s="6" t="inlineStr"/>
+      <c r="AU14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -4232,6 +4360,12 @@
         </is>
       </c>
       <c r="AT15" s="6" t="inlineStr"/>
+      <c r="AU15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -4380,6 +4514,12 @@
         </is>
       </c>
       <c r="AT16" s="6" t="inlineStr"/>
+      <c r="AU16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -4536,6 +4676,12 @@
         </is>
       </c>
       <c r="AT17" s="6" t="inlineStr"/>
+      <c r="AU17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -4684,6 +4830,12 @@
         </is>
       </c>
       <c r="AT18" s="6" t="inlineStr"/>
+      <c r="AU18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -4832,6 +4984,12 @@
         </is>
       </c>
       <c r="AT19" s="6" t="inlineStr"/>
+      <c r="AU19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -4980,6 +5138,12 @@
         </is>
       </c>
       <c r="AT20" s="6" t="inlineStr"/>
+      <c r="AU20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -5128,6 +5292,12 @@
         </is>
       </c>
       <c r="AT21" s="6" t="inlineStr"/>
+      <c r="AU21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV21" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5140,7 +5310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF32"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5201,6 +5371,8 @@
     <col width="40" customWidth="1" min="56" max="56"/>
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="40" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="40" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5535,6 +5707,17 @@
           <t>28회차 메모</t>
         </is>
       </c>
+      <c r="BG4" s="3" t="inlineStr">
+        <is>
+          <t>29회차 결과
+2026-09-29 00:03</t>
+        </is>
+      </c>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>29회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -5723,6 +5906,12 @@
         </is>
       </c>
       <c r="BF5" s="6" t="inlineStr"/>
+      <c r="BG5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -5907,6 +6096,12 @@
         </is>
       </c>
       <c r="BF6" s="6" t="inlineStr"/>
+      <c r="BG6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -6091,6 +6286,12 @@
         </is>
       </c>
       <c r="BF7" s="6" t="inlineStr"/>
+      <c r="BG7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -6279,6 +6480,12 @@
         </is>
       </c>
       <c r="BF8" s="6" t="inlineStr"/>
+      <c r="BG8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -6463,6 +6670,12 @@
         </is>
       </c>
       <c r="BF9" s="6" t="inlineStr"/>
+      <c r="BG9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -6647,6 +6860,12 @@
         </is>
       </c>
       <c r="BF10" s="6" t="inlineStr"/>
+      <c r="BG10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -6831,6 +7050,12 @@
         </is>
       </c>
       <c r="BF11" s="6" t="inlineStr"/>
+      <c r="BG11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -7015,6 +7240,12 @@
         </is>
       </c>
       <c r="BF12" s="6" t="inlineStr"/>
+      <c r="BG12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -7203,6 +7434,12 @@
         </is>
       </c>
       <c r="BF13" s="6" t="inlineStr"/>
+      <c r="BG13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -7395,6 +7632,12 @@
         </is>
       </c>
       <c r="BF14" s="6" t="inlineStr"/>
+      <c r="BG14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -7579,6 +7822,12 @@
         </is>
       </c>
       <c r="BF15" s="6" t="inlineStr"/>
+      <c r="BG15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -7763,6 +8012,12 @@
         </is>
       </c>
       <c r="BF16" s="6" t="inlineStr"/>
+      <c r="BG16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -7947,6 +8202,12 @@
         </is>
       </c>
       <c r="BF17" s="6" t="inlineStr"/>
+      <c r="BG17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -8103,6 +8364,12 @@
         </is>
       </c>
       <c r="BF18" s="6" t="inlineStr"/>
+      <c r="BG18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8237,6 +8504,12 @@
         </is>
       </c>
       <c r="BF19" s="6" t="inlineStr"/>
+      <c r="BG19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -8371,6 +8644,12 @@
         </is>
       </c>
       <c r="BF20" s="6" t="inlineStr"/>
+      <c r="BG20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -8481,6 +8760,12 @@
         </is>
       </c>
       <c r="BF21" s="6" t="inlineStr"/>
+      <c r="BG21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -8591,6 +8876,12 @@
         </is>
       </c>
       <c r="BF22" s="6" t="inlineStr"/>
+      <c r="BG22" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -8687,6 +8978,12 @@
         </is>
       </c>
       <c r="BF23" s="6" t="inlineStr"/>
+      <c r="BG23" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -8783,6 +9080,12 @@
         </is>
       </c>
       <c r="BF24" s="6" t="inlineStr"/>
+      <c r="BG24" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -8875,6 +9178,12 @@
         </is>
       </c>
       <c r="BF25" s="6" t="inlineStr"/>
+      <c r="BG25" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -8967,6 +9276,12 @@
         </is>
       </c>
       <c r="BF26" s="6" t="inlineStr"/>
+      <c r="BG26" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -9036,6 +9351,12 @@
         </is>
       </c>
       <c r="BF27" s="6" t="inlineStr"/>
+      <c r="BG27" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -9110,6 +9431,12 @@
         </is>
       </c>
       <c r="BF28" s="6" t="inlineStr"/>
+      <c r="BG28" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -9172,6 +9499,12 @@
         </is>
       </c>
       <c r="BF29" s="6" t="inlineStr"/>
+      <c r="BG29" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -9234,6 +9567,12 @@
         </is>
       </c>
       <c r="BF30" s="6" t="inlineStr"/>
+      <c r="BG30" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -9284,6 +9623,12 @@
         </is>
       </c>
       <c r="BF31" s="6" t="inlineStr"/>
+      <c r="BG31" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -9311,13 +9656,56 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="BE32" s="10" t="inlineStr">
         <is>
           <t>통과</t>
         </is>
       </c>
       <c r="BF32" s="6" t="inlineStr"/>
+      <c r="BG32" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>C2-29</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>도우미 — 사진·Claude 불가 화면</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>목: 사진 불가 화면으로 새로고침 → 도우미 → Claude 불가 화면으로 새로고침 → 도우미 → 원래대로</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>두 경우 모두 버튼 보임. 사진 불가: 이유 안내·📎 숨김·텍스트 안내·보내기 가능. Claude 불가: 이유 안내·보내기 꺼짐</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>실측: claude.ai 웹은 사진 불가(2026-09-29)</t>
+        </is>
+      </c>
+      <c r="BG33" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="BH33" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9330,2469 +9718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="40" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="40" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="40" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="40" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="40" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
-    <col width="40" customWidth="1" min="38" max="38"/>
-    <col width="12" customWidth="1" min="39" max="39"/>
-    <col width="40" customWidth="1" min="40" max="40"/>
-    <col width="12" customWidth="1" min="41" max="41"/>
-    <col width="40" customWidth="1" min="42" max="42"/>
-    <col width="12" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>CASE3 — 골프 양말 · 봉조 자동화 편직기 (원공고)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 4쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>조작</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>기대 결과</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>자동화 방식</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>근거</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2회차 결과
-2026-09-28 07:56</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2회차 메모</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>3회차 결과
-2026-09-28 07:58</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>3회차 메모</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>4회차 결과
-2026-09-28 08:00</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>4회차 메모</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>5회차 결과
-2026-09-28 08:01</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>5회차 메모</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>6회차 결과
-2026-09-28 08:24</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>6회차 메모</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>7회차 결과
-2026-09-28 08:25</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>7회차 메모</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>10회차 결과
-2026-09-28 08:40</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>10회차 메모</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>11회차 결과
-2026-09-28 08:46</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>11회차 메모</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>13회차 결과
-2026-09-28 09:06</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>13회차 메모</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>14회차 결과
-2026-09-28 09:07</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>14회차 메모</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>15회차 결과
-2026-09-28 09:16</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>15회차 메모</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>17회차 결과
-2026-09-28 09:22</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>17회차 메모</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>18회차 결과
-2026-09-28 09:24</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>18회차 메모</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>21회차 결과
-2026-09-28 11:14</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>21회차 메모</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>22회차 결과
-2026-09-28 23:25</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>22회차 메모</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>23회차 결과
-2026-09-28 23:27</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>23회차 메모</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>25회차 결과
-2026-09-28 23:34</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>25회차 메모</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>27회차 결과
-2026-09-28 23:48</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>27회차 메모</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>28회차 결과
-2026-09-28 23:56</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>28회차 메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>C3-01</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>이사를 소공인 담당자로</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>기관 1곳에 대표·이사 등록, 과제 소공인 = 이사</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>상세 소공인 «[테스트] C3담당 이사»</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>실경영은 담당 이사</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr"/>
-      <c r="U5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V5" s="6" t="inlineStr"/>
-      <c r="W5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X5" s="6" t="inlineStr"/>
-      <c r="Y5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z5" s="6" t="inlineStr"/>
-      <c r="AA5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB5" s="6" t="inlineStr"/>
-      <c r="AC5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD5" s="6" t="inlineStr"/>
-      <c r="AE5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF5" s="6" t="inlineStr"/>
-      <c r="AG5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH5" s="6" t="inlineStr"/>
-      <c r="AI5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ5" s="6" t="inlineStr"/>
-      <c r="AK5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL5" s="6" t="inlineStr"/>
-      <c r="AM5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN5" s="6" t="inlineStr"/>
-      <c r="AO5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP5" s="6" t="inlineStr"/>
-      <c r="AQ5" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>C3-02</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>존칭</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>1단계 보내기 → 소공인 · 일정 조율</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>«[테스트] C3담당 이사님 안녕하세요.»(«이사 대표님» 아님)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr"/>
-      <c r="O6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T6" s="6" t="inlineStr"/>
-      <c r="U6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V6" s="6" t="inlineStr"/>
-      <c r="W6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X6" s="6" t="inlineStr"/>
-      <c r="Y6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z6" s="6" t="inlineStr"/>
-      <c r="AA6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB6" s="6" t="inlineStr"/>
-      <c r="AC6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD6" s="6" t="inlineStr"/>
-      <c r="AE6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF6" s="6" t="inlineStr"/>
-      <c r="AG6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH6" s="6" t="inlineStr"/>
-      <c r="AI6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ6" s="6" t="inlineStr"/>
-      <c r="AK6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL6" s="6" t="inlineStr"/>
-      <c r="AM6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN6" s="6" t="inlineStr"/>
-      <c r="AO6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP6" s="6" t="inlineStr"/>
-      <c r="AQ6" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>C3-03</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>마스터 반영</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>이사 전화 010-0000-3334로 수정</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>과제 스냅샷 전화 자동 반영</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr"/>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr"/>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr"/>
-      <c r="U7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V7" s="6" t="inlineStr"/>
-      <c r="W7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X7" s="6" t="inlineStr"/>
-      <c r="Y7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z7" s="6" t="inlineStr"/>
-      <c r="AA7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB7" s="6" t="inlineStr"/>
-      <c r="AC7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD7" s="6" t="inlineStr"/>
-      <c r="AE7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF7" s="6" t="inlineStr"/>
-      <c r="AG7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH7" s="6" t="inlineStr"/>
-      <c r="AI7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ7" s="6" t="inlineStr"/>
-      <c r="AK7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL7" s="6" t="inlineStr"/>
-      <c r="AM7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN7" s="6" t="inlineStr"/>
-      <c r="AO7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP7" s="6" t="inlineStr"/>
-      <c r="AQ7" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>C3-04</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>전화 검색</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>검색 «01000003334»</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>결과에 과제·담당자</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr"/>
-      <c r="O8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr"/>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T8" s="6" t="inlineStr"/>
-      <c r="U8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V8" s="6" t="inlineStr"/>
-      <c r="W8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X8" s="6" t="inlineStr"/>
-      <c r="Y8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z8" s="6" t="inlineStr"/>
-      <c r="AA8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB8" s="6" t="inlineStr"/>
-      <c r="AC8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD8" s="6" t="inlineStr"/>
-      <c r="AE8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF8" s="6" t="inlineStr"/>
-      <c r="AG8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH8" s="6" t="inlineStr"/>
-      <c r="AI8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ8" s="6" t="inlineStr"/>
-      <c r="AK8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL8" s="6" t="inlineStr"/>
-      <c r="AM8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN8" s="6" t="inlineStr"/>
-      <c r="AO8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP8" s="6" t="inlineStr"/>
-      <c r="AQ8" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>C3-05</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>검색 변형</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>«3334», «0000-3334», «0000 3334»</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>같은 결과</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr"/>
-      <c r="O9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr"/>
-      <c r="U9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V9" s="6" t="inlineStr"/>
-      <c r="W9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X9" s="6" t="inlineStr"/>
-      <c r="Y9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z9" s="6" t="inlineStr"/>
-      <c r="AA9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB9" s="6" t="inlineStr"/>
-      <c r="AC9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD9" s="6" t="inlineStr"/>
-      <c r="AE9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF9" s="6" t="inlineStr"/>
-      <c r="AG9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH9" s="6" t="inlineStr"/>
-      <c r="AI9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ9" s="6" t="inlineStr"/>
-      <c r="AK9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL9" s="6" t="inlineStr"/>
-      <c r="AM9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN9" s="6" t="inlineStr"/>
-      <c r="AO9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP9" s="6" t="inlineStr"/>
-      <c r="AQ9" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>C3-06</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>견적 오기</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>S/W 단가 «6,600,00» 입력 → 거부 확인 후 «6,000,000»으로 등록</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>«쉼표 자리가 맞지 않습니다» 오류로 저장 안 됨 → 6,000,000 저장</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>원문 합계 «6,600,00원»</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr"/>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr"/>
-      <c r="O10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T10" s="6" t="inlineStr"/>
-      <c r="U10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V10" s="6" t="inlineStr"/>
-      <c r="W10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X10" s="6" t="inlineStr"/>
-      <c r="Y10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z10" s="6" t="inlineStr"/>
-      <c r="AA10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB10" s="6" t="inlineStr"/>
-      <c r="AC10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD10" s="6" t="inlineStr"/>
-      <c r="AE10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF10" s="6" t="inlineStr"/>
-      <c r="AG10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH10" s="6" t="inlineStr"/>
-      <c r="AI10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ10" s="6" t="inlineStr"/>
-      <c r="AK10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL10" s="6" t="inlineStr"/>
-      <c r="AM10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN10" s="6" t="inlineStr"/>
-      <c r="AO10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP10" s="6" t="inlineStr"/>
-      <c r="AQ10" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>C3-07</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>편직기 2, S/W 1</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>«검토 중 · 2대»</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr"/>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T11" s="6" t="inlineStr"/>
-      <c r="U11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V11" s="6" t="inlineStr"/>
-      <c r="W11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X11" s="6" t="inlineStr"/>
-      <c r="Y11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z11" s="6" t="inlineStr"/>
-      <c r="AA11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB11" s="6" t="inlineStr"/>
-      <c r="AC11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD11" s="6" t="inlineStr"/>
-      <c r="AE11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF11" s="6" t="inlineStr"/>
-      <c r="AG11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH11" s="6" t="inlineStr"/>
-      <c r="AI11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL11" s="6" t="inlineStr"/>
-      <c r="AM11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN11" s="6" t="inlineStr"/>
-      <c r="AO11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP11" s="6" t="inlineStr"/>
-      <c r="AQ11" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>C3-08</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>납기 예정</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>6단계 예정일 T+30(입금 후 30일)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>카드 «다음 … 장비 공급 D-30»</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>납기 입금 후 30일 이내</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr"/>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr"/>
-      <c r="O12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr"/>
-      <c r="Q12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr"/>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T12" s="6" t="inlineStr"/>
-      <c r="U12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr"/>
-      <c r="W12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X12" s="6" t="inlineStr"/>
-      <c r="Y12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z12" s="6" t="inlineStr"/>
-      <c r="AA12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB12" s="6" t="inlineStr"/>
-      <c r="AC12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD12" s="6" t="inlineStr"/>
-      <c r="AE12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF12" s="6" t="inlineStr"/>
-      <c r="AG12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH12" s="6" t="inlineStr"/>
-      <c r="AI12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL12" s="6" t="inlineStr"/>
-      <c r="AM12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN12" s="6" t="inlineStr"/>
-      <c r="AO12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP12" s="6" t="inlineStr"/>
-      <c r="AQ12" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>C3-09</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>캘린더 등록</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>«일정» 탭 6단계 «등록»</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 1건, «등록됨», 활동 «캘린더 · 자동»</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr"/>
-      <c r="O13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr"/>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr"/>
-      <c r="U13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr"/>
-      <c r="W13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X13" s="6" t="inlineStr"/>
-      <c r="Y13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z13" s="6" t="inlineStr"/>
-      <c r="AA13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB13" s="6" t="inlineStr"/>
-      <c r="AC13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD13" s="6" t="inlineStr"/>
-      <c r="AE13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF13" s="6" t="inlineStr"/>
-      <c r="AG13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH13" s="6" t="inlineStr"/>
-      <c r="AI13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL13" s="6" t="inlineStr"/>
-      <c r="AM13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN13" s="6" t="inlineStr"/>
-      <c r="AO13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP13" s="6" t="inlineStr"/>
-      <c r="AQ13" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>C3-10</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 내용</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>목 이벤트 확인</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>제목 «[스마트제조] … · 6. 장비 공급», 종일, 시작 T+30·끝 T+31, Asia/Seoul</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>캘린더 앱 확인 대체</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr"/>
-      <c r="O14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr"/>
-      <c r="Q14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr"/>
-      <c r="U14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr"/>
-      <c r="W14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X14" s="6" t="inlineStr"/>
-      <c r="Y14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z14" s="6" t="inlineStr"/>
-      <c r="AA14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB14" s="6" t="inlineStr"/>
-      <c r="AC14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD14" s="6" t="inlineStr"/>
-      <c r="AE14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF14" s="6" t="inlineStr"/>
-      <c r="AG14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH14" s="6" t="inlineStr"/>
-      <c r="AI14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL14" s="6" t="inlineStr"/>
-      <c r="AM14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN14" s="6" t="inlineStr"/>
-      <c r="AO14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP14" s="6" t="inlineStr"/>
-      <c r="AQ14" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>C3-11</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>날짜 변경 감지</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>예정일 T+35 → «오늘» 캘린더 미등록</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>«날짜 변경 (캘린더 T+30)»</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr"/>
-      <c r="O15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr"/>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr"/>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr"/>
-      <c r="U15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr"/>
-      <c r="W15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X15" s="6" t="inlineStr"/>
-      <c r="Y15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z15" s="6" t="inlineStr"/>
-      <c r="AA15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB15" s="6" t="inlineStr"/>
-      <c r="AC15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD15" s="6" t="inlineStr"/>
-      <c r="AE15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF15" s="6" t="inlineStr"/>
-      <c r="AG15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH15" s="6" t="inlineStr"/>
-      <c r="AI15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL15" s="6" t="inlineStr"/>
-      <c r="AM15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN15" s="6" t="inlineStr"/>
-      <c r="AO15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP15" s="6" t="inlineStr"/>
-      <c r="AQ15" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>C3-12</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>날짜 수정</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>«일정» 탭 «날짜 수정»</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>이벤트 T+35, 활동 제목 «날짜 변경 T+30 → T+35», 미등록 목록에서 사라짐</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr"/>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr"/>
-      <c r="O16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr"/>
-      <c r="U16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr"/>
-      <c r="W16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X16" s="6" t="inlineStr"/>
-      <c r="Y16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z16" s="6" t="inlineStr"/>
-      <c r="AA16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB16" s="6" t="inlineStr"/>
-      <c r="AC16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD16" s="6" t="inlineStr"/>
-      <c r="AE16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF16" s="6" t="inlineStr"/>
-      <c r="AG16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH16" s="6" t="inlineStr"/>
-      <c r="AI16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL16" s="6" t="inlineStr"/>
-      <c r="AM16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN16" s="6" t="inlineStr"/>
-      <c r="AO16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP16" s="6" t="inlineStr"/>
-      <c r="AQ16" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>C3-13</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>메모 → 초안</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>2단계 메모 후 수행일지 2차 초안</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>활동요약에 «· (MM-DD) 원문»</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr"/>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr"/>
-      <c r="O17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr"/>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T17" s="6" t="inlineStr"/>
-      <c r="U17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr"/>
-      <c r="W17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X17" s="6" t="inlineStr"/>
-      <c r="Y17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z17" s="6" t="inlineStr"/>
-      <c r="AA17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB17" s="6" t="inlineStr"/>
-      <c r="AC17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD17" s="6" t="inlineStr"/>
-      <c r="AE17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF17" s="6" t="inlineStr"/>
-      <c r="AG17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH17" s="6" t="inlineStr"/>
-      <c r="AI17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL17" s="6" t="inlineStr"/>
-      <c r="AM17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN17" s="6" t="inlineStr"/>
-      <c r="AO17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP17" s="6" t="inlineStr"/>
-      <c r="AQ17" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>C3-14</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>서명란</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>2차 초안 서명란 확인</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>«신청인(대표) : [테스트] C3담당» — 이사 이름(질문 3)</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr"/>
-      <c r="O18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr"/>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T18" s="6" t="inlineStr"/>
-      <c r="U18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr"/>
-      <c r="W18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X18" s="6" t="inlineStr"/>
-      <c r="Y18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z18" s="6" t="inlineStr"/>
-      <c r="AA18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB18" s="6" t="inlineStr"/>
-      <c r="AC18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD18" s="6" t="inlineStr"/>
-      <c r="AE18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF18" s="6" t="inlineStr"/>
-      <c r="AG18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH18" s="6" t="inlineStr"/>
-      <c r="AI18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL18" s="6" t="inlineStr"/>
-      <c r="AM18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN18" s="6" t="inlineStr"/>
-      <c r="AO18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP18" s="6" t="inlineStr"/>
-      <c r="AQ18" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>C3-15</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>정리</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>과제 삭제</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>«구글 캘린더에 등록된 일정 1건은 지워지지 않았습니다» 안내, 이후 장비·담당자·기관 삭제</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr"/>
-      <c r="O19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr"/>
-      <c r="Q19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr"/>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="T19" s="6" t="inlineStr"/>
-      <c r="U19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr"/>
-      <c r="W19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="X19" s="6" t="inlineStr"/>
-      <c r="Y19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="Z19" s="6" t="inlineStr"/>
-      <c r="AA19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AB19" s="6" t="inlineStr"/>
-      <c r="AC19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AD19" s="6" t="inlineStr"/>
-      <c r="AE19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AF19" s="6" t="inlineStr"/>
-      <c r="AG19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AH19" s="6" t="inlineStr"/>
-      <c r="AI19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AL19" s="6" t="inlineStr"/>
-      <c r="AM19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AN19" s="6" t="inlineStr"/>
-      <c r="AO19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AP19" s="6" t="inlineStr"/>
-      <c r="AQ19" s="10" t="inlineStr">
-        <is>
-          <t>통과</t>
-        </is>
-      </c>
-      <c r="AR19" s="6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AT18"/>
+  <dimension ref="A1:AT19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11846,14 +9772,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE4 — 지르코니아 치과 보철 · CNC 밀링 (추가공고)</t>
+          <t>CASE3 — 골프 양말 · 봉조 자동화 편직기 (원공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 5쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 4쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
         </is>
       </c>
     </row>
@@ -11957,178 +9883,178 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>8회차 결과
-2026-09-28 08:26</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>8회차 메모</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
           <t>10회차 결과
 2026-09-28 08:40</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>10회차 메모</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>11회차 결과
 2026-09-28 08:46</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>11회차 메모</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>13회차 결과
 2026-09-28 09:06</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>13회차 메모</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>14회차 결과
 2026-09-28 09:07</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>14회차 메모</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>15회차 결과
 2026-09-28 09:16</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>15회차 메모</t>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>17회차 결과
 2026-09-28 09:22</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>17회차 메모</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>18회차 결과
 2026-09-28 09:24</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>18회차 메모</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>21회차 결과
 2026-09-28 11:14</t>
         </is>
       </c>
-      <c r="AJ4" s="3" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>21회차 메모</t>
         </is>
       </c>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>22회차 결과
 2026-09-28 23:25</t>
         </is>
       </c>
-      <c r="AL4" s="3" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr">
         <is>
           <t>22회차 메모</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <t>23회차 결과
 2026-09-28 23:27</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>23회차 메모</t>
         </is>
       </c>
-      <c r="AO4" s="3" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>25회차 결과
 2026-09-28 23:34</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
+      <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>25회차 메모</t>
         </is>
       </c>
-      <c r="AQ4" s="3" t="inlineStr">
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>27회차 결과
 2026-09-28 23:48</t>
         </is>
       </c>
-      <c r="AR4" s="3" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr">
         <is>
           <t>27회차 메모</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
+      <c r="AQ4" s="3" t="inlineStr">
         <is>
           <t>28회차 결과
 2026-09-28 23:56</t>
         </is>
       </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 메모</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>29회차 결과
+2026-09-29 00:03</t>
+        </is>
+      </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>28회차 메모</t>
+          <t>29회차 메모</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C4-01</t>
+          <t>C3-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>공고 미지정</t>
+          <t>이사를 소공인 담당자로</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>공고 구분 비우고 과제 생성</t>
+          <t>기관 1곳에 대표·이사 등록, 과제 소공인 = 이사</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>카드 «공고 미확인», 상세 경고 문구</t>
+          <t>상세 소공인 «[테스트] C3담당 이사»</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -12136,7 +10062,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>실경영은 담당 이사</t>
+        </is>
+      </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -12261,22 +10191,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C4-02</t>
+          <t>C3-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>미확인 필터</t>
+          <t>존칭</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>공고 필터 = 공고 미확인</t>
+          <t>1단계 보내기 → 소공인 · 일정 조율</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>이 과제 보임</t>
+          <t>«[테스트] C3담당 이사님 안녕하세요.»(«이사 대표님» 아님)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -12409,22 +10339,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C4-03</t>
+          <t>C3-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>추가공고 지정</t>
+          <t>마스터 반영</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>상세 공고 구분 = 추가공고</t>
+          <t>이사 전화 010-0000-3334로 수정</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>배지 «추가공고», 원공고 필터에서 숨김, CSV 공고 열 «추가공고»</t>
+          <t>과제 스냅샷 전화 자동 반영</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -12432,11 +10362,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>연매출 2억원 미만</t>
-        </is>
-      </c>
+      <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -12561,34 +10487,30 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C4-04</t>
+          <t>C3-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 화면</t>
+          <t>전화 검색</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>390×844 에뮬레이션</t>
+          <t>검색 «01000003334»</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>하단 탭바(더보기 보임, 기관 탭 숨김), 가로 넘침 없음, 범례 숨김</t>
+          <t>결과에 과제·담당자</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>실기기 대체</t>
-        </is>
-      </c>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -12713,27 +10635,27 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C4-05</t>
+          <t>C3-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 진단 입력</t>
+          <t>검색 변형</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>1차 진단 5칸 입력, 칸 이동은 탭 한 번</t>
+          <t>«3334», «0000-3334», «0000 3334»</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>입력칸 16px, 다음 칸으로 포커스 이동, 값 저장</t>
+          <t>같은 결과</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -12861,32 +10783,32 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C4-06</t>
+          <t>C3-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>입력 중 재그리기</t>
+          <t>견적 오기</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>입력 중 스냅샷 강제 발행</t>
+          <t>S/W 단가 «6,600,00» 입력 → 거부 확인 후 «6,000,000»으로 등록</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>입력 중인 글자 유지</t>
+          <t>«쉼표 자리가 맞지 않습니다» 오류로 저장 안 됨 → 6,000,000 저장</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>다른 기기 수정 대체</t>
+          <t>원문 합계 «6,600,00원»</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -13013,22 +10935,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C4-07</t>
+          <t>C3-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>2차 진단 입력</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>②·③·기록 수준 입력</t>
+          <t>편직기 2, S/W 1</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>«검토 중 · 2대»</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -13161,22 +11083,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C4-08</t>
+          <t>C3-08</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1차 초안 반영</t>
+          <t>납기 예정</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>1단계 초안</t>
+          <t>6단계 예정일 T+30(입금 후 30일)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>입력 5칸 원문, ⑤⑥⑦ «미확인 — …»</t>
+          <t>카드 «다음 … 장비 공급 D-30»</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -13184,7 +11106,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>납기 입금 후 30일 이내</t>
+        </is>
+      </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -13309,27 +11235,27 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C4-09</t>
+          <t>C3-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2·3차 초안</t>
+          <t>캘린더 등록</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>2·7단계 초안</t>
+          <t>«일정» 탭 6단계 «등록»</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>2차 ③ 원문, 3차 향후 사후관리 «미확인 — …»</t>
+          <t>이벤트 1건, «등록됨», 활동 «캘린더 · 자동»</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
@@ -13457,32 +11383,32 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C4-10</t>
+          <t>C3-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>수치 비생성</t>
+          <t>이벤트 내용</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>초안 숫자 대조</t>
+          <t>목 이벤트 확인</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>6개·10개 외 수치(%, 증가율) 없음</t>
+          <t>제목 «[스마트제조] … · 6. 장비 공급», 종일, 시작 T+30·끝 T+31, Asia/Seoul</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>하루 6개 → 10개</t>
+          <t>캘린더 앱 확인 대체</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -13609,22 +11535,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C4-11</t>
+          <t>C3-11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>결과보고서 초안</t>
+          <t>날짜 변경 감지</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>8단계 초안</t>
+          <t>예정일 T+35 → «오늘» 캘린더 미등록</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>3. KPI에 1차 ②·④·2차 ② 진단 줄, 5.에 기록 방식 줄, 초안 표시</t>
+          <t>«날짜 변경 (캘린더 T+30)»</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -13757,27 +11683,27 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C4-12</t>
+          <t>C3-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>장비·자산 → 초안</t>
+          <t>날짜 수정</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>덴탈 CNC밀링기·Dentalsoft 등록, 자산 각 1 → 3차·결과보고서 초안</t>
+          <t>«일정» 탭 «날짜 수정»</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>3차 «④ 도입 장비»·결과보고서 4에 «[H/W] 덴탈 CNC밀링기 마닉스 5SA × 1대 (검토 중)»·«[S/W] Dentalsoft × 1식 (검토 중)», 금액 없음</t>
+          <t>이벤트 T+35, 활동 제목 «날짜 변경 T+30 → T+35», 미등록 목록에서 사라짐</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
@@ -13905,27 +11831,27 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>C4-13</t>
+          <t>C3-13</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>휴대폰 더보기</t>
+          <t>메모 → 초안</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>더보기 → 자산</t>
+          <t>2단계 메모 후 수행일지 2차 초안</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>메뉴 열림, 버튼 라벨 «자산 ▴», 자산 목록</t>
+          <t>활동요약에 «· (MM-DD) 원문»</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>목 대체</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
@@ -14053,22 +11979,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>C4-14</t>
+          <t>C3-14</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>정리</t>
+          <t>서명란</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>과제·장비·담당자·기관 삭제</t>
+          <t>2차 초안 서명란 확인</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>삭제 완료</t>
+          <t>«신청인(대표) : [테스트] C3담당» — 이사 이름(질문 3)</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -14197,19 +12123,167 @@
         </is>
       </c>
       <c r="AT18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>C3-15</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>정리</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>«구글 캘린더에 등록된 일정 1건은 지워지지 않았습니다» 안내, 이후 장비·담당자·기관 삭제</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr"/>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr"/>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr"/>
+      <c r="U19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr"/>
+      <c r="W19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X19" s="6" t="inlineStr"/>
+      <c r="Y19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z19" s="6" t="inlineStr"/>
+      <c r="AA19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB19" s="6" t="inlineStr"/>
+      <c r="AC19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD19" s="6" t="inlineStr"/>
+      <c r="AE19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF19" s="6" t="inlineStr"/>
+      <c r="AG19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr"/>
+      <c r="AI19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ19" s="6" t="inlineStr"/>
+      <c r="AK19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL19" s="6" t="inlineStr"/>
+      <c r="AM19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN19" s="6" t="inlineStr"/>
+      <c r="AO19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP19" s="6" t="inlineStr"/>
+      <c r="AQ19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR19" s="6" t="inlineStr"/>
+      <c r="AS19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT19" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR16"/>
+  <dimension ref="A1:AV18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14256,19 +12330,23 @@
     <col width="40" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="40" customWidth="1" min="46" max="46"/>
+    <col width="12" customWidth="1" min="47" max="47"/>
+    <col width="40" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE5 — 친환경 벽지 · 라텍스 프린터 + 자동견적 (추가공고)</t>
+          <t>CASE4 — 지르코니아 치과 보철 · CNC 밀링 (추가공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 6쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 5쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
         </is>
       </c>
     </row>
@@ -14372,167 +12450,189 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
+          <t>8회차 결과
+2026-09-28 08:26</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>8회차 메모</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
           <t>10회차 결과
 2026-09-28 08:40</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>10회차 메모</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>11회차 결과
 2026-09-28 08:46</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>11회차 메모</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>13회차 결과
 2026-09-28 09:06</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>13회차 메모</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>14회차 결과
 2026-09-28 09:07</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>14회차 메모</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>15회차 결과
 2026-09-28 09:16</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>15회차 메모</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>17회차 결과
 2026-09-28 09:22</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>17회차 메모</t>
         </is>
       </c>
-      <c r="AE4" s="3" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>18회차 결과
 2026-09-28 09:24</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>18회차 메모</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>21회차 결과
 2026-09-28 11:14</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr">
         <is>
           <t>21회차 메모</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
+      <c r="AK4" s="3" t="inlineStr">
         <is>
           <t>22회차 결과
 2026-09-28 23:25</t>
         </is>
       </c>
-      <c r="AJ4" s="3" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>22회차 메모</t>
         </is>
       </c>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>23회차 결과
 2026-09-28 23:27</t>
         </is>
       </c>
-      <c r="AL4" s="3" t="inlineStr">
+      <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>23회차 메모</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>25회차 결과
 2026-09-28 23:34</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr">
         <is>
           <t>25회차 메모</t>
         </is>
       </c>
-      <c r="AO4" s="3" t="inlineStr">
+      <c r="AQ4" s="3" t="inlineStr">
         <is>
           <t>27회차 결과
 2026-09-28 23:48</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
+      <c r="AR4" s="3" t="inlineStr">
         <is>
           <t>27회차 메모</t>
         </is>
       </c>
-      <c r="AQ4" s="3" t="inlineStr">
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>28회차 결과
 2026-09-28 23:56</t>
         </is>
       </c>
-      <c r="AR4" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
         <is>
           <t>28회차 메모</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>29회차 결과
+2026-09-29 00:03</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>29회차 메모</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C5-01</t>
+          <t>C4-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>지연·다음 예정</t>
+          <t>공고 미지정</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>추가공고 과제, 1단계 T-3, 2단계 T+4</t>
+          <t>공고 구분 비우고 과제 생성</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>카드 «다음 … 1차 방문 D+3», «지연 1»</t>
+          <t>카드 «공고 미확인», 상세 경고 문구</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -14655,26 +12755,38 @@
         </is>
       </c>
       <c r="AR5" s="6" t="inlineStr"/>
+      <c r="AS5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT5" s="6" t="inlineStr"/>
+      <c r="AU5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C5-02</t>
+          <t>C4-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>오늘 탭</t>
+          <t>미확인 필터</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>«오늘» 탭</t>
+          <t>공고 필터 = 공고 미확인</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>기한 경과에 1단계, 7일 안의 방문에 2단계</t>
+          <t>이 과제 보임</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -14797,26 +12909,38 @@
         </is>
       </c>
       <c r="AR6" s="6" t="inlineStr"/>
+      <c r="AS6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT6" s="6" t="inlineStr"/>
+      <c r="AU6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C5-03</t>
+          <t>C4-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>완료 누락 알림</t>
+          <t>추가공고 지정</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>1단계 산출물 미체크로 완료</t>
+          <t>상세 공고 구분 = 추가공고</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>알림에 «현장진단표, 1차 방문 확인 서명», 상태 «완료» 유지</t>
+          <t>배지 «추가공고», 원공고 필터에서 숨김, CSV 공고 열 «추가공고»</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -14824,7 +12948,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>연매출 2억원 미만</t>
+        </is>
+      </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -14939,34 +13067,50 @@
         </is>
       </c>
       <c r="AR7" s="6" t="inlineStr"/>
+      <c r="AS7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT7" s="6" t="inlineStr"/>
+      <c r="AU7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C5-04</t>
+          <t>C4-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>알림 줄어듦</t>
+          <t>휴대폰 화면</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>현장진단표 체크 → 나머지 체크</t>
+          <t>390×844 에뮬레이션</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>알림 1개로 줄고, 다 체크하면 사라짐</t>
+          <t>하단 탭바(더보기 보임, 기관 탭 숨김), 가로 넘침 없음, 범례 숨김</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>실기기 대체</t>
+        </is>
+      </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -15081,31 +13225,43 @@
         </is>
       </c>
       <c r="AR8" s="6" t="inlineStr"/>
+      <c r="AS8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT8" s="6" t="inlineStr"/>
+      <c r="AU8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C5-05</t>
+          <t>C4-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>서류 미수집</t>
+          <t>휴대폰 진단 입력</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>체크 1개 해제 → «오늘»</t>
+          <t>1차 진단 5칸 입력, 칸 이동은 탭 한 번</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>서명·서류 미수집에 1단계</t>
+          <t>입력칸 16px, 다음 칸으로 포커스 이동, 값 저장</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>목 대체</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -15223,34 +13379,50 @@
         </is>
       </c>
       <c r="AR9" s="6" t="inlineStr"/>
+      <c r="AS9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT9" s="6" t="inlineStr"/>
+      <c r="AU9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C5-06</t>
+          <t>C4-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>카톡 수동 기록</t>
+          <t>입력 중 재그리기</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>수행일지 송부 → 카톡 보냄 기록</t>
+          <t>입력 중 스냅샷 강제 발행</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>«카톡으로 보냄을 … 기록했습니다(수동 기록)», 버튼 «기록됨» 비활성</t>
+          <t>입력 중인 글자 유지</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>화면</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr"/>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>다른 기기 수정 대체</t>
+        </is>
+      </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -15365,26 +13537,38 @@
         </is>
       </c>
       <c r="AR10" s="6" t="inlineStr"/>
+      <c r="AS10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT10" s="6" t="inlineStr"/>
+      <c r="AU10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C5-07</t>
+          <t>C4-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>기록자</t>
+          <t>2차 진단 입력</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>«활동» 탭</t>
+          <t>②·③·기록 수준 입력</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>«카톡 · 수동», 기록자 «시험자»</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -15507,26 +13691,38 @@
         </is>
       </c>
       <c r="AR11" s="6" t="inlineStr"/>
+      <c r="AS11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT11" s="6" t="inlineStr"/>
+      <c r="AU11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C5-08</t>
+          <t>C4-08</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>메모 작성자</t>
+          <t>1차 초안 반영</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>1단계 메모</t>
+          <t>1단계 초안</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>머리 «… · 시험자», 한국 시간</t>
+          <t>입력 5칸 원문, ⑤⑥⑦ «미확인 — …»</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -15534,11 +13730,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>KPI 설정 필요</t>
-        </is>
-      </c>
+      <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -15653,26 +13845,38 @@
         </is>
       </c>
       <c r="AR12" s="6" t="inlineStr"/>
+      <c r="AS12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT12" s="6" t="inlineStr"/>
+      <c r="AU12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C5-09</t>
+          <t>C4-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>포함 품목</t>
+          <t>2·3차 초안</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>LATEX 730 / CNYX RIP(단가 비움) / QT-AI LITE 5,286,000</t>
+          <t>2·7단계 초안</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>RIP 단가 «—»</t>
+          <t>2차 ③ 원문, 3차 향후 사후관리 «미확인 — …»</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -15680,11 +13884,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>RIP «포함», S/W 할인 −714,000</t>
-        </is>
-      </c>
+      <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -15799,26 +13999,38 @@
         </is>
       </c>
       <c r="AR13" s="6" t="inlineStr"/>
+      <c r="AS13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT13" s="6" t="inlineStr"/>
+      <c r="AU13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C5-10</t>
+          <t>C4-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>자산</t>
+          <t>수치 비생성</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>3건 등록 → 과제 상세 견적 합계</t>
+          <t>초안 숫자 대조</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>H/W 37,000,000원, «단가 없는 장비 1건 제외(CNYX RIP)», 경고 «1,174,889원 초과»</t>
+          <t>6개·10개 외 수치(%, 증가율) 없음</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -15826,7 +14038,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>하루 6개 → 10개</t>
+        </is>
+      </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -15941,26 +14157,38 @@
         </is>
       </c>
       <c r="AR14" s="6" t="inlineStr"/>
+      <c r="AS14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT14" s="6" t="inlineStr"/>
+      <c r="AU14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C5-11</t>
+          <t>C4-11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>전체 백업</t>
+          <t>결과보고서 초안</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>«전체 백업 (JSON)»</t>
+          <t>8단계 초안</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>파일명·counts·notice «extra»·by id 포함, 이름 «시험자» 미포함</t>
+          <t>3. KPI에 1차 ②·④·2차 ② 진단 줄, 5.에 기록 방식 줄, 초안 표시</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -16083,26 +14311,38 @@
         </is>
       </c>
       <c r="AR15" s="6" t="inlineStr"/>
+      <c r="AS15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT15" s="6" t="inlineStr"/>
+      <c r="AU15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C5-12</t>
+          <t>C4-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>정리</t>
+          <t>장비·자산 → 초안</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>과제·CASE5 장비 삭제(QT-AI 공급사 유지)</t>
+          <t>덴탈 CNC밀링기·Dentalsoft 등록, 자산 각 1 → 3차·결과보고서 초안</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>삭제 완료</t>
+          <t>3차 «④ 도입 장비»·결과보고서 4에 «[H/W] 덴탈 CNC밀링기 마닉스 5SA × 1대 (검토 중)»·«[S/W] Dentalsoft × 1식 (검토 중)», 금액 없음</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -16225,19 +14465,339 @@
         </is>
       </c>
       <c r="AR16" s="6" t="inlineStr"/>
+      <c r="AS16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT16" s="6" t="inlineStr"/>
+      <c r="AU16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>C4-13</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>휴대폰 더보기</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>더보기 → 자산</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>메뉴 열림, 버튼 라벨 «자산 ▴», 자산 목록</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>목 대체</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr"/>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr"/>
+      <c r="U17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr"/>
+      <c r="W17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X17" s="6" t="inlineStr"/>
+      <c r="Y17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z17" s="6" t="inlineStr"/>
+      <c r="AA17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB17" s="6" t="inlineStr"/>
+      <c r="AC17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD17" s="6" t="inlineStr"/>
+      <c r="AE17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF17" s="6" t="inlineStr"/>
+      <c r="AG17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr"/>
+      <c r="AI17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ17" s="6" t="inlineStr"/>
+      <c r="AK17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL17" s="6" t="inlineStr"/>
+      <c r="AM17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN17" s="6" t="inlineStr"/>
+      <c r="AO17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP17" s="6" t="inlineStr"/>
+      <c r="AQ17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR17" s="6" t="inlineStr"/>
+      <c r="AS17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT17" s="6" t="inlineStr"/>
+      <c r="AU17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>C4-14</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>정리</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>과제·장비·담당자·기관 삭제</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>삭제 완료</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr"/>
+      <c r="U18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V18" s="6" t="inlineStr"/>
+      <c r="W18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X18" s="6" t="inlineStr"/>
+      <c r="Y18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z18" s="6" t="inlineStr"/>
+      <c r="AA18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB18" s="6" t="inlineStr"/>
+      <c r="AC18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD18" s="6" t="inlineStr"/>
+      <c r="AE18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF18" s="6" t="inlineStr"/>
+      <c r="AG18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH18" s="6" t="inlineStr"/>
+      <c r="AI18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ18" s="6" t="inlineStr"/>
+      <c r="AK18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL18" s="6" t="inlineStr"/>
+      <c r="AM18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN18" s="6" t="inlineStr"/>
+      <c r="AO18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP18" s="6" t="inlineStr"/>
+      <c r="AQ18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR18" s="6" t="inlineStr"/>
+      <c r="AS18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT18" s="6" t="inlineStr"/>
+      <c r="AU18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AV18" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR17"/>
+  <dimension ref="A1:AT16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -16284,19 +14844,21 @@
     <col width="40" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="40" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>CASE6 — 디자인·출력 · 솔벤 플로터·재단기 (원공고)</t>
+          <t>CASE5 — 친환경 벽지 · 라텍스 프린터 + 자동견적 (추가공고)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 7쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 6쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
         </is>
       </c>
     </row>
@@ -16541,26 +15103,37 @@
           <t>28회차 메모</t>
         </is>
       </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>29회차 결과
+2026-09-29 00:03</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>29회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>C6-01</t>
+          <t>C5-01</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>과제 생성</t>
+          <t>지연·다음 예정</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>과제(원공고), H/W 공급사 기관</t>
+          <t>추가공고 과제, 1단계 T-3, 2단계 T+4</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>카드 «다음 … 1차 방문 D+3», «지연 1»</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -16568,11 +15141,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>연매출 2억원 이상</t>
-        </is>
-      </c>
+      <c r="F5" s="6" t="inlineStr"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -16687,26 +15256,32 @@
         </is>
       </c>
       <c r="AR5" s="6" t="inlineStr"/>
+      <c r="AS5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C6-02</t>
+          <t>C5-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>오늘 탭</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>VG3-640 / RET-2002 / QT-AI BASIC(QT-AI 공급사, LITE 표기 메모)</t>
+          <t>«오늘» 탭</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>기한 경과에 1단계, 7일 안의 방문에 2단계</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -16714,11 +15289,7 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>품명 BASIC·사양 LITE형 불일치</t>
-        </is>
-      </c>
+      <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -16833,26 +15404,32 @@
         </is>
       </c>
       <c r="AR6" s="6" t="inlineStr"/>
+      <c r="AS6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C6-03</t>
+          <t>C5-03</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>공급사 장비</t>
+          <t>완료 누락 알림</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>QT-AI 공급사 기관 상세</t>
+          <t>1단계 산출물 미체크로 완료</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>«공급 장비»에 QT-AI 자동견적(BASIC)</t>
+          <t>알림에 «현장진단표, 1차 방문 확인 서명», 상태 «완료» 유지</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -16975,26 +15552,32 @@
         </is>
       </c>
       <c r="AR7" s="6" t="inlineStr"/>
+      <c r="AS7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>C6-04</t>
+          <t>C5-04</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>자산</t>
+          <t>알림 줄어듦</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>3건</t>
+          <t>현장진단표 체크 → 나머지 체크</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>알림 1개로 줄고, 다 체크하면 사라짐</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -17117,26 +15700,32 @@
         </is>
       </c>
       <c r="AR8" s="6" t="inlineStr"/>
+      <c r="AS8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C6-05</t>
+          <t>C5-05</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>장비 필터</t>
+          <t>서류 미수집</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>장비 탭 S/W 칩 + 검색 «QT-AI»</t>
+          <t>체크 1개 해제 → «오늘»</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>QT-AI BASIC만</t>
+          <t>서명·서류 미수집에 1단계</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -17259,26 +15848,32 @@
         </is>
       </c>
       <c r="AR9" s="6" t="inlineStr"/>
+      <c r="AS9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C6-06</t>
+          <t>C5-06</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>통합 검색</t>
+          <t>카톡 수동 기록</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>상단 검색 «VG3» → 결과 클릭</t>
+          <t>수행일지 송부 → 카톡 보냄 기록</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>장비 상세, 도입된 자산에 과제</t>
+          <t>«카톡으로 보냄을 … 기록했습니다(수동 기록)», 버튼 «기록됨» 비활성</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -17401,26 +15996,32 @@
         </is>
       </c>
       <c r="AR10" s="6" t="inlineStr"/>
+      <c r="AS10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>C6-07</t>
+          <t>C5-07</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>S/W 한도</t>
+          <t>기록자</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>42,383,000÷9=4,709,222 &lt; 6,000,000 → 과제 상세 확인 + 메모</t>
+          <t>«활동» 탭</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>H/W 42,383,000원, 경고 «1,290,778원 초과»</t>
+          <t>«카톡 · 수동», 기록자 «시험자»</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -17543,26 +16144,32 @@
         </is>
       </c>
       <c r="AR11" s="6" t="inlineStr"/>
+      <c r="AS11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C6-08</t>
+          <t>C5-08</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>장비 삭제 거부</t>
+          <t>메모 작성자</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>VG3-640 삭제</t>
+          <t>1단계 메모</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>«자산 1건에 쓰이고 있어 삭제할 수 없습니다»</t>
+          <t>머리 «… · 시험자», 한국 시간</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -17570,7 +16177,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>KPI 설정 필요</t>
+        </is>
+      </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -17685,26 +16296,32 @@
         </is>
       </c>
       <c r="AR12" s="6" t="inlineStr"/>
+      <c r="AS12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C6-09</t>
+          <t>C5-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>과제 삭제 안전장치</t>
+          <t>포함 품목</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>과제 «삭제» 1회 후 4초</t>
+          <t>LATEX 730 / CNYX RIP(단가 비움) / QT-AI LITE 5,286,000</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>«삭제 확인» → «삭제»로 복귀</t>
+          <t>RIP 단가 «—»</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -17712,7 +16329,11 @@
           <t>화면</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>RIP «포함», S/W 할인 −714,000</t>
+        </is>
+      </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>통과</t>
@@ -17827,26 +16448,32 @@
         </is>
       </c>
       <c r="AR13" s="6" t="inlineStr"/>
+      <c r="AS13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C6-10</t>
+          <t>C5-10</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>과제 삭제</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>«삭제» 두 번</t>
+          <t>3건 등록 → 과제 상세 견적 합계</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>과제 삭제, 자산 동반 삭제(0건), 장비 3종 남음</t>
+          <t>H/W 37,000,000원, «단가 없는 장비 1건 제외(CNYX RIP)», 경고 «1,174,889원 초과»</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -17969,26 +16596,32 @@
         </is>
       </c>
       <c r="AR14" s="6" t="inlineStr"/>
+      <c r="AS14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C6-11</t>
+          <t>C5-11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>장비 삭제</t>
+          <t>전체 백업</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>VG3-640 삭제</t>
+          <t>«전체 백업 (JSON)»</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>삭제됨</t>
+          <t>파일명·counts·notice «extra»·by id 포함, 이름 «시험자» 미포함</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -18111,26 +16744,32 @@
         </is>
       </c>
       <c r="AR15" s="6" t="inlineStr"/>
+      <c r="AS15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C6-12</t>
+          <t>C5-12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>기관 삭제 거부</t>
+          <t>정리</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>담당자 있는 기관 삭제</t>
+          <t>과제·CASE5 장비 삭제(QT-AI 공급사 유지)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>«소속 담당자 n명이 있어 삭제할 수 없습니다»</t>
+          <t>삭제 완료</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -18253,6 +16892,2125 @@
         </is>
       </c>
       <c r="AR16" s="6" t="inlineStr"/>
+      <c r="AS16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT16" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AT17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="40" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="40" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="40" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="40" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="40" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="40" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="40" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="40" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="40" customWidth="1" min="46" max="46"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>CASE6 — 디자인·출력 · 솔벤 플로터·재단기 (원공고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>근거: 4. 실습 교육 제공 사례.pdf PDF 7쪽 · 자동화 방식: 화면 = 보드 화면 조작 / 목 대체 = 사람·외부 서비스 단계를 목으로 대체 / 보드 밖 계산 = 보드가 하지 않는 계산을 테스트가 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>조작</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>기대 결과</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>자동화 방식</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2회차 결과
+2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2회차 메모</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>3회차 결과
+2026-09-28 07:58</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>3회차 메모</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>4회차 결과
+2026-09-28 08:00</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>4회차 메모</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>5회차 결과
+2026-09-28 08:01</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>5회차 메모</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>6회차 결과
+2026-09-28 08:24</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>6회차 메모</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>7회차 결과
+2026-09-28 08:25</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>7회차 메모</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>10회차 결과
+2026-09-28 08:40</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>10회차 메모</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>11회차 결과
+2026-09-28 08:46</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>11회차 메모</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>13회차 결과
+2026-09-28 09:06</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>13회차 메모</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>14회차 결과
+2026-09-28 09:07</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>14회차 메모</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>15회차 결과
+2026-09-28 09:16</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>15회차 메모</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>17회차 결과
+2026-09-28 09:22</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>17회차 메모</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>18회차 결과
+2026-09-28 09:24</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>18회차 메모</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>21회차 결과
+2026-09-28 11:14</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>21회차 메모</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>22회차 결과
+2026-09-28 23:25</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>22회차 메모</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>23회차 결과
+2026-09-28 23:27</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>23회차 메모</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 결과
+2026-09-28 23:34</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>25회차 메모</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 결과
+2026-09-28 23:48</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>27회차 메모</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 결과
+2026-09-28 23:56</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>28회차 메모</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>29회차 결과
+2026-09-29 00:03</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>29회차 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>C6-01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>과제 생성</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>과제(원공고), H/W 공급사 기관</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>연매출 2억원 이상</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr"/>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr"/>
+      <c r="U5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr"/>
+      <c r="W5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="inlineStr"/>
+      <c r="Y5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z5" s="6" t="inlineStr"/>
+      <c r="AA5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB5" s="6" t="inlineStr"/>
+      <c r="AC5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD5" s="6" t="inlineStr"/>
+      <c r="AE5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF5" s="6" t="inlineStr"/>
+      <c r="AG5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH5" s="6" t="inlineStr"/>
+      <c r="AI5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ5" s="6" t="inlineStr"/>
+      <c r="AK5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL5" s="6" t="inlineStr"/>
+      <c r="AM5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN5" s="6" t="inlineStr"/>
+      <c r="AO5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP5" s="6" t="inlineStr"/>
+      <c r="AQ5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR5" s="6" t="inlineStr"/>
+      <c r="AS5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>C6-02</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>VG3-640 / RET-2002 / QT-AI BASIC(QT-AI 공급사, LITE 표기 메모)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>품명 BASIC·사양 LITE형 불일치</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr"/>
+      <c r="U6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr"/>
+      <c r="W6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X6" s="6" t="inlineStr"/>
+      <c r="Y6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="inlineStr"/>
+      <c r="AA6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB6" s="6" t="inlineStr"/>
+      <c r="AC6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD6" s="6" t="inlineStr"/>
+      <c r="AE6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF6" s="6" t="inlineStr"/>
+      <c r="AG6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH6" s="6" t="inlineStr"/>
+      <c r="AI6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ6" s="6" t="inlineStr"/>
+      <c r="AK6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL6" s="6" t="inlineStr"/>
+      <c r="AM6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN6" s="6" t="inlineStr"/>
+      <c r="AO6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP6" s="6" t="inlineStr"/>
+      <c r="AQ6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR6" s="6" t="inlineStr"/>
+      <c r="AS6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>C6-03</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>공급사 장비</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>QT-AI 공급사 기관 상세</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>«공급 장비»에 QT-AI 자동견적(BASIC)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr"/>
+      <c r="U7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr"/>
+      <c r="Y7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="inlineStr"/>
+      <c r="AA7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB7" s="6" t="inlineStr"/>
+      <c r="AC7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD7" s="6" t="inlineStr"/>
+      <c r="AE7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF7" s="6" t="inlineStr"/>
+      <c r="AG7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH7" s="6" t="inlineStr"/>
+      <c r="AI7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ7" s="6" t="inlineStr"/>
+      <c r="AK7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL7" s="6" t="inlineStr"/>
+      <c r="AM7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN7" s="6" t="inlineStr"/>
+      <c r="AO7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP7" s="6" t="inlineStr"/>
+      <c r="AQ7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR7" s="6" t="inlineStr"/>
+      <c r="AS7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>C6-04</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>3건</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X8" s="6" t="inlineStr"/>
+      <c r="Y8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z8" s="6" t="inlineStr"/>
+      <c r="AA8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB8" s="6" t="inlineStr"/>
+      <c r="AC8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD8" s="6" t="inlineStr"/>
+      <c r="AE8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF8" s="6" t="inlineStr"/>
+      <c r="AG8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH8" s="6" t="inlineStr"/>
+      <c r="AI8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ8" s="6" t="inlineStr"/>
+      <c r="AK8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL8" s="6" t="inlineStr"/>
+      <c r="AM8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN8" s="6" t="inlineStr"/>
+      <c r="AO8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP8" s="6" t="inlineStr"/>
+      <c r="AQ8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR8" s="6" t="inlineStr"/>
+      <c r="AS8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>C6-05</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>장비 필터</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>장비 탭 S/W 칩 + 검색 «QT-AI»</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>QT-AI BASIC만</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X9" s="6" t="inlineStr"/>
+      <c r="Y9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z9" s="6" t="inlineStr"/>
+      <c r="AA9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB9" s="6" t="inlineStr"/>
+      <c r="AC9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD9" s="6" t="inlineStr"/>
+      <c r="AE9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF9" s="6" t="inlineStr"/>
+      <c r="AG9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH9" s="6" t="inlineStr"/>
+      <c r="AI9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ9" s="6" t="inlineStr"/>
+      <c r="AK9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL9" s="6" t="inlineStr"/>
+      <c r="AM9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN9" s="6" t="inlineStr"/>
+      <c r="AO9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP9" s="6" t="inlineStr"/>
+      <c r="AQ9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR9" s="6" t="inlineStr"/>
+      <c r="AS9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>C6-06</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>통합 검색</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>상단 검색 «VG3» → 결과 클릭</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>장비 상세, 도입된 자산에 과제</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr"/>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr"/>
+      <c r="U10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X10" s="6" t="inlineStr"/>
+      <c r="Y10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z10" s="6" t="inlineStr"/>
+      <c r="AA10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB10" s="6" t="inlineStr"/>
+      <c r="AC10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD10" s="6" t="inlineStr"/>
+      <c r="AE10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF10" s="6" t="inlineStr"/>
+      <c r="AG10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH10" s="6" t="inlineStr"/>
+      <c r="AI10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ10" s="6" t="inlineStr"/>
+      <c r="AK10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL10" s="6" t="inlineStr"/>
+      <c r="AM10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN10" s="6" t="inlineStr"/>
+      <c r="AO10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP10" s="6" t="inlineStr"/>
+      <c r="AQ10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR10" s="6" t="inlineStr"/>
+      <c r="AS10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>C6-07</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>S/W 한도</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>42,383,000÷9=4,709,222 &lt; 6,000,000 → 과제 상세 확인 + 메모</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>H/W 42,383,000원, 경고 «1,290,778원 초과»</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr"/>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr"/>
+      <c r="U11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X11" s="6" t="inlineStr"/>
+      <c r="Y11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z11" s="6" t="inlineStr"/>
+      <c r="AA11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB11" s="6" t="inlineStr"/>
+      <c r="AC11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD11" s="6" t="inlineStr"/>
+      <c r="AE11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF11" s="6" t="inlineStr"/>
+      <c r="AG11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr"/>
+      <c r="AI11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ11" s="6" t="inlineStr"/>
+      <c r="AK11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL11" s="6" t="inlineStr"/>
+      <c r="AM11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN11" s="6" t="inlineStr"/>
+      <c r="AO11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP11" s="6" t="inlineStr"/>
+      <c r="AQ11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR11" s="6" t="inlineStr"/>
+      <c r="AS11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>C6-08</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>장비 삭제 거부</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>VG3-640 삭제</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>«자산 1건에 쓰이고 있어 삭제할 수 없습니다»</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr"/>
+      <c r="O12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr"/>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr"/>
+      <c r="U12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V12" s="6" t="inlineStr"/>
+      <c r="W12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X12" s="6" t="inlineStr"/>
+      <c r="Y12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z12" s="6" t="inlineStr"/>
+      <c r="AA12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB12" s="6" t="inlineStr"/>
+      <c r="AC12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD12" s="6" t="inlineStr"/>
+      <c r="AE12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF12" s="6" t="inlineStr"/>
+      <c r="AG12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr"/>
+      <c r="AI12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ12" s="6" t="inlineStr"/>
+      <c r="AK12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL12" s="6" t="inlineStr"/>
+      <c r="AM12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN12" s="6" t="inlineStr"/>
+      <c r="AO12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP12" s="6" t="inlineStr"/>
+      <c r="AQ12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR12" s="6" t="inlineStr"/>
+      <c r="AS12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>C6-09</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제 안전장치</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>과제 «삭제» 1회 후 4초</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>«삭제 확인» → «삭제»로 복귀</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr"/>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr"/>
+      <c r="U13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr"/>
+      <c r="W13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr"/>
+      <c r="Y13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z13" s="6" t="inlineStr"/>
+      <c r="AA13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB13" s="6" t="inlineStr"/>
+      <c r="AC13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD13" s="6" t="inlineStr"/>
+      <c r="AE13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF13" s="6" t="inlineStr"/>
+      <c r="AG13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr"/>
+      <c r="AI13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ13" s="6" t="inlineStr"/>
+      <c r="AK13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL13" s="6" t="inlineStr"/>
+      <c r="AM13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN13" s="6" t="inlineStr"/>
+      <c r="AO13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP13" s="6" t="inlineStr"/>
+      <c r="AQ13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR13" s="6" t="inlineStr"/>
+      <c r="AS13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>C6-10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>«삭제» 두 번</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>과제 삭제, 자산 동반 삭제(0건), 장비 3종 남음</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr"/>
+      <c r="U14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr"/>
+      <c r="W14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X14" s="6" t="inlineStr"/>
+      <c r="Y14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z14" s="6" t="inlineStr"/>
+      <c r="AA14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB14" s="6" t="inlineStr"/>
+      <c r="AC14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD14" s="6" t="inlineStr"/>
+      <c r="AE14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF14" s="6" t="inlineStr"/>
+      <c r="AG14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr"/>
+      <c r="AI14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ14" s="6" t="inlineStr"/>
+      <c r="AK14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL14" s="6" t="inlineStr"/>
+      <c r="AM14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN14" s="6" t="inlineStr"/>
+      <c r="AO14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP14" s="6" t="inlineStr"/>
+      <c r="AQ14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR14" s="6" t="inlineStr"/>
+      <c r="AS14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>C6-11</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>장비 삭제</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>VG3-640 삭제</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>삭제됨</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr"/>
+      <c r="U15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr"/>
+      <c r="W15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr"/>
+      <c r="Y15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z15" s="6" t="inlineStr"/>
+      <c r="AA15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB15" s="6" t="inlineStr"/>
+      <c r="AC15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD15" s="6" t="inlineStr"/>
+      <c r="AE15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF15" s="6" t="inlineStr"/>
+      <c r="AG15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr"/>
+      <c r="AI15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ15" s="6" t="inlineStr"/>
+      <c r="AK15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL15" s="6" t="inlineStr"/>
+      <c r="AM15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN15" s="6" t="inlineStr"/>
+      <c r="AO15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP15" s="6" t="inlineStr"/>
+      <c r="AQ15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR15" s="6" t="inlineStr"/>
+      <c r="AS15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>C6-12</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>기관 삭제 거부</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>담당자 있는 기관 삭제</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>«소속 담당자 n명이 있어 삭제할 수 없습니다»</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>화면</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr"/>
+      <c r="U16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr"/>
+      <c r="W16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr"/>
+      <c r="Y16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="Z16" s="6" t="inlineStr"/>
+      <c r="AA16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AB16" s="6" t="inlineStr"/>
+      <c r="AC16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AD16" s="6" t="inlineStr"/>
+      <c r="AE16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AF16" s="6" t="inlineStr"/>
+      <c r="AG16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AH16" s="6" t="inlineStr"/>
+      <c r="AI16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AJ16" s="6" t="inlineStr"/>
+      <c r="AK16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AL16" s="6" t="inlineStr"/>
+      <c r="AM16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AN16" s="6" t="inlineStr"/>
+      <c r="AO16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AP16" s="6" t="inlineStr"/>
+      <c r="AQ16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AR16" s="6" t="inlineStr"/>
+      <c r="AS16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -18395,6 +19153,12 @@
         </is>
       </c>
       <c r="AR17" s="6" t="inlineStr"/>
+      <c r="AS17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="AT17" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/doc/테스트/E2E_시나리오_CASE1-6.xlsx
+++ b/doc/테스트/E2E_시나리오_CASE1-6.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -610,21 +610,21 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 17:11</t>
+          <t>2026-09-29 17:46</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>65e1419e03</t>
+          <t>2205c6bc26</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -634,26 +634,26 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" s="10" t="n">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0</v>
@@ -665,16 +665,16 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 17:11</t>
+          <t>2026-09-29 17:16</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>65e1419e03</t>
+          <t>b993303acd</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -720,16 +720,16 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 09:16</t>
+          <t>2026-09-29 17:11</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>0fc9d8c7dd</t>
+          <t>65e1419e03</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>32/0/0</t>
+          <t>33/0/0</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="J7" s="10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0</v>
@@ -775,50 +775,50 @@
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:05</t>
+          <t>2026-09-29 17:11</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>0fc9d8c7dd</t>
+          <t>65e1419e03</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
+          <t>33/0/0</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J8" s="10" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0</v>
@@ -830,11 +830,11 @@
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:03</t>
+          <t>2026-09-29 09:16</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>16/1/0</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>31/0/0</t>
+          <t>32/0/0</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -872,33 +872,29 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J9" s="11" t="n">
-        <v>101</v>
+      <c r="J9" s="10" t="n">
+        <v>103</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>C1-11</t>
-        </is>
-      </c>
+      <c r="M9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:41</t>
+          <t>2026-09-29 01:05</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>6f0de73a96</t>
+          <t>0fc9d8c7dd</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -908,31 +904,31 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>31/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="10" t="n">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
@@ -944,21 +940,21 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:38</t>
+          <t>2026-09-29 01:03</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>b21110bd13</t>
+          <t>0fc9d8c7dd</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>16/1/0</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -986,29 +982,33 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J11" s="10" t="n">
-        <v>102</v>
+      <c r="J11" s="11" t="n">
+        <v>101</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="6" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>C1-11</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:31</t>
+          <t>2026-09-29 00:41</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>b21110bd13</t>
+          <t>6f0de73a96</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>21/10/0</t>
+          <t>31/0/0</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>0/15/0</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>3/11/0</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -1038,31 +1038,27 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>12/1/0</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>65</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>102</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>C2-30, C2-31, C2-06, C2-07, C2-08, C2-09, C2-10, C2-11, C2-12, C2-13, C3-01, C3-02, C3-03, C3-04, C3-05, C3-06, C3-07, C3-08, C3-09, C3-10, C3-11, C3-12, C3-13, C3-14, C3-15, C4-01, C4-02, C4-03, C4-05, C4-06, C4-07, C4-08, C4-09, C4-11, C4-10, C4-12, C6-13</t>
-        </is>
-      </c>
+      <c r="M12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:28</t>
+          <t>2026-09-29 00:38</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -1072,56 +1068,52 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>22/9/0</t>
+          <t>31/0/0</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>22</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>102</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>C2-31, C2-06, C2-07, C2-08, C2-09, C2-10, C2-11, C2-12, C2-13</t>
-        </is>
-      </c>
+      <c r="M13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:26</t>
+          <t>2026-09-29 00:31</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1131,61 +1123,61 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>22/9/0</t>
+          <t>21/10/0</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0/15/0</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3/11/0</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/1/0</t>
         </is>
       </c>
       <c r="J14" s="11" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>C2-31, C2-06, C2-07, C2-08, C2-09, C2-10, C2-11, C2-12, C2-13</t>
+          <t>C2-30, C2-31, C2-06, C2-07, C2-08, C2-09, C2-10, C2-11, C2-12, C2-13, C3-01, C3-02, C3-03, C3-04, C3-05, C3-06, C3-07, C3-08, C3-09, C3-10, C3-11, C3-12, C3-13, C3-14, C3-15, C4-01, C4-02, C4-03, C4-05, C4-06, C4-07, C4-08, C4-09, C4-11, C4-10, C4-12, C6-13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:25</t>
+          <t>2026-09-29 00:28</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>d6c838ffc8</t>
+          <t>b21110bd13</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1195,7 +1187,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>29/2/0</t>
+          <t>22/9/0</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
@@ -1219,142 +1211,150 @@
         </is>
       </c>
       <c r="J15" s="11" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>C2-30, C2-31</t>
+          <t>C2-31, C2-06, C2-07, C2-08, C2-09, C2-10, C2-11, C2-12, C2-13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:03</t>
+          <t>2026-09-29 00:26</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>470dd8300a</t>
+          <t>b21110bd13</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>29/0/0</t>
+          <t>22/9/0</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>100</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>22</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>C2-31, C2-06, C2-07, C2-08, C2-09, C2-10, C2-11, C2-12, C2-13</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:56</t>
+          <t>2026-09-29 00:25</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>c9a72f41a0</t>
+          <t>d6c838ffc8</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>28/0/0</t>
+          <t>29/2/0</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>99</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>29</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>C2-30, C2-31</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:48</t>
+          <t>2026-09-29 00:03</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>084be90acd</t>
+          <t>470dd8300a</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>27/0/0</t>
+          <t>29/0/0</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="J18" s="10" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
@@ -1400,50 +1400,50 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:47</t>
+          <t>2026-09-28 23:56</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>084be90acd</t>
+          <t>c9a72f41a0</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>27/0/0</t>
+          <t>28/0/0</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J19" s="10" t="n">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
@@ -1455,16 +1455,16 @@
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:34</t>
+          <t>2026-09-28 23:48</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>09cbe67b2a</t>
+          <t>084be90acd</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>26/0/0</t>
+          <t>27/0/0</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="J20" s="10" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0</v>
@@ -1510,16 +1510,16 @@
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:33</t>
+          <t>2026-09-28 23:47</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>09cbe67b2a</t>
+          <t>084be90acd</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>26/0/0</t>
+          <t>27/0/0</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="J21" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
@@ -1565,16 +1565,16 @@
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:27</t>
+          <t>2026-09-28 23:34</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>0145ba81dd</t>
+          <t>09cbe67b2a</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>24/0/0</t>
+          <t>26/0/0</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="J22" s="10" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
@@ -1620,50 +1620,50 @@
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:25</t>
+          <t>2026-09-28 23:33</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>0145ba81dd</t>
+          <t>09cbe67b2a</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>24/0/0</t>
+          <t>26/0/0</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" s="10" t="n">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
@@ -1675,16 +1675,16 @@
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:14</t>
+          <t>2026-09-28 23:27</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>6c4132ffc2</t>
+          <t>0145ba81dd</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>22/0/0</t>
+          <t>24/0/0</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="J24" s="10" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>0</v>
@@ -1730,50 +1730,50 @@
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:13</t>
+          <t>2026-09-28 23:25</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>6d745d5356</t>
+          <t>0145ba81dd</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>22/0/0</t>
+          <t>24/0/0</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
@@ -1785,109 +1785,105 @@
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:11</t>
+          <t>2026-09-28 11:14</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>b65bfe6fe8</t>
+          <t>6c4132ffc2</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>20/2/0</t>
+          <t>22/0/0</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="n">
-        <v>20</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>93</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>C2-19, C2-20</t>
-        </is>
-      </c>
+      <c r="M26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:24</t>
+          <t>2026-09-28 11:13</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>0ae6ece6c2</t>
+          <t>6d745d5356</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>18/0/0</t>
+          <t>22/0/0</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="10" t="n">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
@@ -1899,76 +1895,80 @@
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:22</t>
+          <t>2026-09-28 11:11</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>f40fc41604</t>
+          <t>b65bfe6fe8</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>18/0/0</t>
+          <t>20/2/0</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>89</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>20</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="6" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>C2-19, C2-20</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:21</t>
+          <t>2026-09-28 09:24</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>f40fc41604</t>
+          <t>0ae6ece6c2</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -1978,26 +1978,26 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J29" s="10" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
@@ -2009,16 +2009,16 @@
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:16</t>
+          <t>2026-09-28 09:22</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>51a52339ab</t>
+          <t>f40fc41604</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>16/0/0</t>
+          <t>18/0/0</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="J30" s="10" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
@@ -2064,50 +2064,50 @@
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:07</t>
+          <t>2026-09-28 09:21</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>07a26890b5</t>
+          <t>f40fc41604</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>16/0/0</t>
+          <t>18/0/0</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J31" s="10" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0</v>
@@ -2119,21 +2119,21 @@
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:06</t>
+          <t>2026-09-28 09:16</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>07a26890b5</t>
+          <t>51a52339ab</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>16/1/0</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2161,28 +2161,24 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J32" s="11" t="n">
-        <v>86</v>
+      <c r="J32" s="10" t="n">
+        <v>87</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>C1-13</t>
-        </is>
-      </c>
+      <c r="M32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:06</t>
+          <t>2026-09-28 09:07</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -2192,7 +2188,7 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2202,26 +2198,26 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J33" s="10" t="n">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
@@ -2233,38 +2229,38 @@
     </row>
     <row r="34">
       <c r="A34" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:46</t>
+          <t>2026-09-28 09:06</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>b588bab9b3</t>
+          <t>07a26890b5</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>16/1/0</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
+          <t>16/0/0</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>15/0/0</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
           <t>14/0/0</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>15/0/0</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>14/0/0</t>
-        </is>
-      </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
           <t>12/0/0</t>
@@ -2275,63 +2271,67 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J34" s="10" t="n">
-        <v>85</v>
+      <c r="J34" s="11" t="n">
+        <v>86</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="6" t="inlineStr"/>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>C1-13</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:40</t>
+          <t>2026-09-28 09:06</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>d5213f9578</t>
+          <t>07a26890b5</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>16/0/0</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J35" s="10" t="n">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
@@ -2339,98 +2339,90 @@
       <c r="L35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>사업계획서 체크포인트(C2-14) 추가 후 전체 통과</t>
-        </is>
-      </c>
+      <c r="M35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:39</t>
+          <t>2026-09-28 08:46</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>d5213f9578</t>
+          <t>b588bab9b3</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>13/1/0</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="n">
-        <v>13</v>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>C2-14</t>
-        </is>
-      </c>
+      <c r="M36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:26</t>
+          <t>2026-09-28 08:40</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>9b24f45ce5</t>
+          <t>d5213f9578</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/0/0</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -2440,16 +2432,16 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J37" s="10" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>0</v>
@@ -2457,90 +2449,98 @@
       <c r="L37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M37" s="6" t="inlineStr"/>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>사업계획서 체크포인트(C2-14) 추가 후 전체 통과</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:25</t>
+          <t>2026-09-28 08:39</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>9b24f45ce5</t>
+          <t>d5213f9578</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>13/1/0</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>14/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="n">
-        <v>84</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>13</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M38" s="6" t="inlineStr"/>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>C2-14</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:24</t>
+          <t>2026-09-28 08:26</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>22774ad88d</t>
+          <t>9b24f45ce5</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>16/1/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -2550,41 +2550,37 @@
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>12/0/0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>13/0/0</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="n">
-        <v>83</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>14</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>C1-02</t>
-        </is>
-      </c>
+      <c r="M39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:01</t>
+          <t>2026-09-28 08:25</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>a6368b6542</t>
+          <t>9b24f45ce5</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -2630,21 +2626,21 @@
     </row>
     <row r="41">
       <c r="A41" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 08:00</t>
+          <t>2026-09-28 08:24</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>a6368b6542</t>
+          <t>22774ad88d</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>17/0/0</t>
+          <t>16/1/0</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -2672,33 +2668,33 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J41" s="10" t="n">
-        <v>84</v>
+      <c r="J41" s="11" t="n">
+        <v>83</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>보드 수정 반영(기동 코드 주석 위치) — 해시 변경</t>
+          <t>C1-02</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:58</t>
+          <t>2026-09-28 08:01</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>a59d40dd6c</t>
+          <t>a6368b6542</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -2744,16 +2740,16 @@
     </row>
     <row r="43">
       <c r="A43" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:56</t>
+          <t>2026-09-28 08:00</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>a59d40dd6c</t>
+          <t>a6368b6542</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -2763,7 +2759,7 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>11/2/0</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
@@ -2786,28 +2782,28 @@
           <t>13/0/0</t>
         </is>
       </c>
-      <c r="J43" s="11" t="n">
-        <v>82</v>
+      <c r="J43" s="10" t="n">
+        <v>84</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>C2-09, C2-10 — 하네스 선택자 결함(보드 무관), 3회차에서 수정 확인</t>
+          <t>보드 수정 반영(기동 코드 주석 위치) — 해시 변경</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 07:56</t>
+          <t>2026-09-28 07:58</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -2822,31 +2818,31 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/0/0</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14/0/0</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/0/0</t>
         </is>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13/0/0</t>
         </is>
       </c>
       <c r="J44" s="10" t="n">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>0</v>
@@ -2854,7 +2850,121 @@
       <c r="L44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M44" s="6" t="inlineStr">
+      <c r="M44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>a59d40dd6c</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>17/0/0</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>11/2/0</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>15/0/0</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>14/0/0</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>12/0/0</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>13/0/0</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>C2-09, C2-10 — 하네스 선택자 결함(보드 무관), 3회차에서 수정 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 07:56</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>a59d40dd6c</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>17/0/0</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
         <is>
           <t>CASE1만 실행(하네스 점검)</t>
         </is>
@@ -6743,7 +6853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB37"/>
+  <dimension ref="A1:CF37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6826,6 +6936,10 @@
     <col width="40" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="40" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="40" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="40" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7280,6 +7394,28 @@
           <t>40회차 메모</t>
         </is>
       </c>
+      <c r="CC4" s="3" t="inlineStr">
+        <is>
+          <t>41회차 결과
+2026-09-29 17:16</t>
+        </is>
+      </c>
+      <c r="CD4" s="3" t="inlineStr">
+        <is>
+          <t>41회차 메모</t>
+        </is>
+      </c>
+      <c r="CE4" s="3" t="inlineStr">
+        <is>
+          <t>42회차 결과
+2026-09-29 17:46</t>
+        </is>
+      </c>
+      <c r="CF4" s="3" t="inlineStr">
+        <is>
+          <t>42회차 메모</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -7534,6 +7670,18 @@
         </is>
       </c>
       <c r="CB5" s="6" t="inlineStr"/>
+      <c r="CC5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD5" s="6" t="inlineStr"/>
+      <c r="CE5" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -7784,6 +7932,18 @@
         </is>
       </c>
       <c r="CB6" s="6" t="inlineStr"/>
+      <c r="CC6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD6" s="6" t="inlineStr"/>
+      <c r="CE6" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -8034,6 +8194,18 @@
         </is>
       </c>
       <c r="CB7" s="6" t="inlineStr"/>
+      <c r="CC7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD7" s="6" t="inlineStr"/>
+      <c r="CE7" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -8288,6 +8460,18 @@
         </is>
       </c>
       <c r="CB8" s="6" t="inlineStr"/>
+      <c r="CC8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD8" s="6" t="inlineStr"/>
+      <c r="CE8" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -8538,6 +8722,18 @@
         </is>
       </c>
       <c r="CB9" s="6" t="inlineStr"/>
+      <c r="CC9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD9" s="6" t="inlineStr"/>
+      <c r="CE9" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -8800,6 +8996,18 @@
         </is>
       </c>
       <c r="CB10" s="6" t="inlineStr"/>
+      <c r="CC10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD10" s="6" t="inlineStr"/>
+      <c r="CE10" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -9062,6 +9270,18 @@
         </is>
       </c>
       <c r="CB11" s="6" t="inlineStr"/>
+      <c r="CC11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD11" s="6" t="inlineStr"/>
+      <c r="CE11" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -9324,6 +9544,18 @@
         </is>
       </c>
       <c r="CB12" s="6" t="inlineStr"/>
+      <c r="CC12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD12" s="6" t="inlineStr"/>
+      <c r="CE12" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -9590,6 +9822,18 @@
         </is>
       </c>
       <c r="CB13" s="6" t="inlineStr"/>
+      <c r="CC13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD13" s="6" t="inlineStr"/>
+      <c r="CE13" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -9860,6 +10104,18 @@
         </is>
       </c>
       <c r="CB14" s="6" t="inlineStr"/>
+      <c r="CC14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD14" s="6" t="inlineStr"/>
+      <c r="CE14" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -10122,6 +10378,18 @@
         </is>
       </c>
       <c r="CB15" s="6" t="inlineStr"/>
+      <c r="CC15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD15" s="6" t="inlineStr"/>
+      <c r="CE15" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -10384,6 +10652,18 @@
         </is>
       </c>
       <c r="CB16" s="6" t="inlineStr"/>
+      <c r="CC16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD16" s="6" t="inlineStr"/>
+      <c r="CE16" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -10646,6 +10926,18 @@
         </is>
       </c>
       <c r="CB17" s="6" t="inlineStr"/>
+      <c r="CC17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD17" s="6" t="inlineStr"/>
+      <c r="CE17" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -10868,6 +11160,18 @@
         </is>
       </c>
       <c r="CB18" s="6" t="inlineStr"/>
+      <c r="CC18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD18" s="6" t="inlineStr"/>
+      <c r="CE18" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -11068,6 +11372,18 @@
         </is>
       </c>
       <c r="CB19" s="6" t="inlineStr"/>
+      <c r="CC19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD19" s="6" t="inlineStr"/>
+      <c r="CE19" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -11268,6 +11584,18 @@
         </is>
       </c>
       <c r="CB20" s="6" t="inlineStr"/>
+      <c r="CC20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD20" s="6" t="inlineStr"/>
+      <c r="CE20" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -11444,6 +11772,18 @@
         </is>
       </c>
       <c r="CB21" s="6" t="inlineStr"/>
+      <c r="CC21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD21" s="6" t="inlineStr"/>
+      <c r="CE21" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -11620,6 +11960,18 @@
         </is>
       </c>
       <c r="CB22" s="6" t="inlineStr"/>
+      <c r="CC22" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD22" s="6" t="inlineStr"/>
+      <c r="CE22" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -11782,6 +12134,18 @@
         </is>
       </c>
       <c r="CB23" s="6" t="inlineStr"/>
+      <c r="CC23" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD23" s="6" t="inlineStr"/>
+      <c r="CE23" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -11944,6 +12308,18 @@
         </is>
       </c>
       <c r="CB24" s="6" t="inlineStr"/>
+      <c r="CC24" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD24" s="6" t="inlineStr"/>
+      <c r="CE24" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -12102,6 +12478,18 @@
         </is>
       </c>
       <c r="CB25" s="6" t="inlineStr"/>
+      <c r="CC25" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD25" s="6" t="inlineStr"/>
+      <c r="CE25" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -12260,6 +12648,18 @@
         </is>
       </c>
       <c r="CB26" s="6" t="inlineStr"/>
+      <c r="CC26" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD26" s="6" t="inlineStr"/>
+      <c r="CE26" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -12395,6 +12795,18 @@
         </is>
       </c>
       <c r="CB27" s="6" t="inlineStr"/>
+      <c r="CC27" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD27" s="6" t="inlineStr"/>
+      <c r="CE27" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -12535,6 +12947,18 @@
         </is>
       </c>
       <c r="CB28" s="6" t="inlineStr"/>
+      <c r="CC28" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD28" s="6" t="inlineStr"/>
+      <c r="CE28" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -12663,6 +13087,18 @@
         </is>
       </c>
       <c r="CB29" s="6" t="inlineStr"/>
+      <c r="CC29" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD29" s="6" t="inlineStr"/>
+      <c r="CE29" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -12791,6 +13227,18 @@
         </is>
       </c>
       <c r="CB30" s="6" t="inlineStr"/>
+      <c r="CC30" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD30" s="6" t="inlineStr"/>
+      <c r="CE30" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -12907,6 +13355,18 @@
         </is>
       </c>
       <c r="CB31" s="6" t="inlineStr"/>
+      <c r="CC31" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD31" s="6" t="inlineStr"/>
+      <c r="CE31" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -13006,6 +13466,18 @@
         </is>
       </c>
       <c r="CB32" s="6" t="inlineStr"/>
+      <c r="CC32" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD32" s="6" t="inlineStr"/>
+      <c r="CE32" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -13104,6 +13576,18 @@
         </is>
       </c>
       <c r="CB33" s="6" t="inlineStr"/>
+      <c r="CC33" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD33" s="6" t="inlineStr"/>
+      <c r="CE33" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -13204,6 +13688,18 @@
         </is>
       </c>
       <c r="CB34" s="6" t="inlineStr"/>
+      <c r="CC34" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD34" s="6" t="inlineStr"/>
+      <c r="CE34" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -13312,6 +13808,18 @@
         </is>
       </c>
       <c r="CB35" s="6" t="inlineStr"/>
+      <c r="CC35" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD35" s="6" t="inlineStr"/>
+      <c r="CE35" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -13362,6 +13870,18 @@
         </is>
       </c>
       <c r="CB36" s="6" t="inlineStr"/>
+      <c r="CC36" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD36" s="6" t="inlineStr"/>
+      <c r="CE36" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -13406,6 +13926,18 @@
         </is>
       </c>
       <c r="CB37" s="6" t="inlineStr"/>
+      <c r="CC37" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CD37" s="6" t="inlineStr"/>
+      <c r="CE37" s="10" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="CF37" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
